--- a/2026/SALTA 1167/Septiembre/SALTA1167-Septiembre.xlsx
+++ b/2026/SALTA 1167/Septiembre/SALTA1167-Septiembre.xlsx
@@ -1,33 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\SALTA 1167\Septiembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\SALTA 1167\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43EB461D-CD07-41F2-A781-D99F45E63FC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6146B3C0-67BC-4322-B5EC-B5C011725E1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
     <sheet name="PRORRATEO" sheetId="2" r:id="rId2"/>
-    <sheet name="EDESUR" sheetId="6" r:id="rId3"/>
+    <sheet name="EDESUR" sheetId="7" r:id="rId3"/>
     <sheet name="Anotaciones" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$96</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$94</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="155">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -432,30 +437,9 @@
     <t>A gaston le doble cobramos un sum erroneamente el mes pasado, corregir en agosto - Debe abonar 132.216,09 , pago 182.216,09</t>
   </si>
   <si>
-    <t>Transf 05/08</t>
-  </si>
-  <si>
-    <t>Transf 13/08</t>
-  </si>
-  <si>
-    <t>Transf 06/08</t>
-  </si>
-  <si>
-    <t>Transf 31/08</t>
-  </si>
-  <si>
-    <t>Easy Barracas - Compra de termotanque - Cuota 6  - Resta 0 cuotas de $157.988,29</t>
-  </si>
-  <si>
-    <t>SUM Mal cobrado</t>
-  </si>
-  <si>
     <t>Mantenimiento de cuenta</t>
   </si>
   <si>
-    <t>SALDO A 30/08</t>
-  </si>
-  <si>
     <t>Bonificado</t>
   </si>
   <si>
@@ -492,9 +476,6 @@
     <t xml:space="preserve">Honorario administracion - Mes de SEPTIEMBRE </t>
   </si>
   <si>
-    <t>Gonzalex Matias - Compra de paneles de luz fria y lamparas</t>
-  </si>
-  <si>
     <t>Transf 18/09</t>
   </si>
   <si>
@@ -502,6 +483,24 @@
   </si>
   <si>
     <t>Transf 13/09</t>
+  </si>
+  <si>
+    <t>Transf 01/09</t>
+  </si>
+  <si>
+    <t>Transf 30/09</t>
+  </si>
+  <si>
+    <t>Gonzalez Matias - Compra de paneles de luz fria y lamparas</t>
+  </si>
+  <si>
+    <t>Arreglo Cielorraso - Dpto. 1C</t>
+  </si>
+  <si>
+    <t>Transferido 1C</t>
+  </si>
+  <si>
+    <t>SALDO A 30/09</t>
   </si>
 </sst>
 </file>
@@ -520,7 +519,7 @@
     <numFmt numFmtId="169" formatCode="_-[$$-2C0A]\ * #,##0.0_-;\-[$$-2C0A]\ * #,##0.0_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="170" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
   </numFmts>
-  <fonts count="28" x14ac:knownFonts="1">
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -731,6 +730,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="14">
     <fill>
@@ -1168,7 +1174,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="248">
+  <cellXfs count="249">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1328,9 +1334,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1458,19 +1461,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="44" fontId="17" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="44" fontId="6" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="6" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="44" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="6" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="8" fontId="6" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="6" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1505,146 +1503,153 @@
     <xf numFmtId="164" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="44" fontId="22" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="7" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="28" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="28" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1724,9 +1729,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1764,9 +1769,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1799,9 +1804,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1834,9 +1856,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2010,22 +2049,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M100"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M98"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.5546875" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.5546875" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.5703125" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.44140625" customWidth="1"/>
+    <col min="12" max="12" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="12"/>
       <c r="B1" s="44" t="s">
         <v>73</v>
@@ -2034,7 +2073,7 @@
       <c r="D1" s="44"/>
       <c r="E1" s="45"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="13"/>
       <c r="B2" s="46" t="s">
         <v>14</v>
@@ -2043,16 +2082,16 @@
       <c r="D2" s="46"/>
       <c r="E2" s="47"/>
     </row>
-    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="13"/>
-      <c r="B3" s="211" t="s">
+      <c r="B3" s="205" t="s">
         <v>75</v>
       </c>
-      <c r="C3" s="211"/>
-      <c r="D3" s="211"/>
-      <c r="E3" s="212"/>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="205"/>
+      <c r="D3" s="205"/>
+      <c r="E3" s="206"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
         <v>0</v>
       </c>
@@ -2063,12 +2102,12 @@
       <c r="D4" s="17"/>
       <c r="E4" s="18"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>74</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="46" t="s">
@@ -2076,7 +2115,7 @@
       </c>
       <c r="E5" s="15"/>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
         <v>122</v>
       </c>
@@ -2087,57 +2126,57 @@
       </c>
       <c r="E6" s="18"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="214" t="s">
-        <v>150</v>
-      </c>
-      <c r="C8" s="214"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="214"/>
-      <c r="C9" s="214"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="214"/>
-      <c r="C10" s="214"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="213" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="208" t="s">
+        <v>143</v>
+      </c>
+      <c r="C8" s="208"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="208"/>
+      <c r="C9" s="208"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="208"/>
+      <c r="C10" s="208"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="207" t="s">
         <v>98</v>
       </c>
-      <c r="B13" s="213"/>
-      <c r="C13" s="213"/>
-      <c r="D13" s="213"/>
-      <c r="E13" s="213"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="213"/>
-      <c r="B14" s="213"/>
-      <c r="C14" s="213"/>
-      <c r="D14" s="213"/>
-      <c r="E14" s="213"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="213"/>
-      <c r="B15" s="213"/>
-      <c r="C15" s="213"/>
-      <c r="D15" s="213"/>
-      <c r="E15" s="213"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="213"/>
-      <c r="B16" s="213"/>
-      <c r="C16" s="213"/>
-      <c r="D16" s="213"/>
-      <c r="E16" s="213"/>
-    </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="207"/>
+      <c r="C13" s="207"/>
+      <c r="D13" s="207"/>
+      <c r="E13" s="207"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="207"/>
+      <c r="B14" s="207"/>
+      <c r="C14" s="207"/>
+      <c r="D14" s="207"/>
+      <c r="E14" s="207"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="207"/>
+      <c r="B15" s="207"/>
+      <c r="C15" s="207"/>
+      <c r="D15" s="207"/>
+      <c r="E15" s="207"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="207"/>
+      <c r="B16" s="207"/>
+      <c r="C16" s="207"/>
+      <c r="D16" s="207"/>
+      <c r="E16" s="207"/>
+    </row>
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
     </row>
-    <row r="19" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
         <v>101</v>
       </c>
@@ -2146,7 +2185,7 @@
       <c r="D20" s="6"/>
       <c r="E20" s="11"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="22" t="s">
         <v>76</v>
       </c>
@@ -2155,714 +2194,695 @@
       <c r="D21" s="98"/>
       <c r="E21" s="93"/>
     </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="207" t="s">
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="203" t="s">
         <v>112</v>
       </c>
-      <c r="B22" s="208"/>
-      <c r="C22" s="151"/>
-      <c r="D22" s="247">
+      <c r="B22" s="204"/>
+      <c r="C22" s="150"/>
+      <c r="D22" s="200">
         <v>510846.85</v>
       </c>
-      <c r="E22" s="146" t="s">
-        <v>156</v>
+      <c r="E22" s="145" t="s">
+        <v>148</v>
       </c>
       <c r="H22" s="82"/>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="207"/>
-      <c r="B23" s="208"/>
-      <c r="C23" s="151"/>
-      <c r="D23" s="180"/>
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="203"/>
+      <c r="B23" s="204"/>
+      <c r="C23" s="150"/>
+      <c r="D23" s="178"/>
       <c r="E23" s="94"/>
       <c r="H23" s="82"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="152" t="s">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="151" t="s">
         <v>9</v>
       </c>
-      <c r="B24" s="152"/>
-      <c r="C24" s="152"/>
-      <c r="D24" s="181"/>
-      <c r="E24" s="137">
+      <c r="B24" s="151"/>
+      <c r="C24" s="151"/>
+      <c r="D24" s="179"/>
+      <c r="E24" s="136">
         <f>SUM(D22:D23)</f>
         <v>510846.85</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="153" t="s">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="152" t="s">
         <v>17</v>
       </c>
-      <c r="B25" s="152"/>
-      <c r="C25" s="152"/>
-      <c r="D25" s="182"/>
-      <c r="E25" s="138"/>
-    </row>
-    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="207" t="s">
+      <c r="B25" s="151"/>
+      <c r="C25" s="151"/>
+      <c r="D25" s="180"/>
+      <c r="E25" s="137"/>
+    </row>
+    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="203" t="s">
         <v>117</v>
       </c>
-      <c r="B26" s="208"/>
-      <c r="C26" s="154"/>
-      <c r="D26" s="183">
-        <v>79873.05</v>
+      <c r="B26" s="204"/>
+      <c r="C26" s="153"/>
+      <c r="D26" s="245">
+        <v>74244</v>
       </c>
       <c r="E26" s="96" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="152" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="151" t="s">
         <v>1</v>
       </c>
-      <c r="B27" s="152"/>
-      <c r="C27" s="152"/>
-      <c r="D27" s="181"/>
+      <c r="B27" s="151"/>
+      <c r="C27" s="151"/>
+      <c r="D27" s="179"/>
       <c r="E27" s="104">
         <f>SUM(D26:D26)</f>
-        <v>79873.05</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="153" t="s">
+        <v>74244</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="152" t="s">
         <v>10</v>
       </c>
-      <c r="B28" s="155"/>
-      <c r="C28" s="155"/>
-      <c r="D28" s="184"/>
-      <c r="E28" s="139"/>
-    </row>
-    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="154"/>
+      <c r="C28" s="154"/>
+      <c r="D28" s="181"/>
+      <c r="E28" s="138"/>
+    </row>
+    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="65" t="s">
         <v>66</v>
       </c>
       <c r="B29" s="65"/>
       <c r="C29" s="65"/>
-      <c r="D29" s="95">
-        <v>14396.25</v>
+      <c r="D29" s="199">
+        <v>265234.65000000002</v>
       </c>
       <c r="E29" s="96" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="65" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B30" s="65"/>
       <c r="C30" s="65"/>
-      <c r="D30" s="246">
-        <v>265234.65000000002</v>
-      </c>
-      <c r="E30" s="96" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D30" s="199">
+        <v>8972.48</v>
+      </c>
+      <c r="E30" s="145" t="str">
+        <f>E31</f>
+        <v>Transf 07/09</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="65" t="s">
         <v>65</v>
       </c>
-      <c r="B31" s="65"/>
+      <c r="B31" s="155"/>
       <c r="C31" s="65"/>
-      <c r="D31" s="246">
-        <v>8972.48</v>
-      </c>
-      <c r="E31" s="146" t="str">
-        <f>E32</f>
-        <v>Transf 07/09</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="65" t="s">
-        <v>65</v>
-      </c>
-      <c r="B32" s="156"/>
+      <c r="D31" s="199">
+        <v>550258.93999999994</v>
+      </c>
+      <c r="E31" s="96" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="201" t="s">
+        <v>67</v>
+      </c>
+      <c r="B32" s="202"/>
       <c r="C32" s="65"/>
-      <c r="D32" s="246">
-        <v>550258.93999999994</v>
+      <c r="D32" s="199">
+        <v>872785.72</v>
       </c>
       <c r="E32" s="96" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="209" t="s">
-        <v>67</v>
-      </c>
-      <c r="B33" s="210"/>
+        <v>147</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="156" t="s">
+        <v>77</v>
+      </c>
+      <c r="B33" s="157"/>
       <c r="C33" s="65"/>
-      <c r="D33" s="246">
-        <v>872785.72</v>
+      <c r="D33" s="199">
+        <v>30111.39</v>
       </c>
       <c r="E33" s="96" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="157" t="s">
-        <v>77</v>
-      </c>
-      <c r="B34" s="158"/>
-      <c r="C34" s="65"/>
-      <c r="D34" s="95">
-        <v>28704.880000000001</v>
-      </c>
-      <c r="E34" s="96" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="152" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="151" t="s">
         <v>2</v>
       </c>
-      <c r="B35" s="152"/>
-      <c r="C35" s="152"/>
-      <c r="D35" s="185"/>
-      <c r="E35" s="140">
-        <f>SUM(D29:D34)</f>
-        <v>1740352.92</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="153"/>
-      <c r="B36" s="152"/>
-      <c r="C36" s="152"/>
-      <c r="D36" s="181"/>
-      <c r="E36" s="141"/>
-    </row>
-    <row r="37" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="207" t="s">
+      <c r="B34" s="151"/>
+      <c r="C34" s="151"/>
+      <c r="D34" s="182"/>
+      <c r="E34" s="139">
+        <f>SUM(D29:D33)</f>
+        <v>1727363.18</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="152"/>
+      <c r="B35" s="151"/>
+      <c r="C35" s="151"/>
+      <c r="D35" s="179"/>
+      <c r="E35" s="140"/>
+    </row>
+    <row r="36" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="203" t="s">
         <v>114</v>
       </c>
-      <c r="B37" s="208"/>
+      <c r="B36" s="204"/>
+      <c r="C36" s="65"/>
+      <c r="D36" s="199">
+        <v>82000</v>
+      </c>
+      <c r="E36" s="96" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="158" t="s">
+        <v>151</v>
+      </c>
+      <c r="B37" s="159"/>
       <c r="C37" s="65"/>
-      <c r="D37" s="95">
-        <v>82000</v>
+      <c r="D37" s="199">
+        <v>52253.440000000002</v>
       </c>
       <c r="E37" s="96" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="203" t="s">
+        <v>152</v>
+      </c>
+      <c r="B38" s="204"/>
+      <c r="C38" s="65"/>
+      <c r="D38" s="248">
+        <v>200000</v>
+      </c>
+      <c r="E38" s="96" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="151" t="s">
+        <v>6</v>
+      </c>
+      <c r="B39" s="152"/>
+      <c r="C39" s="152"/>
+      <c r="D39" s="152"/>
+      <c r="E39" s="104">
+        <f>SUM(D36:D38)</f>
+        <v>334253.44</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="152" t="s">
+        <v>11</v>
+      </c>
+      <c r="B40" s="152"/>
+      <c r="C40" s="152"/>
+      <c r="D40" s="98"/>
+      <c r="E40" s="141"/>
+    </row>
+    <row r="41" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="203" t="s">
+        <v>145</v>
+      </c>
+      <c r="B41" s="204"/>
+      <c r="C41" s="150"/>
+      <c r="D41" s="243">
+        <v>190000</v>
+      </c>
+      <c r="E41" s="142" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="151" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42" s="151"/>
+      <c r="C42" s="151"/>
+      <c r="D42" s="179"/>
+      <c r="E42" s="136">
+        <f>SUM(D41:D41)</f>
+        <v>190000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="152" t="s">
+        <v>8</v>
+      </c>
+      <c r="B43" s="160"/>
+      <c r="C43" s="151"/>
+      <c r="D43" s="183"/>
+      <c r="E43" s="104"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="65" t="s">
+        <v>133</v>
+      </c>
+      <c r="B44" s="65" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="159" t="s">
-        <v>153</v>
-      </c>
-      <c r="B38" s="160"/>
-      <c r="C38" s="65"/>
-      <c r="D38" s="246">
-        <v>62399.97</v>
-      </c>
-      <c r="E38" s="96" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="207" t="s">
-        <v>137</v>
-      </c>
-      <c r="B39" s="208"/>
-      <c r="C39" s="65"/>
-      <c r="D39" s="68">
-        <v>157988.29</v>
-      </c>
-      <c r="E39" s="96"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="152" t="s">
-        <v>6</v>
-      </c>
-      <c r="B40" s="153"/>
-      <c r="C40" s="153"/>
-      <c r="D40" s="153"/>
-      <c r="E40" s="104">
-        <f>SUM(D37:D39)</f>
-        <v>302388.26</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" s="153" t="s">
-        <v>11</v>
-      </c>
-      <c r="B41" s="153"/>
-      <c r="C41" s="153"/>
-      <c r="D41" s="98"/>
-      <c r="E41" s="142"/>
-    </row>
-    <row r="42" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="207" t="s">
-        <v>152</v>
-      </c>
-      <c r="B42" s="208"/>
-      <c r="C42" s="151"/>
-      <c r="D42" s="186">
-        <v>190000</v>
-      </c>
-      <c r="E42" s="143" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" s="152" t="s">
+      <c r="C44" s="65"/>
+      <c r="D44" s="95"/>
+      <c r="E44" s="143"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="65" t="s">
+        <v>113</v>
+      </c>
+      <c r="B45" s="65"/>
+      <c r="C45" s="65"/>
+      <c r="D45" s="199">
+        <v>35494.269999999997</v>
+      </c>
+      <c r="E45" s="144"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="161" t="s">
         <v>9</v>
       </c>
-      <c r="B43" s="152"/>
-      <c r="C43" s="152"/>
-      <c r="D43" s="181"/>
-      <c r="E43" s="137">
-        <f>SUM(D42:D42)</f>
-        <v>190000</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44" s="153" t="s">
-        <v>8</v>
-      </c>
-      <c r="B44" s="161"/>
-      <c r="C44" s="152"/>
-      <c r="D44" s="187"/>
-      <c r="E44" s="104"/>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45" s="65" t="s">
-        <v>139</v>
-      </c>
-      <c r="B45" s="65" t="s">
-        <v>141</v>
-      </c>
-      <c r="C45" s="65"/>
-      <c r="D45" s="95"/>
-      <c r="E45" s="144"/>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46" s="65" t="s">
-        <v>113</v>
-      </c>
-      <c r="B46" s="65"/>
-      <c r="C46" s="65"/>
-      <c r="D46" s="95">
-        <f>374.4+864+181.44+1597.68+33590.8</f>
-        <v>36608.320000000007</v>
-      </c>
-      <c r="E46" s="145"/>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47" s="162" t="s">
-        <v>9</v>
-      </c>
-      <c r="B47" s="162"/>
-      <c r="C47" s="162"/>
-      <c r="D47" s="188"/>
-      <c r="E47" s="104">
-        <f>SUM(D45:D46)</f>
-        <v>36608.320000000007</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="65"/>
-      <c r="B48" s="65"/>
-      <c r="C48" s="65"/>
-      <c r="D48" s="65"/>
-      <c r="E48" s="70"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49" s="163" t="s">
+      <c r="B46" s="161"/>
+      <c r="C46" s="161"/>
+      <c r="D46" s="184"/>
+      <c r="E46" s="104">
+        <f>SUM(D44:D45)</f>
+        <v>35494.269999999997</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="65"/>
+      <c r="B47" s="65"/>
+      <c r="C47" s="65"/>
+      <c r="D47" s="65"/>
+      <c r="E47" s="70"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="162" t="s">
         <v>97</v>
       </c>
-      <c r="B49" s="163"/>
-      <c r="C49" s="163"/>
-      <c r="D49" s="71"/>
-      <c r="E49" s="105">
+      <c r="B48" s="162"/>
+      <c r="C48" s="162"/>
+      <c r="D48" s="71"/>
+      <c r="E48" s="105">
         <f>3000000-2926731.74</f>
         <v>73268.259999999776</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="164"/>
-      <c r="B50" s="72"/>
-      <c r="C50" s="72"/>
-      <c r="D50" s="72"/>
-      <c r="E50" s="73"/>
-      <c r="F50" s="27"/>
-    </row>
-    <row r="51" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="165" t="s">
+    <row r="49" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="163"/>
+      <c r="B49" s="72"/>
+      <c r="C49" s="72"/>
+      <c r="D49" s="72"/>
+      <c r="E49" s="73"/>
+      <c r="F49" s="27"/>
+    </row>
+    <row r="50" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="164" t="s">
         <v>93</v>
       </c>
-      <c r="B51" s="166"/>
-      <c r="C51" s="74"/>
-      <c r="D51" s="74"/>
-      <c r="E51" s="75">
-        <f>(SUM(E21:E49))</f>
-        <v>2933337.6599999997</v>
-      </c>
-      <c r="F51" s="92"/>
-      <c r="G51" s="27"/>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B50" s="165"/>
+      <c r="C50" s="74"/>
+      <c r="D50" s="74"/>
+      <c r="E50" s="75">
+        <f>(SUM(E21:E48))</f>
+        <v>2945469.9999999995</v>
+      </c>
+      <c r="F50" s="92"/>
+      <c r="G50" s="27"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="72"/>
+      <c r="B51" s="72"/>
+      <c r="C51" s="72"/>
+      <c r="D51" s="72"/>
+      <c r="E51" s="72"/>
+    </row>
+    <row r="52" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="72"/>
       <c r="B52" s="72"/>
       <c r="C52" s="72"/>
       <c r="D52" s="72"/>
       <c r="E52" s="72"/>
-    </row>
-    <row r="53" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="72"/>
-      <c r="B53" s="72"/>
-      <c r="C53" s="72"/>
-      <c r="D53" s="72"/>
-      <c r="E53" s="72"/>
-      <c r="H53" s="99"/>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A54" s="167" t="s">
+      <c r="H52" s="99"/>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="166" t="s">
         <v>94</v>
       </c>
-      <c r="B54" s="168"/>
-      <c r="C54" s="169"/>
-      <c r="D54" s="76"/>
-      <c r="E54" s="77"/>
-    </row>
-    <row r="55" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="170"/>
-      <c r="B55" s="158"/>
+      <c r="B53" s="167"/>
+      <c r="C53" s="168"/>
+      <c r="D53" s="76"/>
+      <c r="E53" s="77"/>
+    </row>
+    <row r="54" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="169"/>
+      <c r="B54" s="157"/>
+      <c r="C54" s="65"/>
+      <c r="D54" s="68"/>
+      <c r="E54" s="66"/>
+    </row>
+    <row r="55" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="211"/>
+      <c r="B55" s="211"/>
       <c r="C55" s="65"/>
-      <c r="D55" s="68"/>
+      <c r="D55" s="95"/>
       <c r="E55" s="66"/>
     </row>
-    <row r="56" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="206"/>
-      <c r="B56" s="206"/>
-      <c r="C56" s="65"/>
-      <c r="D56" s="95"/>
-      <c r="E56" s="66"/>
-    </row>
-    <row r="57" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="4"/>
-      <c r="B57" s="4"/>
+    <row r="56" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="4"/>
+      <c r="B56" s="4"/>
+      <c r="C56" s="4"/>
+      <c r="D56" s="4"/>
+      <c r="E56" s="4"/>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="67"/>
+      <c r="B57" s="69"/>
       <c r="C57" s="4"/>
-      <c r="D57" s="4"/>
-      <c r="E57" s="4"/>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A58" s="67"/>
-      <c r="B58" s="69"/>
-      <c r="C58" s="4"/>
-      <c r="D58" s="68"/>
-      <c r="E58" s="66"/>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A59" s="32"/>
-      <c r="B59" s="31"/>
-      <c r="C59" s="31"/>
-      <c r="D59" s="36"/>
-      <c r="E59" s="36">
-        <f>SUM(D55:D58)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="61" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A62" s="20" t="s">
+      <c r="D57" s="68"/>
+      <c r="E57" s="66"/>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="32"/>
+      <c r="B58" s="31"/>
+      <c r="C58" s="31"/>
+      <c r="D58" s="36"/>
+      <c r="E58" s="36">
+        <f>SUM(D54:D57)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="B62" s="20"/>
-      <c r="C62" s="20"/>
-      <c r="D62" s="21"/>
-      <c r="E62" s="135"/>
-    </row>
-    <row r="63" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="64" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="2" t="s">
+      <c r="B61" s="20"/>
+      <c r="C61" s="20"/>
+      <c r="D61" s="21"/>
+      <c r="E61" s="134"/>
+    </row>
+    <row r="62" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="63" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B64" s="7"/>
-      <c r="C64" s="3"/>
-      <c r="D64" s="3"/>
-      <c r="E64" s="43">
-        <f>E59+E62</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="66" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B63" s="7"/>
+      <c r="C63" s="3"/>
+      <c r="D63" s="3"/>
+      <c r="E63" s="43">
+        <f>E58+E61</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="65" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="63" t="s">
+        <v>102</v>
+      </c>
+      <c r="B65" s="64">
+        <f>E50</f>
+        <v>2945469.9999999995</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="63" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B66" s="64">
-        <f>E51</f>
-        <v>2933337.6599999997</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <f>E50-E48</f>
+        <v>2872201.7399999998</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="63" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B67" s="64">
-        <f>E51-E49</f>
-        <v>2860069.4</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <f>E63-E61</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="63" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B68" s="64">
-        <f>E64-E62</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="63" t="s">
-        <v>105</v>
-      </c>
-      <c r="B69" s="64">
-        <f>E64</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A71"/>
-      <c r="B71" s="26"/>
+        <f>E63</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A70"/>
+      <c r="B70" s="26"/>
+      <c r="C70" s="24"/>
+    </row>
+    <row r="71" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="84" t="s">
+        <v>106</v>
+      </c>
+      <c r="B71" s="110">
+        <v>231226.35000000335</v>
+      </c>
       <c r="C71" s="24"/>
-    </row>
-    <row r="72" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="84" t="s">
-        <v>106</v>
-      </c>
-      <c r="B72" s="111">
-        <v>231226.35000000335</v>
-      </c>
-      <c r="C72" s="24"/>
-      <c r="D72" s="30"/>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D71" s="30"/>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="35" t="s">
+        <v>99</v>
+      </c>
+      <c r="B72" s="89">
+        <f>-B66</f>
+        <v>-2872201.7399999998</v>
+      </c>
+      <c r="E72" s="27"/>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="35" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="B73" s="89">
+        <f>B93</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="35" t="s">
+        <v>108</v>
+      </c>
+      <c r="B74" s="90">
+        <f>PRORRATEO!G36-B80</f>
+        <v>3060391.1300000008</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="87" t="s">
+        <v>110</v>
+      </c>
+      <c r="B75" s="88">
+        <f>SUM(B71:C74)</f>
+        <v>419415.74000000441</v>
+      </c>
+      <c r="D75" s="27"/>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="85"/>
+      <c r="B76" s="85"/>
+      <c r="D76" s="27"/>
+      <c r="E76" s="26"/>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="84" t="s">
+        <v>107</v>
+      </c>
+      <c r="B77" s="110">
+        <v>1000000</v>
+      </c>
+      <c r="D77" s="26"/>
+      <c r="E77" s="27"/>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="35" t="s">
+        <v>100</v>
+      </c>
+      <c r="B78" s="89">
         <f>-B67</f>
-        <v>-2860069.4</v>
-      </c>
-      <c r="E73" s="27"/>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A74" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="D78" s="27"/>
+      <c r="E78" s="27"/>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="B74" s="89">
-        <f>B95</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A75" s="35" t="s">
-        <v>108</v>
-      </c>
-      <c r="B75" s="90">
-        <f>PRORRATEO!G36-B82</f>
-        <v>3248082.4500000007</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A76" s="91" t="s">
-        <v>138</v>
-      </c>
-      <c r="B76" s="100">
-        <v>-50000</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="87" t="s">
-        <v>110</v>
-      </c>
-      <c r="B77" s="88">
-        <f>SUM(B72:C76)</f>
-        <v>569239.4000000041</v>
-      </c>
-      <c r="D77" s="27"/>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A78" s="85"/>
-      <c r="B78" s="85"/>
-      <c r="D78" s="27"/>
-      <c r="E78" s="26"/>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A79" s="84" t="s">
-        <v>107</v>
-      </c>
-      <c r="B79" s="111">
+      <c r="B79" s="89">
+        <f>B101</f>
+        <v>0</v>
+      </c>
+      <c r="D79" s="27"/>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="B80" s="90">
+        <v>0</v>
+      </c>
+      <c r="D80" s="135"/>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A81" s="91" t="s">
+        <v>24</v>
+      </c>
+      <c r="B81" s="100"/>
+      <c r="D81" s="27"/>
+      <c r="E81" s="27"/>
+      <c r="F81" s="26"/>
+    </row>
+    <row r="82" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="87" t="s">
+        <v>111</v>
+      </c>
+      <c r="B82" s="88">
+        <f>SUM(B77:C81)</f>
         <v>1000000</v>
       </c>
-      <c r="D79" s="26"/>
-      <c r="E79" s="27"/>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A80" s="35" t="s">
-        <v>100</v>
-      </c>
-      <c r="B80" s="89">
-        <f>-B68</f>
-        <v>0</v>
-      </c>
-      <c r="D80" s="27"/>
-      <c r="E80" s="27"/>
-    </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A81" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="B81" s="89">
-        <f>B103</f>
-        <v>0</v>
-      </c>
-      <c r="D81" s="27"/>
-    </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A82" s="35" t="s">
-        <v>109</v>
-      </c>
-      <c r="B82" s="90">
-        <v>0</v>
-      </c>
-      <c r="D82" s="136"/>
-    </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A83" s="91" t="s">
-        <v>24</v>
-      </c>
-      <c r="B83" s="100"/>
-      <c r="D83" s="27"/>
-      <c r="E83" s="27"/>
-      <c r="F83" s="26"/>
-    </row>
-    <row r="84" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="87" t="s">
-        <v>111</v>
-      </c>
-      <c r="B84" s="88">
-        <f>SUM(B79:C83)</f>
-        <v>1000000</v>
-      </c>
-      <c r="D84" s="27"/>
-      <c r="F84" s="27"/>
-    </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A85" s="85"/>
-      <c r="B85" s="85"/>
-    </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A86" s="85"/>
-      <c r="B86" s="85"/>
-    </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A87" s="84" t="s">
+      <c r="D82" s="27"/>
+      <c r="E82" s="27"/>
+      <c r="F82" s="27"/>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A83" s="85"/>
+      <c r="B83" s="85"/>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A84" s="85"/>
+      <c r="B84" s="85"/>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A85" s="84" t="s">
         <v>124</v>
       </c>
-      <c r="B87" s="111">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A88" s="35" t="s">
+      <c r="B85" s="110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A86" s="35" t="s">
         <v>125</v>
       </c>
-      <c r="B88" s="89">
-        <v>1025063.51</v>
-      </c>
-    </row>
-    <row r="89" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="87" t="s">
-        <v>140</v>
-      </c>
-      <c r="B89" s="88">
+      <c r="B86" s="89">
         <v>1054849.6000000001</v>
       </c>
     </row>
-    <row r="90" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A91" s="205" t="s">
+    <row r="87" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="87" t="s">
+        <v>154</v>
+      </c>
+      <c r="B87" s="88">
+        <v>1070612.72</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A89" s="210" t="s">
         <v>18</v>
       </c>
-      <c r="B91" s="205"/>
-      <c r="C91" s="205"/>
-    </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A92" s="205"/>
-      <c r="B92" s="205"/>
-      <c r="C92" s="205"/>
-    </row>
-    <row r="93" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="79"/>
-      <c r="B93" s="23"/>
-      <c r="C93" s="23">
+      <c r="B89" s="210"/>
+      <c r="C89" s="210"/>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A90" s="210"/>
+      <c r="B90" s="210"/>
+      <c r="C90" s="210"/>
+    </row>
+    <row r="91" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="79"/>
+      <c r="B91" s="23"/>
+      <c r="C91" s="23">
         <v>40000</v>
       </c>
-      <c r="E93" s="92"/>
-    </row>
-    <row r="94" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="79"/>
-      <c r="B94" s="81"/>
-      <c r="C94" s="78"/>
-      <c r="D94" s="92"/>
-    </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A95" s="28" t="s">
+      <c r="E91" s="92"/>
+    </row>
+    <row r="92" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="79"/>
+      <c r="B92" s="81"/>
+      <c r="C92" s="78"/>
+      <c r="D92" s="92"/>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A93" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="B95" s="80">
-        <f>SUM(B93:B94)</f>
-        <v>0</v>
-      </c>
-      <c r="C95" s="29"/>
-    </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M96" s="5"/>
-    </row>
-    <row r="97" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="204"/>
-      <c r="B97" s="204"/>
-      <c r="C97" s="204"/>
-      <c r="D97" s="204"/>
-      <c r="E97" s="204"/>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A98" s="204"/>
-      <c r="B98" s="204"/>
-      <c r="C98" s="204"/>
-      <c r="D98" s="204"/>
-      <c r="E98" s="204"/>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A99" s="204"/>
-      <c r="B99" s="204"/>
-      <c r="C99" s="204"/>
-      <c r="D99" s="204"/>
-      <c r="E99" s="204"/>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A100" s="204"/>
-      <c r="B100" s="204"/>
-      <c r="C100" s="204"/>
-      <c r="D100" s="204"/>
-      <c r="E100" s="204"/>
+      <c r="B93" s="80">
+        <f>SUM(B91:B92)</f>
+        <v>0</v>
+      </c>
+      <c r="C93" s="29"/>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M94" s="5"/>
+    </row>
+    <row r="95" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="209"/>
+      <c r="B95" s="209"/>
+      <c r="C95" s="209"/>
+      <c r="D95" s="209"/>
+      <c r="E95" s="209"/>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A96" s="209"/>
+      <c r="B96" s="209"/>
+      <c r="C96" s="209"/>
+      <c r="D96" s="209"/>
+      <c r="E96" s="209"/>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="209"/>
+      <c r="B97" s="209"/>
+      <c r="C97" s="209"/>
+      <c r="D97" s="209"/>
+      <c r="E97" s="209"/>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="209"/>
+      <c r="B98" s="209"/>
+      <c r="C98" s="209"/>
+      <c r="D98" s="209"/>
+      <c r="E98" s="209"/>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A95:E98"/>
+    <mergeCell ref="A89:C90"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A32:B32"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="B8:C10"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A97:E100"/>
-    <mergeCell ref="A91:C92"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A42:B42"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2873,298 +2893,298 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R44"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="4.44140625" customWidth="1"/>
-    <col min="3" max="3" width="18.5546875" customWidth="1"/>
+    <col min="1" max="2" width="4.42578125" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="8.44140625" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="10.5546875" customWidth="1"/>
-    <col min="9" max="9" width="9.5546875" customWidth="1"/>
-    <col min="10" max="10" width="12.44140625" customWidth="1"/>
-    <col min="11" max="11" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5546875" customWidth="1"/>
-    <col min="13" max="13" width="13.44140625" customWidth="1"/>
-    <col min="14" max="14" width="14.5546875" customWidth="1"/>
+    <col min="5" max="5" width="8.42578125" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="10.5703125" customWidth="1"/>
+    <col min="9" max="9" width="9.5703125" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" customWidth="1"/>
     <col min="15" max="15" width="12" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="14.44140625" customWidth="1"/>
-    <col min="17" max="17" width="7.44140625" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" customWidth="1"/>
+    <col min="17" max="17" width="7.42578125" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="112"/>
-      <c r="B1" s="113"/>
-      <c r="C1" s="114"/>
-      <c r="D1" s="114"/>
-      <c r="E1" s="220"/>
-      <c r="F1" s="220"/>
-      <c r="G1" s="220"/>
-      <c r="H1" s="220"/>
-      <c r="I1" s="220"/>
-      <c r="J1" s="220"/>
-      <c r="K1" s="220"/>
-      <c r="L1" s="220"/>
-      <c r="M1" s="220"/>
-      <c r="N1" s="220"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="115"/>
-    </row>
-    <row r="2" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="116"/>
-      <c r="B2" s="117"/>
-      <c r="C2" s="118"/>
-      <c r="D2" s="119"/>
-      <c r="E2" s="119" t="s">
+    <row r="1" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="111"/>
+      <c r="B1" s="112"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="212"/>
+      <c r="F1" s="212"/>
+      <c r="G1" s="212"/>
+      <c r="H1" s="212"/>
+      <c r="I1" s="212"/>
+      <c r="J1" s="212"/>
+      <c r="K1" s="212"/>
+      <c r="L1" s="212"/>
+      <c r="M1" s="212"/>
+      <c r="N1" s="212"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="114"/>
+    </row>
+    <row r="2" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="115"/>
+      <c r="B2" s="116"/>
+      <c r="C2" s="117"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="118" t="s">
         <v>92</v>
       </c>
-      <c r="F2" s="119"/>
-      <c r="G2" s="120">
-        <v>0</v>
-      </c>
-      <c r="H2" s="119"/>
-      <c r="I2" s="119"/>
-      <c r="J2" s="119" t="s">
+      <c r="F2" s="118"/>
+      <c r="G2" s="119">
+        <v>0</v>
+      </c>
+      <c r="H2" s="118"/>
+      <c r="I2" s="118"/>
+      <c r="J2" s="118" t="s">
         <v>91</v>
       </c>
-      <c r="K2" s="121">
+      <c r="K2" s="120">
         <v>3000000</v>
       </c>
-      <c r="L2" s="121"/>
-      <c r="M2" s="121"/>
-      <c r="N2" s="122"/>
-      <c r="O2" s="123"/>
-      <c r="P2" s="124"/>
+      <c r="L2" s="120"/>
+      <c r="M2" s="120"/>
+      <c r="N2" s="121"/>
+      <c r="O2" s="122"/>
+      <c r="P2" s="123"/>
       <c r="Q2" s="19"/>
     </row>
-    <row r="3" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="116"/>
-      <c r="B3" s="117"/>
-      <c r="C3" s="118"/>
-      <c r="D3" s="118"/>
-      <c r="E3" s="118"/>
-      <c r="F3" s="118"/>
-      <c r="G3" s="125"/>
-      <c r="H3" s="118"/>
-      <c r="I3" s="118"/>
-      <c r="J3" s="118"/>
-      <c r="K3" s="118"/>
-      <c r="L3" s="118"/>
-      <c r="M3" s="118"/>
-      <c r="N3" s="122"/>
-      <c r="O3" s="123"/>
-      <c r="P3" s="124"/>
+    <row r="3" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="115"/>
+      <c r="B3" s="116"/>
+      <c r="C3" s="117"/>
+      <c r="D3" s="117"/>
+      <c r="E3" s="117"/>
+      <c r="F3" s="117"/>
+      <c r="G3" s="124"/>
+      <c r="H3" s="117"/>
+      <c r="I3" s="117"/>
+      <c r="J3" s="117"/>
+      <c r="K3" s="117"/>
+      <c r="L3" s="117"/>
+      <c r="M3" s="117"/>
+      <c r="N3" s="121"/>
+      <c r="O3" s="122"/>
+      <c r="P3" s="123"/>
       <c r="Q3" s="19"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="227" t="s">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="223" t="s">
         <v>119</v>
       </c>
-      <c r="B4" s="228"/>
-      <c r="C4" s="228"/>
-      <c r="D4" s="228"/>
-      <c r="E4" s="228"/>
-      <c r="F4" s="228"/>
-      <c r="G4" s="228"/>
-      <c r="H4" s="228"/>
-      <c r="I4" s="228"/>
-      <c r="J4" s="228"/>
-      <c r="K4" s="228"/>
-      <c r="L4" s="228"/>
-      <c r="M4" s="228"/>
-      <c r="N4" s="228"/>
-      <c r="O4" s="228"/>
-      <c r="P4" s="229"/>
+      <c r="B4" s="224"/>
+      <c r="C4" s="224"/>
+      <c r="D4" s="224"/>
+      <c r="E4" s="224"/>
+      <c r="F4" s="224"/>
+      <c r="G4" s="224"/>
+      <c r="H4" s="224"/>
+      <c r="I4" s="224"/>
+      <c r="J4" s="224"/>
+      <c r="K4" s="224"/>
+      <c r="L4" s="224"/>
+      <c r="M4" s="224"/>
+      <c r="N4" s="224"/>
+      <c r="O4" s="224"/>
+      <c r="P4" s="225"/>
       <c r="Q4" s="19"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A5" s="230"/>
-      <c r="B5" s="231"/>
-      <c r="C5" s="231"/>
-      <c r="D5" s="231"/>
-      <c r="E5" s="231"/>
-      <c r="F5" s="231"/>
-      <c r="G5" s="231"/>
-      <c r="H5" s="231"/>
-      <c r="I5" s="231"/>
-      <c r="J5" s="231"/>
-      <c r="K5" s="231"/>
-      <c r="L5" s="231"/>
-      <c r="M5" s="231"/>
-      <c r="N5" s="231"/>
-      <c r="O5" s="231"/>
-      <c r="P5" s="232"/>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" s="226"/>
+      <c r="B5" s="227"/>
+      <c r="C5" s="227"/>
+      <c r="D5" s="227"/>
+      <c r="E5" s="227"/>
+      <c r="F5" s="227"/>
+      <c r="G5" s="227"/>
+      <c r="H5" s="227"/>
+      <c r="I5" s="227"/>
+      <c r="J5" s="227"/>
+      <c r="K5" s="227"/>
+      <c r="L5" s="227"/>
+      <c r="M5" s="227"/>
+      <c r="N5" s="227"/>
+      <c r="O5" s="227"/>
+      <c r="P5" s="228"/>
       <c r="Q5" s="19"/>
     </row>
-    <row r="6" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="230"/>
-      <c r="B6" s="231"/>
-      <c r="C6" s="231"/>
-      <c r="D6" s="231"/>
-      <c r="E6" s="231"/>
-      <c r="F6" s="231"/>
-      <c r="G6" s="231"/>
-      <c r="H6" s="231"/>
-      <c r="I6" s="231"/>
-      <c r="J6" s="231"/>
-      <c r="K6" s="231"/>
-      <c r="L6" s="231"/>
-      <c r="M6" s="231"/>
-      <c r="N6" s="231"/>
-      <c r="O6" s="231"/>
-      <c r="P6" s="232"/>
+    <row r="6" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="226"/>
+      <c r="B6" s="227"/>
+      <c r="C6" s="227"/>
+      <c r="D6" s="227"/>
+      <c r="E6" s="227"/>
+      <c r="F6" s="227"/>
+      <c r="G6" s="227"/>
+      <c r="H6" s="227"/>
+      <c r="I6" s="227"/>
+      <c r="J6" s="227"/>
+      <c r="K6" s="227"/>
+      <c r="L6" s="227"/>
+      <c r="M6" s="227"/>
+      <c r="N6" s="227"/>
+      <c r="O6" s="227"/>
+      <c r="P6" s="228"/>
       <c r="Q6" s="19"/>
     </row>
-    <row r="7" spans="1:17" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="230"/>
-      <c r="B7" s="231"/>
-      <c r="C7" s="231"/>
-      <c r="D7" s="231"/>
-      <c r="E7" s="231"/>
-      <c r="F7" s="231"/>
-      <c r="G7" s="231"/>
-      <c r="H7" s="231"/>
-      <c r="I7" s="231"/>
-      <c r="J7" s="231"/>
-      <c r="K7" s="231"/>
-      <c r="L7" s="231"/>
-      <c r="M7" s="231"/>
-      <c r="N7" s="231"/>
-      <c r="O7" s="231"/>
-      <c r="P7" s="232"/>
+    <row r="7" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="226"/>
+      <c r="B7" s="227"/>
+      <c r="C7" s="227"/>
+      <c r="D7" s="227"/>
+      <c r="E7" s="227"/>
+      <c r="F7" s="227"/>
+      <c r="G7" s="227"/>
+      <c r="H7" s="227"/>
+      <c r="I7" s="227"/>
+      <c r="J7" s="227"/>
+      <c r="K7" s="227"/>
+      <c r="L7" s="227"/>
+      <c r="M7" s="227"/>
+      <c r="N7" s="227"/>
+      <c r="O7" s="227"/>
+      <c r="P7" s="228"/>
       <c r="Q7" s="19"/>
     </row>
-    <row r="8" spans="1:17" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="233"/>
-      <c r="B8" s="234"/>
-      <c r="C8" s="234"/>
-      <c r="D8" s="234"/>
-      <c r="E8" s="234"/>
-      <c r="F8" s="234"/>
-      <c r="G8" s="234"/>
-      <c r="H8" s="234"/>
-      <c r="I8" s="234"/>
-      <c r="J8" s="234"/>
-      <c r="K8" s="234"/>
-      <c r="L8" s="234"/>
-      <c r="M8" s="234"/>
-      <c r="N8" s="234"/>
-      <c r="O8" s="234"/>
-      <c r="P8" s="235"/>
-    </row>
-    <row r="9" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="238" t="s">
+    <row r="8" spans="1:17" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="229"/>
+      <c r="B8" s="230"/>
+      <c r="C8" s="230"/>
+      <c r="D8" s="230"/>
+      <c r="E8" s="230"/>
+      <c r="F8" s="230"/>
+      <c r="G8" s="230"/>
+      <c r="H8" s="230"/>
+      <c r="I8" s="230"/>
+      <c r="J8" s="230"/>
+      <c r="K8" s="230"/>
+      <c r="L8" s="230"/>
+      <c r="M8" s="230"/>
+      <c r="N8" s="230"/>
+      <c r="O8" s="230"/>
+      <c r="P8" s="231"/>
+    </row>
+    <row r="9" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="234" t="s">
         <v>118</v>
       </c>
-      <c r="B9" s="239"/>
-      <c r="C9" s="239"/>
-      <c r="D9" s="239"/>
-      <c r="E9" s="239"/>
-      <c r="F9" s="239"/>
-      <c r="G9" s="239"/>
-      <c r="H9" s="239"/>
-      <c r="I9" s="239"/>
-      <c r="J9" s="239"/>
-      <c r="K9" s="239"/>
-      <c r="L9" s="239"/>
-      <c r="M9" s="239"/>
-      <c r="N9" s="239"/>
-      <c r="O9" s="239"/>
-      <c r="P9" s="239"/>
-    </row>
-    <row r="10" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="240" t="s">
+      <c r="B9" s="235"/>
+      <c r="C9" s="235"/>
+      <c r="D9" s="235"/>
+      <c r="E9" s="235"/>
+      <c r="F9" s="235"/>
+      <c r="G9" s="235"/>
+      <c r="H9" s="235"/>
+      <c r="I9" s="235"/>
+      <c r="J9" s="235"/>
+      <c r="K9" s="235"/>
+      <c r="L9" s="235"/>
+      <c r="M9" s="235"/>
+      <c r="N9" s="235"/>
+      <c r="O9" s="235"/>
+      <c r="P9" s="235"/>
+    </row>
+    <row r="10" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="236" t="s">
         <v>116</v>
       </c>
-      <c r="B10" s="240"/>
-      <c r="C10" s="240"/>
-      <c r="D10" s="240"/>
-      <c r="E10" s="240"/>
-      <c r="F10" s="240"/>
-      <c r="G10" s="240"/>
-      <c r="H10" s="240"/>
-      <c r="I10" s="240"/>
-      <c r="J10" s="240"/>
-      <c r="K10" s="240"/>
-      <c r="L10" s="240"/>
-      <c r="M10" s="240"/>
-      <c r="N10" s="240"/>
-      <c r="O10" s="240"/>
-      <c r="P10" s="240"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A11" s="215" t="s">
+      <c r="B10" s="236"/>
+      <c r="C10" s="236"/>
+      <c r="D10" s="236"/>
+      <c r="E10" s="236"/>
+      <c r="F10" s="236"/>
+      <c r="G10" s="236"/>
+      <c r="H10" s="236"/>
+      <c r="I10" s="236"/>
+      <c r="J10" s="236"/>
+      <c r="K10" s="236"/>
+      <c r="L10" s="236"/>
+      <c r="M10" s="236"/>
+      <c r="N10" s="236"/>
+      <c r="O10" s="236"/>
+      <c r="P10" s="236"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" s="217" t="s">
         <v>3</v>
       </c>
       <c r="B11" s="101"/>
-      <c r="C11" s="215" t="s">
+      <c r="C11" s="217" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="215" t="s">
+      <c r="D11" s="217" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="215" t="s">
+      <c r="E11" s="217" t="s">
         <v>7</v>
       </c>
-      <c r="F11" s="218" t="s">
+      <c r="F11" s="213" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="215" t="s">
+      <c r="G11" s="217" t="s">
         <v>5</v>
       </c>
-      <c r="H11" s="223" t="s">
+      <c r="H11" s="219" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="218" t="s">
+      <c r="I11" s="213" t="s">
         <v>22</v>
       </c>
-      <c r="J11" s="218" t="s">
+      <c r="J11" s="213" t="s">
         <v>91</v>
       </c>
-      <c r="K11" s="225" t="s">
+      <c r="K11" s="221" t="s">
         <v>92</v>
       </c>
-      <c r="L11" s="218" t="s">
+      <c r="L11" s="213" t="s">
         <v>78</v>
       </c>
-      <c r="M11" s="218" t="s">
+      <c r="M11" s="213" t="s">
         <v>123</v>
       </c>
       <c r="N11" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="O11" s="221" t="s">
+      <c r="O11" s="215" t="s">
         <v>12</v>
       </c>
-      <c r="P11" s="236" t="s">
+      <c r="P11" s="232" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="217"/>
+    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="218"/>
       <c r="B12" s="102"/>
-      <c r="C12" s="217"/>
-      <c r="D12" s="216"/>
-      <c r="E12" s="217"/>
-      <c r="F12" s="219"/>
-      <c r="G12" s="217"/>
-      <c r="H12" s="224"/>
-      <c r="I12" s="219"/>
-      <c r="J12" s="219"/>
-      <c r="K12" s="226"/>
-      <c r="L12" s="219"/>
-      <c r="M12" s="219"/>
+      <c r="C12" s="218"/>
+      <c r="D12" s="237"/>
+      <c r="E12" s="218"/>
+      <c r="F12" s="214"/>
+      <c r="G12" s="218"/>
+      <c r="H12" s="220"/>
+      <c r="I12" s="214"/>
+      <c r="J12" s="214"/>
+      <c r="K12" s="222"/>
+      <c r="L12" s="214"/>
+      <c r="M12" s="214"/>
       <c r="N12" s="37" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 16/10</v>
       </c>
-      <c r="O12" s="222"/>
-      <c r="P12" s="237"/>
-    </row>
-    <row r="13" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O12" s="216"/>
+      <c r="P12" s="233"/>
+    </row>
+    <row r="13" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="40">
         <v>1</v>
       </c>
@@ -3179,19 +3199,19 @@
         <v>12</v>
       </c>
       <c r="F13" s="49">
-        <v>364055.01</v>
-      </c>
-      <c r="G13" s="50">
-        <f>400461-G29-G30</f>
-        <v>364054.65</v>
+        <v>360000.01</v>
+      </c>
+      <c r="G13" s="246">
+        <f>396280-G29-G31</f>
+        <v>359999.64</v>
       </c>
       <c r="H13" s="51">
         <f t="shared" ref="H13:H35" si="0">F13-G13</f>
-        <v>0.35999999998603016</v>
+        <v>0.36999999999534339</v>
       </c>
       <c r="I13" s="51">
         <f>IF(H13&gt;0,H13*3%,0)</f>
-        <v>1.0799999999580905E-2</v>
+        <v>1.1099999999860301E-2</v>
       </c>
       <c r="J13" s="97">
         <f t="shared" ref="J13:J35" si="1">K$2*E13/100</f>
@@ -3201,12 +3221,12 @@
         <f t="shared" ref="K13:K35" si="2">G$2*E13/100</f>
         <v>0</v>
       </c>
-      <c r="L13" s="134">
+      <c r="L13" s="133">
         <f>EDESUR!O4</f>
         <v>0</v>
       </c>
-      <c r="M13" s="148"/>
-      <c r="N13" s="133">
+      <c r="M13" s="147"/>
+      <c r="N13" s="132">
         <f>ROUND(SUM(H13:M13),0) + Q13</f>
         <v>360000.01</v>
       </c>
@@ -3222,68 +3242,68 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="126">
+    <row r="14" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="125">
         <v>2</v>
       </c>
-      <c r="B14" s="126" t="s">
+      <c r="B14" s="125" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="126" t="s">
+      <c r="C14" s="125" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="127"/>
-      <c r="E14" s="128">
+      <c r="D14" s="126"/>
+      <c r="E14" s="127">
         <v>6.6</v>
       </c>
       <c r="F14" s="50">
-        <v>326822.02</v>
-      </c>
-      <c r="G14" s="50">
-        <f>F14</f>
-        <v>326822.02</v>
-      </c>
-      <c r="H14" s="129">
+        <v>339673.02</v>
+      </c>
+      <c r="G14" s="246">
+        <f>200000+140000</f>
+        <v>340000</v>
+      </c>
+      <c r="H14" s="128">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I14" s="129">
+        <v>-326.97999999998137</v>
+      </c>
+      <c r="I14" s="128">
         <f t="shared" ref="I14:I35" si="3">IF(H14&gt;0,H14*3%,0)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="130">
+      <c r="J14" s="129">
         <f t="shared" si="1"/>
         <v>198000</v>
       </c>
-      <c r="K14" s="130">
+      <c r="K14" s="129">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L14" s="134">
+      <c r="L14" s="133">
         <f>EDESUR!O5</f>
-        <v>131673.44765485809</v>
-      </c>
-      <c r="M14" s="149">
-        <v>10000</v>
-      </c>
-      <c r="N14" s="133">
+        <v>125263.16548665638</v>
+      </c>
+      <c r="M14" s="148">
+        <v>0</v>
+      </c>
+      <c r="N14" s="132">
         <f t="shared" ref="N14:N35" si="4">ROUND(SUM(H14:M14),0) + Q14</f>
-        <v>339673.02</v>
-      </c>
-      <c r="O14" s="131">
+        <v>322936.02</v>
+      </c>
+      <c r="O14" s="130">
         <f t="shared" ref="O14:O30" si="5">ROUND(N14*6% + N14,0) + Q14</f>
-        <v>360053.02</v>
-      </c>
-      <c r="P14" s="132">
+        <v>342312.02</v>
+      </c>
+      <c r="P14" s="131">
         <f t="shared" ref="P14:P35" si="6">ROUND(N14*3%,0) + N14</f>
-        <v>349863.02</v>
+        <v>332624.02</v>
       </c>
       <c r="Q14" s="27">
         <f>Q13+0.01</f>
         <v>0.02</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="40">
         <v>3</v>
       </c>
@@ -3300,11 +3320,11 @@
         <v>5.4</v>
       </c>
       <c r="F15" s="49">
-        <v>159057.03</v>
-      </c>
-      <c r="G15" s="50">
+        <v>162000.03</v>
+      </c>
+      <c r="G15" s="246">
         <f>F15</f>
-        <v>159057.03</v>
+        <v>162000.03</v>
       </c>
       <c r="H15" s="51">
         <f t="shared" si="0"/>
@@ -3322,12 +3342,12 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L15" s="134">
+      <c r="L15" s="133">
         <f>EDESUR!O6</f>
         <v>0</v>
       </c>
-      <c r="M15" s="147"/>
-      <c r="N15" s="133">
+      <c r="M15" s="146"/>
+      <c r="N15" s="132">
         <f t="shared" si="4"/>
         <v>162000.03</v>
       </c>
@@ -3344,7 +3364,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="40">
         <v>4</v>
       </c>
@@ -3361,19 +3381,19 @@
         <v>6.6</v>
       </c>
       <c r="F16" s="49">
-        <v>194400.04</v>
-      </c>
-      <c r="G16" s="50">
-        <f>218435-G32</f>
-        <v>200761.8</v>
+        <v>191638.04</v>
+      </c>
+      <c r="G16" s="246">
+        <f>209778-G32</f>
+        <v>191637.8</v>
       </c>
       <c r="H16" s="51">
         <f t="shared" si="0"/>
-        <v>-6361.7599999999802</v>
+        <v>0.2400000000197906</v>
       </c>
       <c r="I16" s="51">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.2000000005937176E-3</v>
       </c>
       <c r="J16" s="97">
         <f t="shared" si="1"/>
@@ -3383,83 +3403,83 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L16" s="134">
-        <f>EDESUR!O8</f>
-        <v>0</v>
-      </c>
-      <c r="M16" s="148"/>
-      <c r="N16" s="133">
+      <c r="L16" s="133">
+        <f>EDESUR!O7</f>
+        <v>0</v>
+      </c>
+      <c r="M16" s="147"/>
+      <c r="N16" s="132">
         <f t="shared" si="4"/>
-        <v>191638.04</v>
+        <v>198000.04</v>
       </c>
       <c r="O16" s="52">
         <f t="shared" si="5"/>
-        <v>203136.04</v>
+        <v>209880.04</v>
       </c>
       <c r="P16" s="53">
         <f t="shared" si="6"/>
-        <v>197387.04</v>
+        <v>203940.04</v>
       </c>
       <c r="Q16" s="27">
         <f t="shared" si="7"/>
         <v>0.04</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="126">
+    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="125">
         <v>5</v>
       </c>
-      <c r="B17" s="126" t="s">
+      <c r="B17" s="125" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="126" t="s">
+      <c r="C17" s="125" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="126" t="s">
+      <c r="D17" s="125" t="s">
         <v>90</v>
       </c>
-      <c r="E17" s="128">
+      <c r="E17" s="127">
         <v>6.6</v>
       </c>
       <c r="F17" s="50">
-        <v>194403.05</v>
-      </c>
-      <c r="G17" s="50">
+        <v>198000.05</v>
+      </c>
+      <c r="G17" s="246">
         <f>F17</f>
-        <v>194403.05</v>
-      </c>
-      <c r="H17" s="129">
+        <v>198000.05</v>
+      </c>
+      <c r="H17" s="128">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I17" s="129">
+      <c r="I17" s="128">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J17" s="130">
+      <c r="J17" s="129">
         <f t="shared" si="1"/>
         <v>198000</v>
       </c>
-      <c r="K17" s="130">
+      <c r="K17" s="129">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L17" s="134">
-        <f>EDESUR!O9</f>
-        <v>0</v>
-      </c>
-      <c r="M17" s="149">
-        <v>0</v>
-      </c>
-      <c r="N17" s="133">
+      <c r="L17" s="133">
+        <f>EDESUR!O8</f>
+        <v>0</v>
+      </c>
+      <c r="M17" s="148">
+        <v>0</v>
+      </c>
+      <c r="N17" s="132">
         <f t="shared" si="4"/>
         <v>198000.05</v>
       </c>
-      <c r="O17" s="131">
+      <c r="O17" s="130">
         <f t="shared" si="5"/>
         <v>209880.05</v>
       </c>
-      <c r="P17" s="132">
+      <c r="P17" s="131">
         <f t="shared" si="6"/>
         <v>203940.05</v>
       </c>
@@ -3471,7 +3491,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="40">
         <v>6</v>
       </c>
@@ -3488,11 +3508,11 @@
         <v>5.4</v>
       </c>
       <c r="F18" s="49">
-        <v>187201.06</v>
-      </c>
-      <c r="G18" s="50">
+        <v>162000.06</v>
+      </c>
+      <c r="G18" s="246">
         <f>F18</f>
-        <v>187201.06</v>
+        <v>162000.06</v>
       </c>
       <c r="H18" s="51">
         <f t="shared" si="0"/>
@@ -3510,12 +3530,12 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L18" s="134">
-        <f>EDESUR!O10</f>
-        <v>0</v>
-      </c>
-      <c r="M18" s="148"/>
-      <c r="N18" s="133">
+      <c r="L18" s="133">
+        <f>EDESUR!O9</f>
+        <v>0</v>
+      </c>
+      <c r="M18" s="147"/>
+      <c r="N18" s="132">
         <f t="shared" si="4"/>
         <v>162000.06</v>
       </c>
@@ -3532,59 +3552,59 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="126">
+    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="125">
         <v>7</v>
       </c>
-      <c r="B19" s="126" t="s">
+      <c r="B19" s="125" t="s">
         <v>38</v>
       </c>
-      <c r="C19" s="126" t="s">
+      <c r="C19" s="125" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="126" t="s">
+      <c r="D19" s="125" t="s">
         <v>88</v>
       </c>
-      <c r="E19" s="128">
+      <c r="E19" s="127">
         <v>5.4</v>
       </c>
       <c r="F19" s="50">
-        <v>159057.07</v>
-      </c>
-      <c r="G19" s="50">
+        <v>166860.07</v>
+      </c>
+      <c r="G19" s="246">
         <f>F19</f>
-        <v>159057.07</v>
-      </c>
-      <c r="H19" s="129">
+        <v>166860.07</v>
+      </c>
+      <c r="H19" s="128">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I19" s="129">
+      <c r="I19" s="128">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J19" s="130">
+      <c r="J19" s="129">
         <f t="shared" si="1"/>
         <v>162000.00000000003</v>
       </c>
-      <c r="K19" s="130">
+      <c r="K19" s="129">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L19" s="134">
-        <f>EDESUR!O7</f>
-        <v>0</v>
-      </c>
-      <c r="M19" s="148"/>
-      <c r="N19" s="133">
+      <c r="L19" s="133">
+        <f>EDESUR!O10</f>
+        <v>0</v>
+      </c>
+      <c r="M19" s="147"/>
+      <c r="N19" s="132">
         <f t="shared" si="4"/>
         <v>162000.07</v>
       </c>
-      <c r="O19" s="131">
+      <c r="O19" s="130">
         <f t="shared" si="5"/>
         <v>171720.07</v>
       </c>
-      <c r="P19" s="132">
+      <c r="P19" s="131">
         <f t="shared" si="6"/>
         <v>166860.07</v>
       </c>
@@ -3593,90 +3613,89 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="126">
+    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="125">
         <v>8</v>
       </c>
-      <c r="B20" s="126" t="s">
+      <c r="B20" s="125" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="126" t="s">
+      <c r="C20" s="125" t="s">
         <v>41</v>
       </c>
-      <c r="D20" s="127" t="s">
+      <c r="D20" s="126" t="s">
         <v>69</v>
       </c>
-      <c r="E20" s="128">
+      <c r="E20" s="127">
         <v>6.6</v>
       </c>
       <c r="F20" s="50">
-        <v>258648.08</v>
-      </c>
-      <c r="G20" s="50">
+        <v>275013.08</v>
+      </c>
+      <c r="G20" s="246">
         <f>F20</f>
-        <v>258648.08</v>
-      </c>
-      <c r="H20" s="129">
+        <v>275013.08</v>
+      </c>
+      <c r="H20" s="128">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I20" s="129">
+      <c r="I20" s="128">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J20" s="130">
+      <c r="J20" s="129">
         <f t="shared" si="1"/>
         <v>198000</v>
       </c>
-      <c r="K20" s="130">
+      <c r="K20" s="129">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L20" s="134">
+      <c r="L20" s="133">
         <f>EDESUR!O12</f>
-        <v>77012.898489841638</v>
-      </c>
-      <c r="M20" s="148"/>
-      <c r="N20" s="133">
+        <v>98658.340164570633</v>
+      </c>
+      <c r="M20" s="147"/>
+      <c r="N20" s="132">
         <f t="shared" si="4"/>
-        <v>275013.08</v>
-      </c>
-      <c r="O20" s="131">
+        <v>296658.08</v>
+      </c>
+      <c r="O20" s="130">
         <f t="shared" si="5"/>
-        <v>291514.08</v>
-      </c>
-      <c r="P20" s="132">
+        <v>314458.08</v>
+      </c>
+      <c r="P20" s="131">
         <f t="shared" si="6"/>
-        <v>283263.08</v>
+        <v>305558.08</v>
       </c>
       <c r="Q20" s="27">
         <f t="shared" si="7"/>
         <v>0.08</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="126">
+    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="125">
         <v>9</v>
       </c>
-      <c r="B21" s="126" t="s">
+      <c r="B21" s="125" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="126" t="s">
+      <c r="C21" s="125" t="s">
         <v>43</v>
       </c>
-      <c r="D21" s="127" t="s">
+      <c r="D21" s="126" t="s">
         <v>72</v>
       </c>
       <c r="E21" s="48">
         <v>6.6</v>
       </c>
       <c r="F21" s="49">
-        <f>50000+182216.09</f>
-        <v>232216.09</v>
-      </c>
-      <c r="G21" s="50">
+        <v>198000.09</v>
+      </c>
+      <c r="G21" s="246">
         <f>F21</f>
-        <v>232216.09</v>
+        <v>198000.09</v>
       </c>
       <c r="H21" s="51">
         <f t="shared" si="0"/>
@@ -3694,56 +3713,55 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L21" s="134">
-        <f>EDESUR!O13</f>
-        <v>0</v>
-      </c>
-      <c r="M21" s="148">
-        <v>0</v>
-      </c>
-      <c r="N21" s="133">
+      <c r="L21" s="133">
+        <v>0</v>
+      </c>
+      <c r="M21" s="147">
+        <v>50000</v>
+      </c>
+      <c r="N21" s="132">
         <f t="shared" si="4"/>
-        <v>198000.09</v>
+        <v>248000.09</v>
       </c>
       <c r="O21" s="52">
         <f t="shared" si="5"/>
-        <v>209880.09</v>
+        <v>262880.09000000003</v>
       </c>
       <c r="P21" s="53">
         <f t="shared" si="6"/>
-        <v>203940.09</v>
+        <v>255440.09</v>
       </c>
       <c r="Q21" s="27">
         <f t="shared" si="7"/>
         <v>0.09</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="126">
+    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="125">
         <v>10</v>
       </c>
-      <c r="B22" s="126" t="s">
+      <c r="B22" s="125" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="126" t="s">
+      <c r="C22" s="125" t="s">
         <v>45</v>
       </c>
-      <c r="D22" s="127" t="s">
+      <c r="D22" s="126" t="s">
         <v>70</v>
       </c>
       <c r="E22" s="48">
         <v>5.4</v>
       </c>
       <c r="F22" s="49">
-        <v>13257.1</v>
-      </c>
-      <c r="G22" s="50">
-        <f>F22+RESUMEN!D39</f>
-        <v>171245.39</v>
+        <v>4012.1</v>
+      </c>
+      <c r="G22" s="246">
+        <f>F22</f>
+        <v>4012.1</v>
       </c>
       <c r="H22" s="51">
         <f>F22-G22</f>
-        <v>-157988.29</v>
+        <v>0</v>
       </c>
       <c r="I22" s="51">
         <f t="shared" si="3"/>
@@ -3757,29 +3775,29 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L22" s="134">
-        <f>EDESUR!O14</f>
-        <v>0</v>
-      </c>
-      <c r="M22" s="148"/>
-      <c r="N22" s="133">
+      <c r="L22" s="133">
+        <f>EDESUR!O13</f>
+        <v>0</v>
+      </c>
+      <c r="M22" s="147"/>
+      <c r="N22" s="132">
         <f t="shared" si="4"/>
-        <v>4012.1</v>
+        <v>162000.1</v>
       </c>
       <c r="O22" s="52">
         <f t="shared" si="5"/>
-        <v>4253.1000000000004</v>
+        <v>171720.1</v>
       </c>
       <c r="P22" s="53">
         <f t="shared" si="6"/>
-        <v>4132.1000000000004</v>
+        <v>166860.1</v>
       </c>
       <c r="Q22" s="27">
         <f t="shared" si="7"/>
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="40">
         <v>11</v>
       </c>
@@ -3794,11 +3812,11 @@
         <v>5.4</v>
       </c>
       <c r="F23" s="49">
-        <v>159057.10999999999</v>
-      </c>
-      <c r="G23" s="50">
-        <f>167894.33-G34</f>
-        <v>159057.10999999999</v>
+        <v>162000.10999999999</v>
+      </c>
+      <c r="G23" s="246">
+        <f>171070.33-G34</f>
+        <v>162000.10999999999</v>
       </c>
       <c r="H23" s="51">
         <f t="shared" si="0"/>
@@ -3816,12 +3834,12 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L23" s="134">
-        <f>EDESUR!O11</f>
-        <v>0</v>
-      </c>
-      <c r="M23" s="148"/>
-      <c r="N23" s="133">
+      <c r="L23" s="133">
+        <f>EDESUR!O14</f>
+        <v>0</v>
+      </c>
+      <c r="M23" s="147"/>
+      <c r="N23" s="132">
         <f t="shared" si="4"/>
         <v>162000.10999999999</v>
       </c>
@@ -3841,7 +3859,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="40">
         <v>12</v>
       </c>
@@ -3858,11 +3876,11 @@
         <v>6.6</v>
       </c>
       <c r="F24" s="49">
-        <v>194403.12</v>
-      </c>
-      <c r="G24" s="50">
+        <v>198000.12</v>
+      </c>
+      <c r="G24" s="246">
         <f>F24</f>
-        <v>194403.12</v>
+        <v>198000.12</v>
       </c>
       <c r="H24" s="51">
         <f t="shared" si="0"/>
@@ -3880,12 +3898,12 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L24" s="134">
-        <f>EDESUR!O16</f>
-        <v>0</v>
-      </c>
-      <c r="M24" s="148"/>
-      <c r="N24" s="133">
+      <c r="L24" s="133">
+        <f>EDESUR!O15</f>
+        <v>0</v>
+      </c>
+      <c r="M24" s="147"/>
+      <c r="N24" s="132">
         <f t="shared" si="4"/>
         <v>198000.12</v>
       </c>
@@ -3902,7 +3920,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="40">
         <v>13</v>
       </c>
@@ -3919,14 +3937,14 @@
         <v>6.6</v>
       </c>
       <c r="F25" s="49">
-        <v>194403.13</v>
-      </c>
-      <c r="G25" s="50">
-        <v>200235.13</v>
+        <v>192168.13</v>
+      </c>
+      <c r="G25" s="246">
+        <v>197933.13</v>
       </c>
       <c r="H25" s="51">
         <f t="shared" si="0"/>
-        <v>-5832</v>
+        <v>-5765</v>
       </c>
       <c r="I25" s="51">
         <f t="shared" si="3"/>
@@ -3940,79 +3958,79 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L25" s="134">
-        <f>EDESUR!O17</f>
-        <v>0</v>
-      </c>
-      <c r="M25" s="148"/>
-      <c r="N25" s="133">
+      <c r="L25" s="133">
+        <f>EDESUR!O16</f>
+        <v>0</v>
+      </c>
+      <c r="M25" s="147"/>
+      <c r="N25" s="132">
         <f t="shared" si="4"/>
-        <v>192168.13</v>
+        <v>192235.13</v>
       </c>
       <c r="O25" s="52">
         <f t="shared" si="5"/>
-        <v>203698.13</v>
+        <v>203769.13</v>
       </c>
       <c r="P25" s="53">
         <f t="shared" si="6"/>
-        <v>197933.13</v>
+        <v>198002.13</v>
       </c>
       <c r="Q25" s="27">
         <f t="shared" si="7"/>
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="126">
+    <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="125">
         <v>14</v>
       </c>
-      <c r="B26" s="126" t="s">
+      <c r="B26" s="125" t="s">
         <v>52</v>
       </c>
-      <c r="C26" s="126" t="s">
+      <c r="C26" s="125" t="s">
         <v>53</v>
       </c>
-      <c r="D26" s="127"/>
-      <c r="E26" s="128">
+      <c r="D26" s="126"/>
+      <c r="E26" s="127">
         <v>5.4</v>
       </c>
       <c r="F26" s="50">
-        <v>159057.14000000001</v>
-      </c>
-      <c r="G26" s="50">
+        <v>162000.14000000001</v>
+      </c>
+      <c r="G26" s="246">
         <f t="shared" ref="G26:G33" si="8">F26</f>
-        <v>159057.14000000001</v>
-      </c>
-      <c r="H26" s="129">
+        <v>162000.14000000001</v>
+      </c>
+      <c r="H26" s="128">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I26" s="129">
+      <c r="I26" s="128">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J26" s="130">
+      <c r="J26" s="129">
         <f t="shared" si="1"/>
         <v>162000.00000000003</v>
       </c>
-      <c r="K26" s="130">
+      <c r="K26" s="129">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L26" s="134">
-        <f>EDESUR!O18</f>
-        <v>0</v>
-      </c>
-      <c r="M26" s="149"/>
-      <c r="N26" s="133">
+      <c r="L26" s="133">
+        <f>EDESUR!O17</f>
+        <v>0</v>
+      </c>
+      <c r="M26" s="148"/>
+      <c r="N26" s="132">
         <f t="shared" si="4"/>
         <v>162000.14000000001</v>
       </c>
-      <c r="O26" s="131">
+      <c r="O26" s="130">
         <f t="shared" si="5"/>
         <v>171720.14</v>
       </c>
-      <c r="P26" s="132">
+      <c r="P26" s="131">
         <f t="shared" si="6"/>
         <v>166860.14000000001</v>
       </c>
@@ -4021,7 +4039,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="40">
         <v>15</v>
       </c>
@@ -4036,11 +4054,11 @@
         <v>5.4</v>
       </c>
       <c r="F27" s="49">
-        <v>159057.15</v>
-      </c>
-      <c r="G27" s="50">
+        <v>162000.15</v>
+      </c>
+      <c r="G27" s="246">
         <f t="shared" si="8"/>
-        <v>159057.15</v>
+        <v>162000.15</v>
       </c>
       <c r="H27" s="51">
         <f t="shared" si="0"/>
@@ -4058,12 +4076,12 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L27" s="134">
-        <f>EDESUR!O15</f>
-        <v>0</v>
-      </c>
-      <c r="M27" s="148"/>
-      <c r="N27" s="133">
+      <c r="L27" s="133">
+        <f>EDESUR!O18</f>
+        <v>0</v>
+      </c>
+      <c r="M27" s="147"/>
+      <c r="N27" s="132">
         <f t="shared" si="4"/>
         <v>162000.15</v>
       </c>
@@ -4080,14 +4098,14 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="126">
+    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="125">
         <v>16</v>
       </c>
-      <c r="B28" s="126" t="s">
+      <c r="B28" s="125" t="s">
         <v>56</v>
       </c>
-      <c r="C28" s="126" t="s">
+      <c r="C28" s="125" t="s">
         <v>37</v>
       </c>
       <c r="D28" s="40" t="s">
@@ -4097,11 +4115,11 @@
         <v>0.7</v>
       </c>
       <c r="F28" s="49">
-        <v>24542.16</v>
-      </c>
-      <c r="G28" s="50">
-        <f t="shared" si="8"/>
-        <v>24542.16</v>
+        <v>21163.16</v>
+      </c>
+      <c r="G28" s="246">
+        <f>F28</f>
+        <v>21163.16</v>
       </c>
       <c r="H28" s="51">
         <f t="shared" si="0"/>
@@ -4119,36 +4137,36 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L28" s="134">
-        <f>EDESUR!O22</f>
-        <v>163.15059560726027</v>
-      </c>
-      <c r="M28" s="148"/>
-      <c r="N28" s="133">
+      <c r="L28" s="133">
+        <f>EDESUR!O19</f>
+        <v>0</v>
+      </c>
+      <c r="M28" s="147"/>
+      <c r="N28" s="132">
         <f t="shared" si="4"/>
-        <v>21163.16</v>
+        <v>21000.16</v>
       </c>
       <c r="O28" s="52">
         <f t="shared" si="5"/>
-        <v>22433.16</v>
+        <v>22260.16</v>
       </c>
       <c r="P28" s="53">
         <f t="shared" si="6"/>
-        <v>21798.16</v>
+        <v>21630.16</v>
       </c>
       <c r="Q28" s="27">
         <f t="shared" si="7"/>
         <v>0.16</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="126">
+    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="125">
         <v>17</v>
       </c>
-      <c r="B29" s="126" t="s">
+      <c r="B29" s="125" t="s">
         <v>57</v>
       </c>
-      <c r="C29" s="126" t="s">
+      <c r="C29" s="125" t="s">
         <v>27</v>
       </c>
       <c r="D29" s="41"/>
@@ -4156,11 +4174,11 @@
         <v>0.6</v>
       </c>
       <c r="F29" s="50">
-        <v>18203.169999999998</v>
-      </c>
-      <c r="G29" s="50">
+        <v>18140.169999999998</v>
+      </c>
+      <c r="G29" s="246">
         <f t="shared" si="8"/>
-        <v>18203.169999999998</v>
+        <v>18140.169999999998</v>
       </c>
       <c r="H29" s="51">
         <f t="shared" si="0"/>
@@ -4178,29 +4196,28 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L29" s="134">
-        <f>EDESUR!O23</f>
-        <v>139.84336766336594</v>
-      </c>
-      <c r="M29" s="148"/>
-      <c r="N29" s="133">
+      <c r="L29" s="133">
+        <v>0</v>
+      </c>
+      <c r="M29" s="147"/>
+      <c r="N29" s="132">
         <f t="shared" si="4"/>
-        <v>18140.169999999998</v>
+        <v>18000.169999999998</v>
       </c>
       <c r="O29" s="52">
         <f t="shared" si="5"/>
-        <v>19229.169999999998</v>
+        <v>19080.169999999998</v>
       </c>
       <c r="P29" s="53">
         <f t="shared" si="6"/>
-        <v>18684.169999999998</v>
+        <v>18540.169999999998</v>
       </c>
       <c r="Q29" s="27">
         <f t="shared" si="7"/>
         <v>0.17</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="40">
         <v>18</v>
       </c>
@@ -4215,11 +4232,11 @@
         <v>0.6</v>
       </c>
       <c r="F30" s="49">
-        <v>18203.18</v>
-      </c>
-      <c r="G30" s="50">
-        <f t="shared" si="8"/>
-        <v>18203.18</v>
+        <v>18140.18</v>
+      </c>
+      <c r="G30" s="246">
+        <f>F30</f>
+        <v>18140.18</v>
       </c>
       <c r="H30" s="51">
         <f t="shared" si="0"/>
@@ -4237,85 +4254,85 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L30" s="134">
-        <f>EDESUR!O24</f>
-        <v>139.84336766336594</v>
-      </c>
-      <c r="M30" s="148"/>
-      <c r="N30" s="133">
+      <c r="L30" s="133">
+        <f>EDESUR!O21</f>
+        <v>0</v>
+      </c>
+      <c r="M30" s="147"/>
+      <c r="N30" s="132">
         <f t="shared" si="4"/>
-        <v>18140.18</v>
+        <v>18000.18</v>
       </c>
       <c r="O30" s="52">
         <f t="shared" si="5"/>
-        <v>19229.18</v>
+        <v>19080.18</v>
       </c>
       <c r="P30" s="53">
         <f t="shared" si="6"/>
-        <v>18684.18</v>
+        <v>18540.18</v>
       </c>
       <c r="Q30" s="27">
         <f t="shared" si="7"/>
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A31" s="126">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A31" s="125">
         <v>19</v>
       </c>
-      <c r="B31" s="126" t="s">
+      <c r="B31" s="125" t="s">
         <v>59</v>
       </c>
-      <c r="C31" s="126" t="s">
+      <c r="C31" s="125" t="s">
         <v>49</v>
       </c>
-      <c r="D31" s="127"/>
-      <c r="E31" s="128">
+      <c r="D31" s="126"/>
+      <c r="E31" s="127">
         <v>0.6</v>
       </c>
       <c r="F31" s="50">
-        <v>17673.189999999999</v>
-      </c>
-      <c r="G31" s="50">
+        <v>18140.189999999999</v>
+      </c>
+      <c r="G31" s="246">
         <f t="shared" si="8"/>
-        <v>17673.189999999999</v>
-      </c>
-      <c r="H31" s="129">
+        <v>18140.189999999999</v>
+      </c>
+      <c r="H31" s="128">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I31" s="129">
+      <c r="I31" s="128">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J31" s="130">
+      <c r="J31" s="129">
         <f t="shared" si="1"/>
         <v>18000</v>
       </c>
-      <c r="K31" s="130">
+      <c r="K31" s="129">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L31" s="134">
-        <f>EDESUR!O25</f>
-        <v>139.84336766336594</v>
-      </c>
-      <c r="M31" s="149"/>
-      <c r="N31" s="133">
+      <c r="L31" s="133">
+        <f>EDESUR!O22</f>
+        <v>0</v>
+      </c>
+      <c r="M31" s="148"/>
+      <c r="N31" s="132">
         <f t="shared" si="4"/>
-        <v>18140.189999999999</v>
-      </c>
-      <c r="O31" s="131"/>
-      <c r="P31" s="132">
+        <v>18000.189999999999</v>
+      </c>
+      <c r="O31" s="130"/>
+      <c r="P31" s="131">
         <f t="shared" si="6"/>
-        <v>18684.189999999999</v>
+        <v>18540.189999999999</v>
       </c>
       <c r="Q31" s="27">
         <f>Q30+0.01</f>
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="21.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A32" s="54">
         <v>20</v>
       </c>
@@ -4332,11 +4349,11 @@
         <v>0.6</v>
       </c>
       <c r="F32" s="56">
-        <v>17673.2</v>
-      </c>
-      <c r="G32" s="50">
+        <v>18140.2</v>
+      </c>
+      <c r="G32" s="246">
         <f t="shared" si="8"/>
-        <v>17673.2</v>
+        <v>18140.2</v>
       </c>
       <c r="H32" s="51">
         <f t="shared" si="0"/>
@@ -4354,26 +4371,26 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L32" s="134">
-        <f>EDESUR!O26</f>
-        <v>139.84336766336594</v>
-      </c>
-      <c r="M32" s="148"/>
-      <c r="N32" s="133">
+      <c r="L32" s="133">
+        <f>EDESUR!O23</f>
+        <v>0</v>
+      </c>
+      <c r="M32" s="147"/>
+      <c r="N32" s="132">
         <f t="shared" si="4"/>
-        <v>18140.2</v>
+        <v>18000.2</v>
       </c>
       <c r="O32" s="52"/>
       <c r="P32" s="53">
         <f t="shared" si="6"/>
-        <v>18684.2</v>
+        <v>18540.2</v>
       </c>
       <c r="Q32" s="27">
         <f t="shared" ref="Q32:Q35" si="9">Q31+0.01</f>
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="54">
         <v>21</v>
       </c>
@@ -4390,11 +4407,11 @@
         <v>0.3</v>
       </c>
       <c r="F33" s="56">
-        <v>8837.2099999999991</v>
-      </c>
-      <c r="G33" s="50">
-        <f t="shared" si="8"/>
-        <v>8837.2099999999991</v>
+        <v>9070.2099999999991</v>
+      </c>
+      <c r="G33" s="246">
+        <f>F33</f>
+        <v>9070.2099999999991</v>
       </c>
       <c r="H33" s="51">
         <f t="shared" si="0"/>
@@ -4412,26 +4429,26 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L33" s="134">
-        <f>EDESUR!O27</f>
-        <v>69.921683831682969</v>
-      </c>
-      <c r="M33" s="148"/>
-      <c r="N33" s="133">
+      <c r="L33" s="133">
+        <f>EDESUR!O24</f>
+        <v>0</v>
+      </c>
+      <c r="M33" s="147"/>
+      <c r="N33" s="132">
         <f t="shared" si="4"/>
-        <v>9070.2099999999991</v>
+        <v>9000.2099999999991</v>
       </c>
       <c r="O33" s="52"/>
       <c r="P33" s="53">
         <f t="shared" si="6"/>
-        <v>9342.2099999999991</v>
+        <v>9270.2099999999991</v>
       </c>
       <c r="Q33" s="27">
         <f t="shared" si="9"/>
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="55">
         <v>22</v>
       </c>
@@ -4446,11 +4463,11 @@
         <v>0.3</v>
       </c>
       <c r="F34" s="56">
-        <v>8837.2199999999993</v>
-      </c>
-      <c r="G34" s="179">
+        <v>9070.2199999999993</v>
+      </c>
+      <c r="G34" s="247">
         <f t="shared" ref="G34" si="10">F34</f>
-        <v>8837.2199999999993</v>
+        <v>9070.2199999999993</v>
       </c>
       <c r="H34" s="51">
         <f t="shared" si="0"/>
@@ -4468,26 +4485,26 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L34" s="134">
-        <f>EDESUR!O28</f>
-        <v>69.921683831682969</v>
-      </c>
-      <c r="M34" s="148"/>
-      <c r="N34" s="133">
+      <c r="L34" s="133">
+        <f>EDESUR!O25</f>
+        <v>0</v>
+      </c>
+      <c r="M34" s="147"/>
+      <c r="N34" s="132">
         <f t="shared" si="4"/>
-        <v>9070.2199999999993</v>
+        <v>9000.2199999999993</v>
       </c>
       <c r="O34" s="52"/>
       <c r="P34" s="53">
         <f t="shared" si="6"/>
-        <v>9342.2199999999993</v>
+        <v>9270.2199999999993</v>
       </c>
       <c r="Q34" s="27">
         <f t="shared" si="9"/>
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="40">
         <v>23</v>
       </c>
@@ -4504,11 +4521,11 @@
         <v>0.3</v>
       </c>
       <c r="F35" s="56">
-        <v>8837.23</v>
-      </c>
-      <c r="G35" s="50">
+        <v>9070.23</v>
+      </c>
+      <c r="G35" s="246">
         <f>F35</f>
-        <v>8837.23</v>
+        <v>9070.23</v>
       </c>
       <c r="H35" s="51">
         <f t="shared" si="0"/>
@@ -4526,26 +4543,26 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L35" s="134">
-        <f>EDESUR!O29</f>
-        <v>69.921683831682969</v>
-      </c>
-      <c r="M35" s="148"/>
-      <c r="N35" s="133">
+      <c r="L35" s="133">
+        <f>EDESUR!O26</f>
+        <v>0</v>
+      </c>
+      <c r="M35" s="147"/>
+      <c r="N35" s="132">
         <f t="shared" si="4"/>
-        <v>9070.23</v>
+        <v>9000.23</v>
       </c>
       <c r="O35" s="58"/>
       <c r="P35" s="53">
         <f t="shared" si="6"/>
-        <v>9342.23</v>
+        <v>9270.23</v>
       </c>
       <c r="Q35" s="27">
         <f t="shared" si="9"/>
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="59"/>
       <c r="B36" s="59"/>
       <c r="C36" s="60"/>
@@ -4556,19 +4573,19 @@
       </c>
       <c r="F36" s="34">
         <f>SUM(F13:F35)</f>
-        <v>3077900.7600000012</v>
+        <v>3054299.7600000012</v>
       </c>
       <c r="G36" s="38">
         <f>SUM(G13:G35)</f>
-        <v>3248082.4500000007</v>
+        <v>3060391.1300000008</v>
       </c>
       <c r="H36" s="38">
         <f>SUM(H13:H35)</f>
-        <v>-170181.69</v>
+        <v>-6091.3699999999662</v>
       </c>
       <c r="I36" s="38">
         <f t="shared" ref="I36:O36" si="11">SUM(I13:I35)</f>
-        <v>1.0799999999580905E-2</v>
+        <v>1.8300000000454019E-2</v>
       </c>
       <c r="J36" s="86">
         <f t="shared" si="11"/>
@@ -4580,116 +4597,122 @@
       </c>
       <c r="L36" s="61">
         <f>SUM(L13:L35)</f>
-        <v>209618.6352624555</v>
+        <v>223921.50565122702</v>
       </c>
       <c r="M36" s="61"/>
       <c r="N36" s="61">
         <f>SUM(N13:N35)</f>
-        <v>3049439.7600000012</v>
+        <v>3267831.7600000007</v>
       </c>
       <c r="O36" s="61">
         <f t="shared" si="11"/>
-        <v>3165106.7100000004</v>
+        <v>3397120.7100000004</v>
       </c>
       <c r="P36" s="61">
         <f>SUM(P13:P35)</f>
-        <v>3140920.7600000007</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>3365866.7600000007</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C37" s="33"/>
       <c r="D37" s="33"/>
     </row>
-    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="39" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C39" s="204" t="str">
+    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C39" s="209" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. PORFAVOR RESPETAR LOS CENTAVOS AL ABONAR.</v>
       </c>
-      <c r="D39" s="204"/>
-      <c r="E39" s="204"/>
-      <c r="F39" s="204"/>
-      <c r="G39" s="204"/>
-      <c r="H39" s="204"/>
-      <c r="I39" s="204"/>
-      <c r="J39" s="204"/>
-      <c r="K39" s="204"/>
-      <c r="L39" s="204"/>
-      <c r="M39" s="204"/>
-      <c r="N39" s="204"/>
-    </row>
-    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C40" s="204"/>
-      <c r="D40" s="204"/>
-      <c r="E40" s="204"/>
-      <c r="F40" s="204"/>
-      <c r="G40" s="204"/>
-      <c r="H40" s="204"/>
-      <c r="I40" s="204"/>
-      <c r="J40" s="204"/>
-      <c r="K40" s="204"/>
-      <c r="L40" s="204"/>
-      <c r="M40" s="204"/>
-      <c r="N40" s="204"/>
-    </row>
-    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="204"/>
-      <c r="D41" s="204"/>
-      <c r="E41" s="204"/>
-      <c r="F41" s="204"/>
-      <c r="G41" s="204"/>
-      <c r="H41" s="204"/>
-      <c r="I41" s="204"/>
-      <c r="J41" s="204"/>
-      <c r="K41" s="204"/>
-      <c r="L41" s="204"/>
-      <c r="M41" s="204"/>
-      <c r="N41" s="204"/>
-    </row>
-    <row r="42" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C42" s="204"/>
-      <c r="D42" s="204"/>
-      <c r="E42" s="204"/>
-      <c r="F42" s="204"/>
-      <c r="G42" s="204"/>
-      <c r="H42" s="204"/>
-      <c r="I42" s="204"/>
-      <c r="J42" s="204"/>
-      <c r="K42" s="204"/>
-      <c r="L42" s="204"/>
-      <c r="M42" s="204"/>
-      <c r="N42" s="204"/>
-    </row>
-    <row r="43" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C43" s="204"/>
-      <c r="D43" s="204"/>
-      <c r="E43" s="204"/>
-      <c r="F43" s="204"/>
-      <c r="G43" s="204"/>
-      <c r="H43" s="204"/>
-      <c r="I43" s="204"/>
-      <c r="J43" s="204"/>
-      <c r="K43" s="204"/>
-      <c r="L43" s="204"/>
-      <c r="M43" s="204"/>
-      <c r="N43" s="204"/>
-    </row>
-    <row r="44" spans="1:17" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C44" s="204"/>
-      <c r="D44" s="204"/>
-      <c r="E44" s="204"/>
-      <c r="F44" s="204"/>
-      <c r="G44" s="204"/>
-      <c r="H44" s="204"/>
-      <c r="I44" s="204"/>
-      <c r="J44" s="204"/>
-      <c r="K44" s="204"/>
-      <c r="L44" s="204"/>
-      <c r="M44" s="204"/>
-      <c r="N44" s="204"/>
+      <c r="D39" s="209"/>
+      <c r="E39" s="209"/>
+      <c r="F39" s="209"/>
+      <c r="G39" s="209"/>
+      <c r="H39" s="209"/>
+      <c r="I39" s="209"/>
+      <c r="J39" s="209"/>
+      <c r="K39" s="209"/>
+      <c r="L39" s="209"/>
+      <c r="M39" s="209"/>
+      <c r="N39" s="209"/>
+    </row>
+    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C40" s="209"/>
+      <c r="D40" s="209"/>
+      <c r="E40" s="209"/>
+      <c r="F40" s="209"/>
+      <c r="G40" s="209"/>
+      <c r="H40" s="209"/>
+      <c r="I40" s="209"/>
+      <c r="J40" s="209"/>
+      <c r="K40" s="209"/>
+      <c r="L40" s="209"/>
+      <c r="M40" s="209"/>
+      <c r="N40" s="209"/>
+    </row>
+    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C41" s="209"/>
+      <c r="D41" s="209"/>
+      <c r="E41" s="209"/>
+      <c r="F41" s="209"/>
+      <c r="G41" s="209"/>
+      <c r="H41" s="209"/>
+      <c r="I41" s="209"/>
+      <c r="J41" s="209"/>
+      <c r="K41" s="209"/>
+      <c r="L41" s="209"/>
+      <c r="M41" s="209"/>
+      <c r="N41" s="209"/>
+    </row>
+    <row r="42" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C42" s="209"/>
+      <c r="D42" s="209"/>
+      <c r="E42" s="209"/>
+      <c r="F42" s="209"/>
+      <c r="G42" s="209"/>
+      <c r="H42" s="209"/>
+      <c r="I42" s="209"/>
+      <c r="J42" s="209"/>
+      <c r="K42" s="209"/>
+      <c r="L42" s="209"/>
+      <c r="M42" s="209"/>
+      <c r="N42" s="209"/>
+    </row>
+    <row r="43" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C43" s="209"/>
+      <c r="D43" s="209"/>
+      <c r="E43" s="209"/>
+      <c r="F43" s="209"/>
+      <c r="G43" s="209"/>
+      <c r="H43" s="209"/>
+      <c r="I43" s="209"/>
+      <c r="J43" s="209"/>
+      <c r="K43" s="209"/>
+      <c r="L43" s="209"/>
+      <c r="M43" s="209"/>
+      <c r="N43" s="209"/>
+    </row>
+    <row r="44" spans="1:17" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C44" s="209"/>
+      <c r="D44" s="209"/>
+      <c r="E44" s="209"/>
+      <c r="F44" s="209"/>
+      <c r="G44" s="209"/>
+      <c r="H44" s="209"/>
+      <c r="I44" s="209"/>
+      <c r="J44" s="209"/>
+      <c r="K44" s="209"/>
+      <c r="L44" s="209"/>
+      <c r="M44" s="209"/>
+      <c r="N44" s="209"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="C39:N44"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="M11:M12"/>
     <mergeCell ref="E1:N1"/>
     <mergeCell ref="I11:I12"/>
     <mergeCell ref="F11:F12"/>
@@ -4703,12 +4726,6 @@
     <mergeCell ref="A9:P9"/>
     <mergeCell ref="A10:P10"/>
     <mergeCell ref="L11:L12"/>
-    <mergeCell ref="C39:N44"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="M11:M12"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" orientation="landscape" r:id="rId1"/>
@@ -4716,50 +4733,50 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFC03CC8-EEB1-4121-A90D-748455B927ED}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E11DE44-94AC-4627-8367-E065E39D764D}">
   <dimension ref="B2:O32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="8.44140625" customWidth="1"/>
-    <col min="3" max="3" width="7.88671875" customWidth="1"/>
-    <col min="4" max="4" width="12.5546875" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="15.33203125" customWidth="1"/>
-    <col min="7" max="7" width="1.6640625" customWidth="1"/>
-    <col min="8" max="8" width="10.44140625" customWidth="1"/>
-    <col min="9" max="9" width="14.33203125" customWidth="1"/>
-    <col min="10" max="10" width="1.6640625" customWidth="1"/>
-    <col min="11" max="11" width="19.5546875" style="109" customWidth="1"/>
-    <col min="12" max="12" width="2.109375" customWidth="1"/>
-    <col min="13" max="13" width="19.6640625" style="110" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" customWidth="1"/>
+    <col min="7" max="7" width="1.85546875" customWidth="1"/>
+    <col min="8" max="8" width="10.5703125" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" customWidth="1"/>
+    <col min="10" max="10" width="1.85546875" customWidth="1"/>
+    <col min="11" max="11" width="19.5703125" style="108" customWidth="1"/>
+    <col min="12" max="12" width="2.140625" customWidth="1"/>
+    <col min="13" max="13" width="19.7109375" style="109" customWidth="1"/>
     <col min="14" max="14" width="2" customWidth="1"/>
-    <col min="15" max="15" width="15.33203125" style="176" customWidth="1"/>
+    <col min="15" max="15" width="15.28515625" style="175" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="D2" s="241" t="s">
-        <v>142</v>
-      </c>
-      <c r="E2" s="241"/>
-      <c r="F2" s="241"/>
+    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="D2" s="238" t="s">
+        <v>135</v>
+      </c>
+      <c r="E2" s="238"/>
+      <c r="F2" s="238"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="242" t="s">
-        <v>143</v>
-      </c>
-      <c r="I2" s="243"/>
+      <c r="H2" s="239" t="s">
+        <v>136</v>
+      </c>
+      <c r="I2" s="240"/>
       <c r="J2" s="1"/>
-      <c r="K2" s="107" t="s">
-        <v>144</v>
-      </c>
-      <c r="M2" s="189" t="s">
-        <v>145</v>
-      </c>
-      <c r="O2" s="107" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="K2" s="198" t="s">
+        <v>137</v>
+      </c>
+      <c r="M2" s="185" t="s">
+        <v>138</v>
+      </c>
+      <c r="O2" s="198" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B3" s="106" t="s">
         <v>79</v>
       </c>
@@ -4772,596 +4789,596 @@
       <c r="E3" s="106" t="s">
         <v>127</v>
       </c>
-      <c r="F3" s="107" t="s">
+      <c r="F3" s="198" t="s">
         <v>128</v>
       </c>
       <c r="H3" s="106" t="s">
-        <v>147</v>
-      </c>
-      <c r="I3" s="171" t="s">
+        <v>140</v>
+      </c>
+      <c r="I3" s="170" t="s">
         <v>129</v>
       </c>
       <c r="K3" s="106"/>
-      <c r="M3" s="108"/>
-      <c r="O3" s="107"/>
-    </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B4" s="190">
+      <c r="M3" s="107"/>
+      <c r="O3" s="198"/>
+    </row>
+    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B4" s="186">
         <v>1</v>
       </c>
-      <c r="C4" s="190" t="s">
+      <c r="C4" s="186" t="s">
         <v>81</v>
       </c>
-      <c r="D4" s="191">
-        <v>0</v>
-      </c>
-      <c r="E4" s="192">
-        <v>0</v>
-      </c>
-      <c r="F4" s="193">
-        <v>0</v>
-      </c>
-      <c r="H4" s="172">
+      <c r="D4" s="187">
+        <v>0</v>
+      </c>
+      <c r="E4" s="188">
+        <v>0</v>
+      </c>
+      <c r="F4" s="189">
+        <v>0</v>
+      </c>
+      <c r="H4" s="171">
         <v>0.12</v>
       </c>
-      <c r="I4" s="194">
-        <v>2796.8673532673188</v>
-      </c>
-      <c r="K4" s="150">
+      <c r="I4" s="190">
+        <v>5711.4946104294486</v>
+      </c>
+      <c r="K4" s="149">
         <f>I4+F4</f>
-        <v>2796.8673532673188</v>
-      </c>
-      <c r="M4" s="195">
+        <v>5711.4946104294486</v>
+      </c>
+      <c r="M4" s="191">
         <f>K4</f>
-        <v>2796.8673532673188</v>
-      </c>
-      <c r="O4" s="150">
+        <v>5711.4946104294486</v>
+      </c>
+      <c r="O4" s="149">
         <f>K4-M4</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B5" s="106">
         <v>1</v>
       </c>
       <c r="C5" s="106" t="s">
         <v>82</v>
       </c>
-      <c r="D5" s="174">
-        <v>344.5</v>
-      </c>
-      <c r="E5" s="192">
-        <v>0.63292302039316528</v>
-      </c>
-      <c r="F5" s="193">
-        <v>130135.17061056105</v>
-      </c>
-      <c r="H5" s="173">
+      <c r="D5" s="173">
+        <v>300.19999999999982</v>
+      </c>
+      <c r="E5" s="188">
+        <v>0.56112149532710243</v>
+      </c>
+      <c r="F5" s="189">
+        <v>122121.84345092018</v>
+      </c>
+      <c r="H5" s="172">
         <v>6.6000000000000003E-2</v>
       </c>
-      <c r="I5" s="194">
-        <v>1538.2770442970254</v>
-      </c>
-      <c r="K5" s="150">
+      <c r="I5" s="190">
+        <v>3141.322035736197</v>
+      </c>
+      <c r="K5" s="149">
         <f t="shared" ref="K5:K18" si="0">I5+F5</f>
-        <v>131673.44765485809</v>
-      </c>
-      <c r="M5" s="195">
-        <v>0</v>
-      </c>
-      <c r="O5" s="150">
+        <v>125263.16548665638</v>
+      </c>
+      <c r="M5" s="191">
+        <v>0</v>
+      </c>
+      <c r="O5" s="149">
         <f t="shared" ref="O5:O18" si="1">K5-M5</f>
-        <v>131673.44765485809</v>
-      </c>
-    </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B6" s="190">
+        <v>125263.16548665638</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B6" s="186">
         <v>1</v>
       </c>
-      <c r="C6" s="190" t="s">
+      <c r="C6" s="186" t="s">
         <v>83</v>
       </c>
-      <c r="D6" s="191">
-        <v>0</v>
-      </c>
-      <c r="E6" s="192">
-        <v>0</v>
-      </c>
-      <c r="F6" s="193">
-        <v>0</v>
-      </c>
-      <c r="H6" s="173">
+      <c r="D6" s="187">
+        <v>0</v>
+      </c>
+      <c r="E6" s="188">
+        <v>0</v>
+      </c>
+      <c r="F6" s="189">
+        <v>0</v>
+      </c>
+      <c r="H6" s="172">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="I6" s="194">
-        <v>1258.5903089702933</v>
-      </c>
-      <c r="K6" s="150">
+      <c r="I6" s="190">
+        <v>2570.172574693252</v>
+      </c>
+      <c r="K6" s="149">
         <f t="shared" si="0"/>
-        <v>1258.5903089702933</v>
-      </c>
-      <c r="M6" s="195">
+        <v>2570.172574693252</v>
+      </c>
+      <c r="M6" s="191">
         <f t="shared" ref="M6:M18" si="2">K6</f>
-        <v>1258.5903089702933</v>
-      </c>
-      <c r="O6" s="150">
+        <v>2570.172574693252</v>
+      </c>
+      <c r="O6" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B7" s="190">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B7" s="186">
         <v>2</v>
       </c>
-      <c r="C7" s="190" t="s">
+      <c r="C7" s="186" t="s">
         <v>81</v>
       </c>
-      <c r="D7" s="191">
-        <v>0</v>
-      </c>
-      <c r="E7" s="192">
-        <v>0</v>
-      </c>
-      <c r="F7" s="193">
-        <v>0</v>
-      </c>
-      <c r="H7" s="173">
+      <c r="D7" s="187">
+        <v>0</v>
+      </c>
+      <c r="E7" s="188">
+        <v>0</v>
+      </c>
+      <c r="F7" s="189">
+        <v>0</v>
+      </c>
+      <c r="H7" s="172">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="I7" s="194">
-        <v>1258.5903089702933</v>
-      </c>
-      <c r="K7" s="150">
+      <c r="I7" s="190">
+        <v>2570.172574693252</v>
+      </c>
+      <c r="K7" s="149">
         <f t="shared" si="0"/>
-        <v>1258.5903089702933</v>
-      </c>
-      <c r="M7" s="195">
+        <v>2570.172574693252</v>
+      </c>
+      <c r="M7" s="191">
         <f t="shared" si="2"/>
-        <v>1258.5903089702933</v>
-      </c>
-      <c r="O7" s="150">
+        <v>2570.172574693252</v>
+      </c>
+      <c r="O7" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B8" s="190">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B8" s="186">
         <v>2</v>
       </c>
-      <c r="C8" s="190" t="s">
+      <c r="C8" s="186" t="s">
         <v>84</v>
       </c>
-      <c r="D8" s="191">
-        <v>0</v>
-      </c>
-      <c r="E8" s="192">
-        <v>0</v>
-      </c>
-      <c r="F8" s="193">
-        <v>0</v>
-      </c>
-      <c r="H8" s="173">
+      <c r="D8" s="187">
+        <v>0</v>
+      </c>
+      <c r="E8" s="188">
+        <v>0</v>
+      </c>
+      <c r="F8" s="189">
+        <v>0</v>
+      </c>
+      <c r="H8" s="172">
         <v>6.6000000000000003E-2</v>
       </c>
-      <c r="I8" s="194">
-        <v>1538.2770442970254</v>
-      </c>
-      <c r="K8" s="150">
+      <c r="I8" s="190">
+        <v>3141.322035736197</v>
+      </c>
+      <c r="K8" s="149">
         <f t="shared" si="0"/>
-        <v>1538.2770442970254</v>
-      </c>
-      <c r="M8" s="195">
+        <v>3141.322035736197</v>
+      </c>
+      <c r="M8" s="191">
         <f t="shared" si="2"/>
-        <v>1538.2770442970254</v>
-      </c>
-      <c r="O8" s="150">
+        <v>3141.322035736197</v>
+      </c>
+      <c r="O8" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B9" s="190">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B9" s="186">
         <v>2</v>
       </c>
-      <c r="C9" s="190" t="s">
+      <c r="C9" s="186" t="s">
         <v>82</v>
       </c>
-      <c r="D9" s="191">
-        <v>0</v>
-      </c>
-      <c r="E9" s="192">
-        <v>0</v>
-      </c>
-      <c r="F9" s="193">
-        <v>0</v>
-      </c>
-      <c r="H9" s="173">
+      <c r="D9" s="187">
+        <v>0</v>
+      </c>
+      <c r="E9" s="188">
+        <v>0</v>
+      </c>
+      <c r="F9" s="189">
+        <v>0</v>
+      </c>
+      <c r="H9" s="172">
         <v>6.6000000000000003E-2</v>
       </c>
-      <c r="I9" s="194">
-        <v>1538.2770442970254</v>
-      </c>
-      <c r="K9" s="150">
+      <c r="I9" s="190">
+        <v>3141.322035736197</v>
+      </c>
+      <c r="K9" s="149">
         <f t="shared" si="0"/>
-        <v>1538.2770442970254</v>
-      </c>
-      <c r="M9" s="195">
+        <v>3141.322035736197</v>
+      </c>
+      <c r="M9" s="191">
         <f t="shared" si="2"/>
-        <v>1538.2770442970254</v>
-      </c>
-      <c r="O9" s="150">
+        <v>3141.322035736197</v>
+      </c>
+      <c r="O9" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B10" s="190">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B10" s="186">
         <v>2</v>
       </c>
-      <c r="C10" s="190" t="s">
+      <c r="C10" s="186" t="s">
         <v>83</v>
       </c>
-      <c r="D10" s="191">
-        <v>0</v>
-      </c>
-      <c r="E10" s="192">
-        <v>0</v>
-      </c>
-      <c r="F10" s="196">
-        <v>0</v>
-      </c>
-      <c r="H10" s="173">
+      <c r="D10" s="187">
+        <v>0</v>
+      </c>
+      <c r="E10" s="188">
+        <v>0</v>
+      </c>
+      <c r="F10" s="192">
+        <v>0</v>
+      </c>
+      <c r="H10" s="172">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="I10" s="194">
-        <v>1258.5903089702933</v>
-      </c>
-      <c r="K10" s="150">
+      <c r="I10" s="190">
+        <v>2570.172574693252</v>
+      </c>
+      <c r="K10" s="149">
         <f t="shared" si="0"/>
-        <v>1258.5903089702933</v>
-      </c>
-      <c r="M10" s="195">
+        <v>2570.172574693252</v>
+      </c>
+      <c r="M10" s="191">
         <f t="shared" si="2"/>
-        <v>1258.5903089702933</v>
-      </c>
-      <c r="O10" s="150">
+        <v>2570.172574693252</v>
+      </c>
+      <c r="O10" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B11" s="190">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B11" s="186">
         <v>3</v>
       </c>
-      <c r="C11" s="190" t="s">
+      <c r="C11" s="186" t="s">
         <v>81</v>
       </c>
-      <c r="D11" s="191">
-        <v>0</v>
-      </c>
-      <c r="E11" s="192">
-        <v>0</v>
-      </c>
-      <c r="F11" s="193">
-        <v>0</v>
-      </c>
-      <c r="H11" s="173">
+      <c r="D11" s="187">
+        <v>0</v>
+      </c>
+      <c r="E11" s="188">
+        <v>0</v>
+      </c>
+      <c r="F11" s="189">
+        <v>0</v>
+      </c>
+      <c r="H11" s="172">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="I11" s="194">
-        <v>1258.5903089702933</v>
-      </c>
-      <c r="K11" s="150">
+      <c r="I11" s="190">
+        <v>2570.172574693252</v>
+      </c>
+      <c r="K11" s="149">
         <f t="shared" si="0"/>
-        <v>1258.5903089702933</v>
-      </c>
-      <c r="M11" s="195">
+        <v>2570.172574693252</v>
+      </c>
+      <c r="M11" s="191">
         <f t="shared" si="2"/>
-        <v>1258.5903089702933</v>
-      </c>
-      <c r="O11" s="150">
+        <v>2570.172574693252</v>
+      </c>
+      <c r="O11" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B12" s="106">
         <v>3</v>
       </c>
       <c r="C12" s="106" t="s">
         <v>84</v>
       </c>
-      <c r="D12" s="174">
-        <v>199.80000000000018</v>
-      </c>
-      <c r="E12" s="192">
-        <v>0.36707697960683466</v>
-      </c>
-      <c r="F12" s="193">
-        <v>75474.621445544617</v>
-      </c>
-      <c r="H12" s="173">
+      <c r="D12" s="173">
+        <v>234.80000000000018</v>
+      </c>
+      <c r="E12" s="188">
+        <v>0.43887850467289752</v>
+      </c>
+      <c r="F12" s="189">
+        <v>95517.018128834432</v>
+      </c>
+      <c r="H12" s="172">
         <v>6.6000000000000003E-2</v>
       </c>
-      <c r="I12" s="194">
-        <v>1538.2770442970254</v>
-      </c>
-      <c r="K12" s="150">
+      <c r="I12" s="190">
+        <v>3141.322035736197</v>
+      </c>
+      <c r="K12" s="149">
         <f t="shared" si="0"/>
-        <v>77012.898489841638</v>
-      </c>
-      <c r="M12" s="195">
-        <v>0</v>
-      </c>
-      <c r="O12" s="150">
+        <v>98658.340164570633</v>
+      </c>
+      <c r="M12" s="191">
+        <v>0</v>
+      </c>
+      <c r="O12" s="149">
         <f t="shared" si="1"/>
-        <v>77012.898489841638</v>
-      </c>
-    </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B13" s="190">
+        <v>98658.340164570633</v>
+      </c>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B13" s="186">
         <v>3</v>
       </c>
-      <c r="C13" s="190" t="s">
+      <c r="C13" s="186" t="s">
         <v>82</v>
       </c>
-      <c r="D13" s="191">
-        <v>0</v>
-      </c>
-      <c r="E13" s="192">
-        <v>0</v>
-      </c>
-      <c r="F13" s="193">
-        <v>0</v>
-      </c>
-      <c r="H13" s="173">
+      <c r="D13" s="187">
+        <v>0</v>
+      </c>
+      <c r="E13" s="188">
+        <v>0</v>
+      </c>
+      <c r="F13" s="189">
+        <v>0</v>
+      </c>
+      <c r="H13" s="172">
         <v>6.6000000000000003E-2</v>
       </c>
-      <c r="I13" s="194">
-        <v>1538.2770442970254</v>
-      </c>
-      <c r="K13" s="150">
+      <c r="I13" s="190">
+        <v>3141.322035736197</v>
+      </c>
+      <c r="K13" s="149">
         <f t="shared" si="0"/>
-        <v>1538.2770442970254</v>
-      </c>
-      <c r="M13" s="195">
+        <v>3141.322035736197</v>
+      </c>
+      <c r="M13" s="191">
         <f t="shared" si="2"/>
-        <v>1538.2770442970254</v>
-      </c>
-      <c r="O13" s="150">
+        <v>3141.322035736197</v>
+      </c>
+      <c r="O13" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B14" s="190">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B14" s="186">
         <v>3</v>
       </c>
-      <c r="C14" s="190" t="s">
+      <c r="C14" s="186" t="s">
         <v>83</v>
       </c>
-      <c r="D14" s="191">
-        <v>0</v>
-      </c>
-      <c r="E14" s="192">
-        <v>0</v>
-      </c>
-      <c r="F14" s="193">
-        <v>0</v>
-      </c>
-      <c r="H14" s="173">
+      <c r="D14" s="187">
+        <v>0</v>
+      </c>
+      <c r="E14" s="188">
+        <v>0</v>
+      </c>
+      <c r="F14" s="189">
+        <v>0</v>
+      </c>
+      <c r="H14" s="172">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="I14" s="194">
-        <v>1258.5903089702933</v>
-      </c>
-      <c r="K14" s="150">
+      <c r="I14" s="190">
+        <v>2570.172574693252</v>
+      </c>
+      <c r="K14" s="149">
         <f t="shared" si="0"/>
-        <v>1258.5903089702933</v>
-      </c>
-      <c r="M14" s="195">
+        <v>2570.172574693252</v>
+      </c>
+      <c r="M14" s="191">
         <f t="shared" si="2"/>
-        <v>1258.5903089702933</v>
-      </c>
-      <c r="O14" s="150">
+        <v>2570.172574693252</v>
+      </c>
+      <c r="O14" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B15" s="190">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B15" s="186">
         <v>4</v>
       </c>
-      <c r="C15" s="190" t="s">
+      <c r="C15" s="186" t="s">
         <v>81</v>
       </c>
-      <c r="D15" s="191">
-        <v>0</v>
-      </c>
-      <c r="E15" s="192">
-        <v>0</v>
-      </c>
-      <c r="F15" s="193">
-        <v>0</v>
-      </c>
-      <c r="H15" s="173">
+      <c r="D15" s="187">
+        <v>0</v>
+      </c>
+      <c r="E15" s="188">
+        <v>0</v>
+      </c>
+      <c r="F15" s="189">
+        <v>0</v>
+      </c>
+      <c r="H15" s="172">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="I15" s="194">
-        <v>1258.5903089702933</v>
-      </c>
-      <c r="K15" s="150">
+      <c r="I15" s="190">
+        <v>2570.172574693252</v>
+      </c>
+      <c r="K15" s="149">
         <f t="shared" si="0"/>
-        <v>1258.5903089702933</v>
-      </c>
-      <c r="M15" s="195">
+        <v>2570.172574693252</v>
+      </c>
+      <c r="M15" s="191">
         <f t="shared" si="2"/>
-        <v>1258.5903089702933</v>
-      </c>
-      <c r="O15" s="150">
+        <v>2570.172574693252</v>
+      </c>
+      <c r="O15" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B16" s="190">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B16" s="186">
         <v>4</v>
       </c>
-      <c r="C16" s="190" t="s">
+      <c r="C16" s="186" t="s">
         <v>84</v>
       </c>
-      <c r="D16" s="191">
-        <v>0</v>
-      </c>
-      <c r="E16" s="192">
-        <v>0</v>
-      </c>
-      <c r="F16" s="193">
-        <v>0</v>
-      </c>
-      <c r="H16" s="173">
+      <c r="D16" s="187">
+        <v>0</v>
+      </c>
+      <c r="E16" s="188">
+        <v>0</v>
+      </c>
+      <c r="F16" s="189">
+        <v>0</v>
+      </c>
+      <c r="H16" s="172">
         <v>6.6000000000000003E-2</v>
       </c>
-      <c r="I16" s="194">
-        <v>1538.2770442970254</v>
-      </c>
-      <c r="K16" s="150">
+      <c r="I16" s="190">
+        <v>3141.322035736197</v>
+      </c>
+      <c r="K16" s="149">
         <f t="shared" si="0"/>
-        <v>1538.2770442970254</v>
-      </c>
-      <c r="M16" s="195">
+        <v>3141.322035736197</v>
+      </c>
+      <c r="M16" s="191">
         <f t="shared" si="2"/>
-        <v>1538.2770442970254</v>
-      </c>
-      <c r="O16" s="150">
+        <v>3141.322035736197</v>
+      </c>
+      <c r="O16" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B17" s="190">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B17" s="186">
         <v>4</v>
       </c>
-      <c r="C17" s="190" t="s">
+      <c r="C17" s="186" t="s">
         <v>82</v>
       </c>
-      <c r="D17" s="191">
-        <v>0</v>
-      </c>
-      <c r="E17" s="192">
-        <v>0</v>
-      </c>
-      <c r="F17" s="193">
-        <v>0</v>
-      </c>
-      <c r="H17" s="173">
+      <c r="D17" s="187">
+        <v>0</v>
+      </c>
+      <c r="E17" s="188">
+        <v>0</v>
+      </c>
+      <c r="F17" s="189">
+        <v>0</v>
+      </c>
+      <c r="H17" s="172">
         <v>6.6000000000000003E-2</v>
       </c>
-      <c r="I17" s="194">
-        <v>1538.2770442970254</v>
-      </c>
-      <c r="K17" s="150">
+      <c r="I17" s="190">
+        <v>3141.322035736197</v>
+      </c>
+      <c r="K17" s="149">
         <f t="shared" si="0"/>
-        <v>1538.2770442970254</v>
-      </c>
-      <c r="M17" s="195">
+        <v>3141.322035736197</v>
+      </c>
+      <c r="M17" s="191">
         <f t="shared" si="2"/>
-        <v>1538.2770442970254</v>
-      </c>
-      <c r="O17" s="150">
+        <v>3141.322035736197</v>
+      </c>
+      <c r="O17" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B18" s="190">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B18" s="186">
         <v>4</v>
       </c>
-      <c r="C18" s="190" t="s">
+      <c r="C18" s="186" t="s">
         <v>83</v>
       </c>
-      <c r="D18" s="191">
-        <v>0</v>
-      </c>
-      <c r="E18" s="192">
-        <v>0</v>
-      </c>
-      <c r="F18" s="193">
-        <v>0</v>
-      </c>
-      <c r="H18" s="173">
+      <c r="D18" s="187">
+        <v>0</v>
+      </c>
+      <c r="E18" s="188">
+        <v>0</v>
+      </c>
+      <c r="F18" s="189">
+        <v>0</v>
+      </c>
+      <c r="H18" s="172">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="I18" s="194">
-        <v>1258.5903089702933</v>
-      </c>
-      <c r="K18" s="150">
+      <c r="I18" s="190">
+        <v>2570.172574693252</v>
+      </c>
+      <c r="K18" s="149">
         <f t="shared" si="0"/>
-        <v>1258.5903089702933</v>
-      </c>
-      <c r="M18" s="195">
+        <v>2570.172574693252</v>
+      </c>
+      <c r="M18" s="191">
         <f t="shared" si="2"/>
-        <v>1258.5903089702933</v>
-      </c>
-      <c r="O18" s="150">
+        <v>2570.172574693252</v>
+      </c>
+      <c r="O18" s="149">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B19" s="190"/>
-      <c r="C19" s="190"/>
-      <c r="D19" s="191"/>
-      <c r="E19" s="192"/>
-      <c r="F19" s="197"/>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B19" s="186"/>
+      <c r="C19" s="186"/>
+      <c r="D19" s="187"/>
+      <c r="E19" s="188"/>
+      <c r="F19" s="193"/>
       <c r="H19" s="106"/>
-      <c r="I19" s="175"/>
+      <c r="I19" s="174"/>
       <c r="K19" s="106"/>
-      <c r="M19" s="108"/>
-      <c r="O19" s="107"/>
-    </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="M19" s="107"/>
+      <c r="O19" s="198"/>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B20" s="106"/>
       <c r="C20" s="106" t="s">
-        <v>148</v>
-      </c>
-      <c r="D20" s="174">
+        <v>141</v>
+      </c>
+      <c r="D20" s="173">
         <f>SUM(D4:D19)</f>
-        <v>544.30000000000018</v>
-      </c>
-      <c r="E20" s="107"/>
-      <c r="F20" s="197">
+        <v>535</v>
+      </c>
+      <c r="E20" s="198"/>
+      <c r="F20" s="193">
         <f>SUM(F4:F19)</f>
-        <v>205609.79205610568</v>
-      </c>
-      <c r="H20" s="198"/>
-      <c r="I20" s="175">
+        <v>217638.86157975462</v>
+      </c>
+      <c r="H20" s="194"/>
+      <c r="I20" s="174">
         <f>SUM(I4:I19)</f>
-        <v>22374.938826138547</v>
-      </c>
-      <c r="K20" s="150">
+        <v>45691.956883435589</v>
+      </c>
+      <c r="K20" s="149">
         <f>SUM(K4:K19)</f>
-        <v>227984.7308822443</v>
-      </c>
-      <c r="M20" s="199">
+        <v>263330.81846319023</v>
+      </c>
+      <c r="M20" s="195">
         <f>SUM(M4:M19)</f>
-        <v>19298.384737544497</v>
-      </c>
-      <c r="O20" s="150">
+        <v>39409.312811963202</v>
+      </c>
+      <c r="O20" s="149">
         <f>SUM(O4:O19)</f>
-        <v>208686.34614469972</v>
-      </c>
-    </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
+        <v>223921.50565122702</v>
+      </c>
+    </row>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B21" s="106"/>
       <c r="C21" s="106"/>
       <c r="D21" s="4"/>
       <c r="E21" s="4" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="F21" s="4"/>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B22" s="106" t="s">
         <v>85</v>
       </c>
@@ -5371,23 +5388,25 @@
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
-      <c r="H22" s="173">
+      <c r="H22" s="172">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="I22" s="194">
-        <v>163.15059560726027</v>
-      </c>
-      <c r="K22" s="200">
+      <c r="I22" s="190">
+        <v>333.17051894171789</v>
+      </c>
+      <c r="K22" s="190">
         <f>I22</f>
-        <v>163.15059560726027</v>
-      </c>
-      <c r="M22" s="201"/>
-      <c r="O22" s="150">
+        <v>333.17051894171789</v>
+      </c>
+      <c r="M22" s="196">
+        <v>333.17051894171789</v>
+      </c>
+      <c r="O22" s="149">
         <f>K22-M22</f>
-        <v>163.15059560726027</v>
-      </c>
-    </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B23" s="106" t="s">
         <v>85</v>
       </c>
@@ -5397,23 +5416,25 @@
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
-      <c r="H23" s="173">
+      <c r="H23" s="172">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="I23" s="194">
-        <v>139.84336766336594</v>
-      </c>
-      <c r="K23" s="200">
+      <c r="I23" s="190">
+        <v>285.57473052147247</v>
+      </c>
+      <c r="K23" s="190">
         <f t="shared" ref="K23:K29" si="3">I23</f>
-        <v>139.84336766336594</v>
-      </c>
-      <c r="M23" s="201"/>
-      <c r="O23" s="150">
+        <v>285.57473052147247</v>
+      </c>
+      <c r="M23" s="196">
+        <v>285.57473052147247</v>
+      </c>
+      <c r="O23" s="149">
         <f t="shared" ref="O23:O29" si="4">K23-M23</f>
-        <v>139.84336766336594</v>
-      </c>
-    </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B24" s="106" t="s">
         <v>85</v>
       </c>
@@ -5423,23 +5444,25 @@
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
-      <c r="H24" s="173">
+      <c r="H24" s="172">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="I24" s="194">
-        <v>139.84336766336594</v>
-      </c>
-      <c r="K24" s="200">
+      <c r="I24" s="190">
+        <v>285.57473052147247</v>
+      </c>
+      <c r="K24" s="190">
         <f t="shared" si="3"/>
-        <v>139.84336766336594</v>
-      </c>
-      <c r="M24" s="201"/>
-      <c r="O24" s="150">
+        <v>285.57473052147247</v>
+      </c>
+      <c r="M24" s="196">
+        <v>285.57473052147247</v>
+      </c>
+      <c r="O24" s="149">
         <f t="shared" si="4"/>
-        <v>139.84336766336594</v>
-      </c>
-    </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B25" s="106" t="s">
         <v>85</v>
       </c>
@@ -5449,23 +5472,25 @@
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
-      <c r="H25" s="173">
+      <c r="H25" s="172">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="I25" s="194">
-        <v>139.84336766336594</v>
-      </c>
-      <c r="K25" s="200">
+      <c r="I25" s="190">
+        <v>285.57473052147247</v>
+      </c>
+      <c r="K25" s="190">
         <f t="shared" si="3"/>
-        <v>139.84336766336594</v>
-      </c>
-      <c r="M25" s="201"/>
-      <c r="O25" s="150">
+        <v>285.57473052147247</v>
+      </c>
+      <c r="M25" s="196">
+        <v>285.57473052147247</v>
+      </c>
+      <c r="O25" s="149">
         <f t="shared" si="4"/>
-        <v>139.84336766336594</v>
-      </c>
-    </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B26" s="106" t="s">
         <v>85</v>
       </c>
@@ -5475,23 +5500,25 @@
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
-      <c r="H26" s="173">
+      <c r="H26" s="172">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="I26" s="194">
-        <v>139.84336766336594</v>
-      </c>
-      <c r="K26" s="200">
+      <c r="I26" s="190">
+        <v>285.57473052147247</v>
+      </c>
+      <c r="K26" s="190">
         <f t="shared" si="3"/>
-        <v>139.84336766336594</v>
-      </c>
-      <c r="M26" s="201"/>
-      <c r="O26" s="150">
+        <v>285.57473052147247</v>
+      </c>
+      <c r="M26" s="196">
+        <v>285.57473052147247</v>
+      </c>
+      <c r="O26" s="149">
         <f t="shared" si="4"/>
-        <v>139.84336766336594</v>
-      </c>
-    </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B27" s="106" t="s">
         <v>85</v>
       </c>
@@ -5501,23 +5528,25 @@
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
-      <c r="H27" s="173">
+      <c r="H27" s="172">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="I27" s="194">
-        <v>69.921683831682969</v>
-      </c>
-      <c r="K27" s="200">
+      <c r="I27" s="190">
+        <v>142.78736526073624</v>
+      </c>
+      <c r="K27" s="190">
         <f t="shared" si="3"/>
-        <v>69.921683831682969</v>
-      </c>
-      <c r="M27" s="201"/>
-      <c r="O27" s="150">
+        <v>142.78736526073624</v>
+      </c>
+      <c r="M27" s="196">
+        <v>142.78736526073624</v>
+      </c>
+      <c r="O27" s="149">
         <f t="shared" si="4"/>
-        <v>69.921683831682969</v>
-      </c>
-    </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B28" s="106" t="s">
         <v>85</v>
       </c>
@@ -5527,23 +5556,25 @@
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
-      <c r="H28" s="173">
+      <c r="H28" s="172">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="I28" s="194">
-        <v>69.921683831682969</v>
-      </c>
-      <c r="K28" s="200">
+      <c r="I28" s="190">
+        <v>142.78736526073624</v>
+      </c>
+      <c r="K28" s="190">
         <f t="shared" si="3"/>
-        <v>69.921683831682969</v>
-      </c>
-      <c r="M28" s="201"/>
-      <c r="O28" s="150">
+        <v>142.78736526073624</v>
+      </c>
+      <c r="M28" s="196">
+        <v>142.78736526073624</v>
+      </c>
+      <c r="O28" s="149">
         <f t="shared" si="4"/>
-        <v>69.921683831682969</v>
-      </c>
-    </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B29" s="106" t="s">
         <v>85</v>
       </c>
@@ -5553,69 +5584,71 @@
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
-      <c r="H29" s="173">
+      <c r="H29" s="172">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="I29" s="194">
-        <v>69.921683831682969</v>
-      </c>
-      <c r="K29" s="200">
+      <c r="I29" s="190">
+        <v>142.78736526073624</v>
+      </c>
+      <c r="K29" s="190">
         <f t="shared" si="3"/>
-        <v>69.921683831682969</v>
-      </c>
-      <c r="M29" s="201"/>
-      <c r="O29" s="150">
+        <v>142.78736526073624</v>
+      </c>
+      <c r="M29" s="196">
+        <v>142.78736526073624</v>
+      </c>
+      <c r="O29" s="149">
         <f t="shared" si="4"/>
-        <v>69.921683831682969</v>
-      </c>
-    </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="H30" s="107" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="H30" s="198" t="s">
         <v>130</v>
       </c>
-      <c r="I30" s="194">
+      <c r="I30" s="190">
         <f>SUM(I22:I29)</f>
-        <v>932.28911775577285</v>
-      </c>
-      <c r="K30" s="202">
+        <v>1903.8315368098165</v>
+      </c>
+      <c r="K30" s="244">
         <f>SUM(K22:K29)</f>
-        <v>932.28911775577285</v>
-      </c>
-      <c r="M30" s="199">
+        <v>1903.8315368098165</v>
+      </c>
+      <c r="M30" s="195">
         <f>SUM(M22:M29)</f>
-        <v>0</v>
-      </c>
-      <c r="O30" s="150">
+        <v>1903.8315368098165</v>
+      </c>
+      <c r="O30" s="149">
         <f>SUM(O22:O29)</f>
-        <v>932.28911775577285</v>
-      </c>
-    </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="O31" s="150"/>
-    </row>
-    <row r="32" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D32" s="244" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="O31" s="149"/>
+    </row>
+    <row r="32" spans="2:15" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D32" s="241" t="s">
         <v>131</v>
       </c>
-      <c r="E32" s="245"/>
-      <c r="F32" s="177">
-        <v>228917.02000000002</v>
-      </c>
-      <c r="I32" s="203">
+      <c r="E32" s="242"/>
+      <c r="F32" s="176">
+        <v>265234.65000000002</v>
+      </c>
+      <c r="I32" s="197">
         <f>F20+I20+I30</f>
-        <v>228917.02000000002</v>
-      </c>
-      <c r="K32" s="150">
+        <v>265234.65000000002</v>
+      </c>
+      <c r="K32" s="149">
         <f>K20+K30</f>
-        <v>228917.02000000008</v>
-      </c>
-      <c r="M32" s="199">
+        <v>265234.65000000002</v>
+      </c>
+      <c r="M32" s="195">
         <f>M20+M30</f>
-        <v>19298.384737544497</v>
-      </c>
-      <c r="O32" s="150">
+        <v>41313.144348773021</v>
+      </c>
+      <c r="O32" s="149">
         <f>O20+O30</f>
-        <v>209618.6352624555</v>
+        <v>223921.50565122702</v>
       </c>
     </row>
   </sheetData>
@@ -5624,18 +5657,17 @@
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="D32:E32"/>
   </mergeCells>
-  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="90" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B474AF3-BA14-4AC3-BE41-D99CD4C43EE8}">
   <dimension ref="C3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="3" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C3" s="178" t="s">
+    <row r="3" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C3" s="177" t="s">
         <v>132</v>
       </c>
     </row>

--- a/2026/SALTA 1167/Septiembre/SALTA1167-Septiembre.xlsx
+++ b/2026/SALTA 1167/Septiembre/SALTA1167-Septiembre.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\SALTA 1167\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6146B3C0-67BC-4322-B5EC-B5C011725E1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ED1FC23-7FB0-4F03-96CA-618F395DA8E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -519,7 +519,7 @@
     <numFmt numFmtId="169" formatCode="_-[$$-2C0A]\ * #,##0.0_-;\-[$$-2C0A]\ * #,##0.0_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="170" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
   </numFmts>
-  <fonts count="29" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -602,16 +602,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <i/>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="9"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -632,22 +622,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -662,16 +636,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <u/>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -731,8 +695,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color rgb="FFFF0000"/>
+      <b/>
+      <sz val="16"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1174,19 +1138,14 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="249">
+  <cellXfs count="241">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="2" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1197,7 +1156,6 @@
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1214,24 +1172,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="44" fontId="13" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="12" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="5" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1239,29 +1197,29 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="17" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="17" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="17" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="17" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="17" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="13" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="14" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="14" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="14" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="14" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="12" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="5" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1271,10 +1229,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="9" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1288,12 +1246,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="12" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1310,23 +1268,22 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="20" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="13" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="12" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="9" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1372,38 +1329,38 @@
     <xf numFmtId="167" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="17" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="17" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="17" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="12" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="12" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="14" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="14" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="14" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="11" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="8" fontId="9" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="9" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="19" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="9" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="9" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="24" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="19" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="20" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="19" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="19" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="13" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="13" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="12" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="12" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1423,9 +1380,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1441,7 +1395,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1453,11 +1407,11 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
@@ -1472,13 +1426,13 @@
     </xf>
     <xf numFmtId="8" fontId="6" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="6" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1487,7 +1441,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="23" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="19" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1500,19 +1454,39 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="22" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="18" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1520,97 +1494,79 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1622,9 +1578,6 @@
     <xf numFmtId="0" fontId="8" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1634,22 +1587,25 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="8" fontId="7" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="28" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="28" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="7" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="14" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -2065,503 +2021,541 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="12"/>
-      <c r="B1" s="44" t="s">
+      <c r="A1" s="7"/>
+      <c r="B1" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="45"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="39"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="13"/>
-      <c r="B2" s="46" t="s">
+      <c r="A2" s="8"/>
+      <c r="B2" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="47"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="41"/>
     </row>
     <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="13"/>
-      <c r="B3" s="205" t="s">
+      <c r="A3" s="8"/>
+      <c r="B3" s="201" t="s">
         <v>75</v>
       </c>
-      <c r="C3" s="205"/>
-      <c r="D3" s="205"/>
-      <c r="E3" s="206"/>
+      <c r="C3" s="201"/>
+      <c r="D3" s="201"/>
+      <c r="E3" s="202"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="62" t="s">
+      <c r="A4" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="56" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="18"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="13"/>
     </row>
     <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="46" t="s">
+      <c r="C5" s="9"/>
+      <c r="D5" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="15"/>
+      <c r="E5" s="10"/>
     </row>
     <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17" t="s">
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="E6" s="18"/>
+      <c r="E6" s="13"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="208" t="s">
+      <c r="A8" s="66"/>
+      <c r="B8" s="234" t="s">
         <v>143</v>
       </c>
-      <c r="C8" s="208"/>
+      <c r="C8" s="234"/>
+      <c r="D8" s="66"/>
+      <c r="E8" s="66"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="208"/>
-      <c r="C9" s="208"/>
+      <c r="A9" s="66"/>
+      <c r="B9" s="234"/>
+      <c r="C9" s="234"/>
+      <c r="D9" s="66"/>
+      <c r="E9" s="66"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="208"/>
-      <c r="C10" s="208"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+      <c r="A10" s="66"/>
+      <c r="B10" s="234"/>
+      <c r="C10" s="234"/>
+      <c r="D10" s="66"/>
+      <c r="E10" s="66"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="66"/>
+      <c r="B11" s="66"/>
+      <c r="C11" s="66"/>
+      <c r="D11" s="66"/>
+      <c r="E11" s="66"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="66"/>
+      <c r="B12" s="66"/>
+      <c r="C12" s="66"/>
+      <c r="D12" s="66"/>
+      <c r="E12" s="66"/>
+    </row>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="207" t="s">
+      <c r="A13" s="235" t="s">
         <v>98</v>
       </c>
-      <c r="B13" s="207"/>
-      <c r="C13" s="207"/>
-      <c r="D13" s="207"/>
-      <c r="E13" s="207"/>
+      <c r="B13" s="235"/>
+      <c r="C13" s="235"/>
+      <c r="D13" s="235"/>
+      <c r="E13" s="235"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="207"/>
-      <c r="B14" s="207"/>
-      <c r="C14" s="207"/>
-      <c r="D14" s="207"/>
-      <c r="E14" s="207"/>
+      <c r="A14" s="235"/>
+      <c r="B14" s="235"/>
+      <c r="C14" s="235"/>
+      <c r="D14" s="235"/>
+      <c r="E14" s="235"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="207"/>
-      <c r="B15" s="207"/>
-      <c r="C15" s="207"/>
-      <c r="D15" s="207"/>
-      <c r="E15" s="207"/>
+      <c r="A15" s="235"/>
+      <c r="B15" s="235"/>
+      <c r="C15" s="235"/>
+      <c r="D15" s="235"/>
+      <c r="E15" s="235"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="207"/>
-      <c r="B16" s="207"/>
-      <c r="C16" s="207"/>
-      <c r="D16" s="207"/>
-      <c r="E16" s="207"/>
-    </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+      <c r="A16" s="235"/>
+      <c r="B16" s="235"/>
+      <c r="C16" s="235"/>
+      <c r="D16" s="235"/>
+      <c r="E16" s="235"/>
+    </row>
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="66"/>
+      <c r="B17" s="66"/>
+      <c r="C17" s="66"/>
+      <c r="D17" s="66"/>
+      <c r="E17" s="66"/>
+    </row>
     <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
-    </row>
-    <row r="19" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+      <c r="A18" s="236"/>
+      <c r="B18" s="66"/>
+      <c r="C18" s="66"/>
+      <c r="D18" s="66"/>
+      <c r="E18" s="66"/>
+    </row>
+    <row r="19" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="66"/>
+      <c r="B19" s="66"/>
+      <c r="C19" s="66"/>
+      <c r="D19" s="66"/>
+      <c r="E19" s="66"/>
+    </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="158" t="s">
         <v>101</v>
       </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="11"/>
+      <c r="B20" s="159"/>
+      <c r="C20" s="160"/>
+      <c r="D20" s="70"/>
+      <c r="E20" s="71"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="22" t="s">
+      <c r="A21" s="145" t="s">
         <v>76</v>
       </c>
-      <c r="B21" s="22"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="98"/>
-      <c r="E21" s="93"/>
+      <c r="B21" s="145"/>
+      <c r="C21" s="145"/>
+      <c r="D21" s="91"/>
+      <c r="E21" s="134"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="203" t="s">
+      <c r="A22" s="197" t="s">
         <v>112</v>
       </c>
-      <c r="B22" s="204"/>
-      <c r="C22" s="150"/>
-      <c r="D22" s="200">
+      <c r="B22" s="198"/>
+      <c r="C22" s="143"/>
+      <c r="D22" s="170">
         <v>510846.85</v>
       </c>
-      <c r="E22" s="145" t="s">
+      <c r="E22" s="138" t="s">
         <v>148</v>
       </c>
-      <c r="H22" s="82"/>
+      <c r="H22" s="76"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="203"/>
-      <c r="B23" s="204"/>
-      <c r="C23" s="150"/>
-      <c r="D23" s="178"/>
-      <c r="E23" s="94"/>
-      <c r="H23" s="82"/>
+      <c r="A23" s="197"/>
+      <c r="B23" s="198"/>
+      <c r="C23" s="143"/>
+      <c r="D23" s="170"/>
+      <c r="E23" s="87"/>
+      <c r="H23" s="76"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="151" t="s">
+      <c r="A24" s="144" t="s">
         <v>9</v>
       </c>
-      <c r="B24" s="151"/>
-      <c r="C24" s="151"/>
-      <c r="D24" s="179"/>
-      <c r="E24" s="136">
+      <c r="B24" s="144"/>
+      <c r="C24" s="144"/>
+      <c r="D24" s="171"/>
+      <c r="E24" s="129">
         <f>SUM(D22:D23)</f>
         <v>510846.85</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="152" t="s">
+      <c r="A25" s="145" t="s">
         <v>17</v>
       </c>
-      <c r="B25" s="151"/>
-      <c r="C25" s="151"/>
-      <c r="D25" s="180"/>
-      <c r="E25" s="137"/>
+      <c r="B25" s="144"/>
+      <c r="C25" s="144"/>
+      <c r="D25" s="172"/>
+      <c r="E25" s="130"/>
     </row>
     <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="203" t="s">
+      <c r="A26" s="197" t="s">
         <v>117</v>
       </c>
-      <c r="B26" s="204"/>
-      <c r="C26" s="153"/>
-      <c r="D26" s="245">
+      <c r="B26" s="198"/>
+      <c r="C26" s="146"/>
+      <c r="D26" s="237">
         <v>74244</v>
       </c>
-      <c r="E26" s="96" t="s">
+      <c r="E26" s="89" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="151" t="s">
+      <c r="A27" s="144" t="s">
         <v>1</v>
       </c>
-      <c r="B27" s="151"/>
-      <c r="C27" s="151"/>
-      <c r="D27" s="179"/>
-      <c r="E27" s="104">
+      <c r="B27" s="144"/>
+      <c r="C27" s="144"/>
+      <c r="D27" s="171"/>
+      <c r="E27" s="97">
         <f>SUM(D26:D26)</f>
         <v>74244</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="152" t="s">
+      <c r="A28" s="145" t="s">
         <v>10</v>
       </c>
-      <c r="B28" s="154"/>
-      <c r="C28" s="154"/>
-      <c r="D28" s="181"/>
-      <c r="E28" s="138"/>
+      <c r="B28" s="147"/>
+      <c r="C28" s="147"/>
+      <c r="D28" s="173"/>
+      <c r="E28" s="131"/>
     </row>
     <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="65" t="s">
+      <c r="A29" s="59" t="s">
         <v>66</v>
       </c>
-      <c r="B29" s="65"/>
-      <c r="C29" s="65"/>
-      <c r="D29" s="199">
+      <c r="B29" s="59"/>
+      <c r="C29" s="59"/>
+      <c r="D29" s="88">
         <v>265234.65000000002</v>
       </c>
-      <c r="E29" s="96" t="s">
+      <c r="E29" s="89" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="65" t="s">
+      <c r="A30" s="59" t="s">
         <v>65</v>
       </c>
-      <c r="B30" s="65"/>
-      <c r="C30" s="65"/>
-      <c r="D30" s="199">
+      <c r="B30" s="59"/>
+      <c r="C30" s="59"/>
+      <c r="D30" s="88">
         <v>8972.48</v>
       </c>
-      <c r="E30" s="145" t="str">
+      <c r="E30" s="138" t="str">
         <f>E31</f>
         <v>Transf 07/09</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="65" t="s">
+      <c r="A31" s="59" t="s">
         <v>65</v>
       </c>
-      <c r="B31" s="155"/>
-      <c r="C31" s="65"/>
-      <c r="D31" s="199">
+      <c r="B31" s="148"/>
+      <c r="C31" s="59"/>
+      <c r="D31" s="88">
         <v>550258.93999999994</v>
       </c>
-      <c r="E31" s="96" t="s">
+      <c r="E31" s="89" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="201" t="s">
+      <c r="A32" s="199" t="s">
         <v>67</v>
       </c>
-      <c r="B32" s="202"/>
-      <c r="C32" s="65"/>
-      <c r="D32" s="199">
+      <c r="B32" s="200"/>
+      <c r="C32" s="59"/>
+      <c r="D32" s="88">
         <v>872785.72</v>
       </c>
-      <c r="E32" s="96" t="s">
+      <c r="E32" s="89" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="156" t="s">
+      <c r="A33" s="149" t="s">
         <v>77</v>
       </c>
-      <c r="B33" s="157"/>
-      <c r="C33" s="65"/>
-      <c r="D33" s="199">
+      <c r="B33" s="191"/>
+      <c r="C33" s="59"/>
+      <c r="D33" s="88">
         <v>30111.39</v>
       </c>
-      <c r="E33" s="96" t="s">
+      <c r="E33" s="89" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="151" t="s">
+      <c r="A34" s="144" t="s">
         <v>2</v>
       </c>
-      <c r="B34" s="151"/>
-      <c r="C34" s="151"/>
-      <c r="D34" s="182"/>
-      <c r="E34" s="139">
+      <c r="B34" s="144"/>
+      <c r="C34" s="144"/>
+      <c r="D34" s="174"/>
+      <c r="E34" s="132">
         <f>SUM(D29:D33)</f>
         <v>1727363.18</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="152"/>
-      <c r="B35" s="151"/>
-      <c r="C35" s="151"/>
-      <c r="D35" s="179"/>
-      <c r="E35" s="140"/>
+      <c r="A35" s="145"/>
+      <c r="B35" s="144"/>
+      <c r="C35" s="144"/>
+      <c r="D35" s="171"/>
+      <c r="E35" s="133"/>
     </row>
     <row r="36" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="203" t="s">
+      <c r="A36" s="197" t="s">
         <v>114</v>
       </c>
-      <c r="B36" s="204"/>
-      <c r="C36" s="65"/>
-      <c r="D36" s="199">
+      <c r="B36" s="198"/>
+      <c r="C36" s="59"/>
+      <c r="D36" s="88">
         <v>82000</v>
       </c>
-      <c r="E36" s="96" t="s">
+      <c r="E36" s="89" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="158" t="s">
+      <c r="A37" s="151" t="s">
         <v>151</v>
       </c>
-      <c r="B37" s="159"/>
-      <c r="C37" s="65"/>
-      <c r="D37" s="199">
+      <c r="B37" s="192"/>
+      <c r="C37" s="59"/>
+      <c r="D37" s="88">
         <v>52253.440000000002</v>
       </c>
-      <c r="E37" s="96" t="s">
+      <c r="E37" s="89" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="203" t="s">
+      <c r="A38" s="197" t="s">
         <v>152</v>
       </c>
-      <c r="B38" s="204"/>
-      <c r="C38" s="65"/>
-      <c r="D38" s="248">
+      <c r="B38" s="198"/>
+      <c r="C38" s="59"/>
+      <c r="D38" s="62">
         <v>200000</v>
       </c>
-      <c r="E38" s="96" t="s">
+      <c r="E38" s="89" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="151" t="s">
+      <c r="A39" s="144" t="s">
         <v>6</v>
       </c>
-      <c r="B39" s="152"/>
-      <c r="C39" s="152"/>
-      <c r="D39" s="152"/>
-      <c r="E39" s="104">
+      <c r="B39" s="145"/>
+      <c r="C39" s="145"/>
+      <c r="D39" s="145"/>
+      <c r="E39" s="97">
         <f>SUM(D36:D38)</f>
         <v>334253.44</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="152" t="s">
+      <c r="A40" s="145" t="s">
         <v>11</v>
       </c>
-      <c r="B40" s="152"/>
-      <c r="C40" s="152"/>
-      <c r="D40" s="98"/>
-      <c r="E40" s="141"/>
+      <c r="B40" s="145"/>
+      <c r="C40" s="145"/>
+      <c r="D40" s="91"/>
+      <c r="E40" s="134"/>
     </row>
     <row r="41" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="203" t="s">
+      <c r="A41" s="197" t="s">
         <v>145</v>
       </c>
-      <c r="B41" s="204"/>
-      <c r="C41" s="150"/>
-      <c r="D41" s="243">
+      <c r="B41" s="198"/>
+      <c r="C41" s="143"/>
+      <c r="D41" s="238">
         <v>190000</v>
       </c>
-      <c r="E41" s="142" t="s">
+      <c r="E41" s="135" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="151" t="s">
+      <c r="A42" s="144" t="s">
         <v>9</v>
       </c>
-      <c r="B42" s="151"/>
-      <c r="C42" s="151"/>
-      <c r="D42" s="179"/>
-      <c r="E42" s="136">
+      <c r="B42" s="144"/>
+      <c r="C42" s="144"/>
+      <c r="D42" s="171"/>
+      <c r="E42" s="129">
         <f>SUM(D41:D41)</f>
         <v>190000</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="152" t="s">
+      <c r="A43" s="145" t="s">
         <v>8</v>
       </c>
-      <c r="B43" s="160"/>
-      <c r="C43" s="151"/>
-      <c r="D43" s="183"/>
-      <c r="E43" s="104"/>
+      <c r="B43" s="152"/>
+      <c r="C43" s="144"/>
+      <c r="D43" s="175"/>
+      <c r="E43" s="97"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="65" t="s">
+      <c r="A44" s="59" t="s">
         <v>133</v>
       </c>
-      <c r="B44" s="65" t="s">
+      <c r="B44" s="59" t="s">
         <v>134</v>
       </c>
-      <c r="C44" s="65"/>
-      <c r="D44" s="95"/>
-      <c r="E44" s="143"/>
+      <c r="C44" s="59"/>
+      <c r="D44" s="88"/>
+      <c r="E44" s="136"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="65" t="s">
+      <c r="A45" s="59" t="s">
         <v>113</v>
       </c>
-      <c r="B45" s="65"/>
-      <c r="C45" s="65"/>
-      <c r="D45" s="199">
+      <c r="B45" s="59"/>
+      <c r="C45" s="59"/>
+      <c r="D45" s="88">
         <v>35494.269999999997</v>
       </c>
-      <c r="E45" s="144"/>
+      <c r="E45" s="137"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="161" t="s">
+      <c r="A46" s="153" t="s">
         <v>9</v>
       </c>
-      <c r="B46" s="161"/>
-      <c r="C46" s="161"/>
-      <c r="D46" s="184"/>
-      <c r="E46" s="104">
+      <c r="B46" s="153"/>
+      <c r="C46" s="153"/>
+      <c r="D46" s="176"/>
+      <c r="E46" s="97">
         <f>SUM(D44:D45)</f>
         <v>35494.269999999997</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="65"/>
-      <c r="B47" s="65"/>
-      <c r="C47" s="65"/>
-      <c r="D47" s="65"/>
-      <c r="E47" s="70"/>
+      <c r="A47" s="59"/>
+      <c r="B47" s="59"/>
+      <c r="C47" s="59"/>
+      <c r="D47" s="59"/>
+      <c r="E47" s="64"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="162" t="s">
+      <c r="A48" s="154" t="s">
         <v>97</v>
       </c>
-      <c r="B48" s="162"/>
-      <c r="C48" s="162"/>
-      <c r="D48" s="71"/>
-      <c r="E48" s="105">
-        <f>3000000-2926731.74</f>
-        <v>73268.259999999776</v>
+      <c r="B48" s="154"/>
+      <c r="C48" s="154"/>
+      <c r="D48" s="65"/>
+      <c r="E48" s="98">
+        <f>3000000-2872201.74</f>
+        <v>127798.25999999978</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="163"/>
-      <c r="B49" s="72"/>
-      <c r="C49" s="72"/>
-      <c r="D49" s="72"/>
-      <c r="E49" s="73"/>
-      <c r="F49" s="27"/>
+      <c r="A49" s="155"/>
+      <c r="B49" s="66"/>
+      <c r="C49" s="66"/>
+      <c r="D49" s="66"/>
+      <c r="E49" s="67"/>
+      <c r="F49" s="21"/>
     </row>
     <row r="50" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="164" t="s">
+      <c r="A50" s="156" t="s">
         <v>93</v>
       </c>
-      <c r="B50" s="165"/>
-      <c r="C50" s="74"/>
-      <c r="D50" s="74"/>
-      <c r="E50" s="75">
+      <c r="B50" s="157"/>
+      <c r="C50" s="68"/>
+      <c r="D50" s="68"/>
+      <c r="E50" s="69">
         <f>(SUM(E21:E48))</f>
-        <v>2945469.9999999995</v>
-      </c>
-      <c r="F50" s="92"/>
-      <c r="G50" s="27"/>
+        <v>2999999.9999999995</v>
+      </c>
+      <c r="F50" s="86"/>
+      <c r="G50" s="21"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="72"/>
-      <c r="B51" s="72"/>
-      <c r="C51" s="72"/>
-      <c r="D51" s="72"/>
-      <c r="E51" s="72"/>
+      <c r="A51" s="66"/>
+      <c r="B51" s="66"/>
+      <c r="C51" s="66"/>
+      <c r="D51" s="66"/>
+      <c r="E51" s="66"/>
     </row>
     <row r="52" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="72"/>
-      <c r="B52" s="72"/>
-      <c r="C52" s="72"/>
-      <c r="D52" s="72"/>
-      <c r="E52" s="72"/>
-      <c r="H52" s="99"/>
+      <c r="A52" s="66"/>
+      <c r="B52" s="66"/>
+      <c r="C52" s="66"/>
+      <c r="D52" s="66"/>
+      <c r="E52" s="66"/>
+      <c r="H52" s="92"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="166" t="s">
+      <c r="A53" s="158" t="s">
         <v>94</v>
       </c>
-      <c r="B53" s="167"/>
-      <c r="C53" s="168"/>
-      <c r="D53" s="76"/>
-      <c r="E53" s="77"/>
+      <c r="B53" s="159"/>
+      <c r="C53" s="160"/>
+      <c r="D53" s="70"/>
+      <c r="E53" s="71"/>
     </row>
     <row r="54" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="169"/>
-      <c r="B54" s="157"/>
-      <c r="C54" s="65"/>
-      <c r="D54" s="68"/>
-      <c r="E54" s="66"/>
+      <c r="A54" s="161"/>
+      <c r="B54" s="150"/>
+      <c r="C54" s="59"/>
+      <c r="D54" s="62"/>
+      <c r="E54" s="60"/>
     </row>
     <row r="55" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="211"/>
-      <c r="B55" s="211"/>
-      <c r="C55" s="65"/>
-      <c r="D55" s="95"/>
-      <c r="E55" s="66"/>
+      <c r="A55" s="196"/>
+      <c r="B55" s="196"/>
+      <c r="C55" s="59"/>
+      <c r="D55" s="88"/>
+      <c r="E55" s="60"/>
     </row>
     <row r="56" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="4"/>
@@ -2571,18 +2565,18 @@
       <c r="E56" s="4"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="67"/>
-      <c r="B57" s="69"/>
+      <c r="A57" s="61"/>
+      <c r="B57" s="63"/>
       <c r="C57" s="4"/>
-      <c r="D57" s="68"/>
-      <c r="E57" s="66"/>
+      <c r="D57" s="62"/>
+      <c r="E57" s="60"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="32"/>
-      <c r="B58" s="31"/>
-      <c r="C58" s="31"/>
-      <c r="D58" s="36"/>
-      <c r="E58" s="36">
+      <c r="A58" s="26"/>
+      <c r="B58" s="25"/>
+      <c r="C58" s="25"/>
+      <c r="D58" s="30"/>
+      <c r="E58" s="30">
         <f>SUM(D54:D57)</f>
         <v>0</v>
       </c>
@@ -2590,292 +2584,286 @@
     <row r="59" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="60" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="20" t="s">
+      <c r="A61" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="B61" s="20"/>
-      <c r="C61" s="20"/>
-      <c r="D61" s="21"/>
-      <c r="E61" s="134"/>
+      <c r="B61" s="15"/>
+      <c r="C61" s="15"/>
+      <c r="D61" s="16"/>
+      <c r="E61" s="127"/>
     </row>
     <row r="62" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="63" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B63" s="7"/>
+      <c r="B63" s="6"/>
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
-      <c r="E63" s="43">
+      <c r="E63" s="37">
         <f>E58+E61</f>
         <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="65" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="63" t="s">
+      <c r="A65" s="57" t="s">
         <v>102</v>
       </c>
-      <c r="B65" s="64">
+      <c r="B65" s="58">
         <f>E50</f>
-        <v>2945469.9999999995</v>
+        <v>2999999.9999999995</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="63" t="s">
+      <c r="A66" s="57" t="s">
         <v>103</v>
       </c>
-      <c r="B66" s="64">
+      <c r="B66" s="58">
         <f>E50-E48</f>
         <v>2872201.7399999998</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="63" t="s">
+      <c r="A67" s="57" t="s">
         <v>104</v>
       </c>
-      <c r="B67" s="64">
+      <c r="B67" s="58">
         <f>E63-E61</f>
         <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="63" t="s">
+      <c r="A68" s="57" t="s">
         <v>105</v>
       </c>
-      <c r="B68" s="64">
+      <c r="B68" s="58">
         <f>E63</f>
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70"/>
-      <c r="B70" s="26"/>
-      <c r="C70" s="24"/>
-    </row>
-    <row r="71" spans="1:5" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="84" t="s">
+      <c r="B70" s="20"/>
+      <c r="C70" s="18"/>
+    </row>
+    <row r="71" spans="1:5" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="78" t="s">
         <v>106</v>
       </c>
-      <c r="B71" s="110">
+      <c r="B71" s="103">
         <v>231226.35000000335</v>
       </c>
-      <c r="C71" s="24"/>
-      <c r="D71" s="30"/>
+      <c r="C71" s="18"/>
+      <c r="D71" s="24"/>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="35" t="s">
+      <c r="A72" s="29" t="s">
         <v>99</v>
       </c>
-      <c r="B72" s="89">
+      <c r="B72" s="83">
         <f>-B66</f>
         <v>-2872201.7399999998</v>
       </c>
-      <c r="E72" s="27"/>
+      <c r="E72" s="21"/>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="35" t="s">
+      <c r="A73" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="B73" s="89">
+      <c r="B73" s="83">
         <f>B93</f>
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="35" t="s">
+      <c r="A74" s="29" t="s">
         <v>108</v>
       </c>
-      <c r="B74" s="90">
+      <c r="B74" s="84">
         <f>PRORRATEO!G36-B80</f>
         <v>3060391.1300000008</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="87" t="s">
+      <c r="A75" s="81" t="s">
         <v>110</v>
       </c>
-      <c r="B75" s="88">
+      <c r="B75" s="82">
         <f>SUM(B71:C74)</f>
         <v>419415.74000000441</v>
       </c>
-      <c r="D75" s="27"/>
+      <c r="D75" s="21"/>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" s="85"/>
-      <c r="B76" s="85"/>
-      <c r="D76" s="27"/>
-      <c r="E76" s="26"/>
+      <c r="A76" s="79"/>
+      <c r="B76" s="79"/>
+      <c r="D76" s="21"/>
+      <c r="E76" s="20"/>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="84" t="s">
+      <c r="A77" s="78" t="s">
         <v>107</v>
       </c>
-      <c r="B77" s="110">
+      <c r="B77" s="103">
         <v>1000000</v>
       </c>
-      <c r="D77" s="26"/>
-      <c r="E77" s="27"/>
+      <c r="D77" s="20"/>
+      <c r="E77" s="21"/>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="35" t="s">
+      <c r="A78" s="29" t="s">
         <v>100</v>
       </c>
-      <c r="B78" s="89">
+      <c r="B78" s="83">
         <f>-B67</f>
         <v>0</v>
       </c>
-      <c r="D78" s="27"/>
-      <c r="E78" s="27"/>
+      <c r="D78" s="21"/>
+      <c r="E78" s="21"/>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="35" t="s">
+      <c r="A79" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="B79" s="89">
+      <c r="B79" s="83">
         <f>B101</f>
         <v>0</v>
       </c>
-      <c r="D79" s="27"/>
+      <c r="D79" s="21"/>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" s="35" t="s">
+      <c r="A80" s="29" t="s">
         <v>109</v>
       </c>
-      <c r="B80" s="90">
-        <v>0</v>
-      </c>
-      <c r="D80" s="135"/>
+      <c r="B80" s="84">
+        <v>0</v>
+      </c>
+      <c r="D80" s="128"/>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A81" s="91" t="s">
+      <c r="A81" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="B81" s="100"/>
-      <c r="D81" s="27"/>
-      <c r="E81" s="27"/>
-      <c r="F81" s="26"/>
+      <c r="B81" s="93"/>
+      <c r="D81" s="21"/>
+      <c r="E81" s="21"/>
+      <c r="F81" s="20"/>
     </row>
     <row r="82" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="87" t="s">
+      <c r="A82" s="81" t="s">
         <v>111</v>
       </c>
-      <c r="B82" s="88">
+      <c r="B82" s="82">
         <f>SUM(B77:C81)</f>
         <v>1000000</v>
       </c>
-      <c r="D82" s="27"/>
-      <c r="E82" s="27"/>
-      <c r="F82" s="27"/>
+      <c r="D82" s="21"/>
+      <c r="E82" s="21"/>
+      <c r="F82" s="21"/>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A83" s="85"/>
-      <c r="B83" s="85"/>
+      <c r="A83" s="79"/>
+      <c r="B83" s="79"/>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A84" s="85"/>
-      <c r="B84" s="85"/>
+      <c r="A84" s="79"/>
+      <c r="B84" s="79"/>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A85" s="84" t="s">
+      <c r="A85" s="78" t="s">
         <v>124</v>
       </c>
-      <c r="B85" s="110">
+      <c r="B85" s="103">
         <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A86" s="35" t="s">
+      <c r="A86" s="29" t="s">
         <v>125</v>
       </c>
-      <c r="B86" s="89">
+      <c r="B86" s="83">
         <v>1054849.6000000001</v>
       </c>
     </row>
     <row r="87" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="87" t="s">
+      <c r="A87" s="81" t="s">
         <v>154</v>
       </c>
-      <c r="B87" s="88">
+      <c r="B87" s="82">
         <v>1070612.72</v>
       </c>
     </row>
     <row r="88" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="89" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A89" s="210" t="s">
+      <c r="A89" s="195" t="s">
         <v>18</v>
       </c>
-      <c r="B89" s="210"/>
-      <c r="C89" s="210"/>
+      <c r="B89" s="195"/>
+      <c r="C89" s="195"/>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A90" s="210"/>
-      <c r="B90" s="210"/>
-      <c r="C90" s="210"/>
+      <c r="A90" s="195"/>
+      <c r="B90" s="195"/>
+      <c r="C90" s="195"/>
     </row>
     <row r="91" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="79"/>
-      <c r="B91" s="23"/>
-      <c r="C91" s="23">
+      <c r="A91" s="73"/>
+      <c r="B91" s="17"/>
+      <c r="C91" s="17">
         <v>40000</v>
       </c>
-      <c r="E91" s="92"/>
+      <c r="E91" s="86"/>
     </row>
     <row r="92" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="79"/>
-      <c r="B92" s="81"/>
-      <c r="C92" s="78"/>
-      <c r="D92" s="92"/>
+      <c r="A92" s="73"/>
+      <c r="B92" s="75"/>
+      <c r="C92" s="72"/>
+      <c r="D92" s="86"/>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A93" s="28" t="s">
+      <c r="A93" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="B93" s="80">
+      <c r="B93" s="74">
         <f>SUM(B91:B92)</f>
         <v>0</v>
       </c>
-      <c r="C93" s="29"/>
+      <c r="C93" s="23"/>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="M94" s="5"/>
     </row>
     <row r="95" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="209"/>
-      <c r="B95" s="209"/>
-      <c r="C95" s="209"/>
-      <c r="D95" s="209"/>
-      <c r="E95" s="209"/>
+      <c r="A95" s="194"/>
+      <c r="B95" s="194"/>
+      <c r="C95" s="194"/>
+      <c r="D95" s="194"/>
+      <c r="E95" s="194"/>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A96" s="209"/>
-      <c r="B96" s="209"/>
-      <c r="C96" s="209"/>
-      <c r="D96" s="209"/>
-      <c r="E96" s="209"/>
+      <c r="A96" s="194"/>
+      <c r="B96" s="194"/>
+      <c r="C96" s="194"/>
+      <c r="D96" s="194"/>
+      <c r="E96" s="194"/>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" s="209"/>
-      <c r="B97" s="209"/>
-      <c r="C97" s="209"/>
-      <c r="D97" s="209"/>
-      <c r="E97" s="209"/>
+      <c r="A97" s="194"/>
+      <c r="B97" s="194"/>
+      <c r="C97" s="194"/>
+      <c r="D97" s="194"/>
+      <c r="E97" s="194"/>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="209"/>
-      <c r="B98" s="209"/>
-      <c r="C98" s="209"/>
-      <c r="D98" s="209"/>
-      <c r="E98" s="209"/>
+      <c r="A98" s="194"/>
+      <c r="B98" s="194"/>
+      <c r="C98" s="194"/>
+      <c r="D98" s="194"/>
+      <c r="E98" s="194"/>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A95:E98"/>
-    <mergeCell ref="A89:C90"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A41:B41"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="A22:B22"/>
@@ -2883,6 +2871,12 @@
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="B8:C10"/>
     <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A95:E98"/>
+    <mergeCell ref="A89:C90"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A41:B41"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2916,574 +2910,574 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="111"/>
-      <c r="B1" s="112"/>
-      <c r="C1" s="113"/>
-      <c r="D1" s="113"/>
-      <c r="E1" s="212"/>
-      <c r="F1" s="212"/>
-      <c r="G1" s="212"/>
-      <c r="H1" s="212"/>
-      <c r="I1" s="212"/>
-      <c r="J1" s="212"/>
-      <c r="K1" s="212"/>
-      <c r="L1" s="212"/>
-      <c r="M1" s="212"/>
-      <c r="N1" s="212"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="114"/>
+      <c r="A1" s="104"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="208"/>
+      <c r="F1" s="208"/>
+      <c r="G1" s="208"/>
+      <c r="H1" s="208"/>
+      <c r="I1" s="208"/>
+      <c r="J1" s="208"/>
+      <c r="K1" s="208"/>
+      <c r="L1" s="208"/>
+      <c r="M1" s="208"/>
+      <c r="N1" s="208"/>
+      <c r="O1" s="105"/>
+      <c r="P1" s="107"/>
     </row>
     <row r="2" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="115"/>
-      <c r="B2" s="116"/>
-      <c r="C2" s="117"/>
-      <c r="D2" s="118"/>
-      <c r="E2" s="118" t="s">
+      <c r="A2" s="108"/>
+      <c r="B2" s="109"/>
+      <c r="C2" s="110"/>
+      <c r="D2" s="111"/>
+      <c r="E2" s="111" t="s">
         <v>92</v>
       </c>
-      <c r="F2" s="118"/>
-      <c r="G2" s="119">
-        <v>0</v>
-      </c>
-      <c r="H2" s="118"/>
-      <c r="I2" s="118"/>
-      <c r="J2" s="118" t="s">
+      <c r="F2" s="111"/>
+      <c r="G2" s="112">
+        <v>0</v>
+      </c>
+      <c r="H2" s="111"/>
+      <c r="I2" s="111"/>
+      <c r="J2" s="111" t="s">
         <v>91</v>
       </c>
-      <c r="K2" s="120">
+      <c r="K2" s="113">
         <v>3000000</v>
       </c>
-      <c r="L2" s="120"/>
-      <c r="M2" s="120"/>
-      <c r="N2" s="121"/>
-      <c r="O2" s="122"/>
-      <c r="P2" s="123"/>
-      <c r="Q2" s="19"/>
+      <c r="L2" s="113"/>
+      <c r="M2" s="113"/>
+      <c r="N2" s="114"/>
+      <c r="O2" s="115"/>
+      <c r="P2" s="116"/>
+      <c r="Q2" s="14"/>
     </row>
     <row r="3" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="115"/>
-      <c r="B3" s="116"/>
-      <c r="C3" s="117"/>
-      <c r="D3" s="117"/>
-      <c r="E3" s="117"/>
-      <c r="F3" s="117"/>
-      <c r="G3" s="124"/>
-      <c r="H3" s="117"/>
-      <c r="I3" s="117"/>
-      <c r="J3" s="117"/>
-      <c r="K3" s="117"/>
-      <c r="L3" s="117"/>
-      <c r="M3" s="117"/>
-      <c r="N3" s="121"/>
-      <c r="O3" s="122"/>
-      <c r="P3" s="123"/>
-      <c r="Q3" s="19"/>
+      <c r="A3" s="108"/>
+      <c r="B3" s="109"/>
+      <c r="C3" s="110"/>
+      <c r="D3" s="110"/>
+      <c r="E3" s="110"/>
+      <c r="F3" s="110"/>
+      <c r="G3" s="117"/>
+      <c r="H3" s="110"/>
+      <c r="I3" s="110"/>
+      <c r="J3" s="110"/>
+      <c r="K3" s="110"/>
+      <c r="L3" s="110"/>
+      <c r="M3" s="110"/>
+      <c r="N3" s="114"/>
+      <c r="O3" s="115"/>
+      <c r="P3" s="116"/>
+      <c r="Q3" s="14"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="223" t="s">
+      <c r="A4" s="215" t="s">
         <v>119</v>
       </c>
-      <c r="B4" s="224"/>
-      <c r="C4" s="224"/>
-      <c r="D4" s="224"/>
-      <c r="E4" s="224"/>
-      <c r="F4" s="224"/>
-      <c r="G4" s="224"/>
-      <c r="H4" s="224"/>
-      <c r="I4" s="224"/>
-      <c r="J4" s="224"/>
-      <c r="K4" s="224"/>
-      <c r="L4" s="224"/>
-      <c r="M4" s="224"/>
-      <c r="N4" s="224"/>
-      <c r="O4" s="224"/>
-      <c r="P4" s="225"/>
-      <c r="Q4" s="19"/>
+      <c r="B4" s="216"/>
+      <c r="C4" s="216"/>
+      <c r="D4" s="216"/>
+      <c r="E4" s="216"/>
+      <c r="F4" s="216"/>
+      <c r="G4" s="216"/>
+      <c r="H4" s="216"/>
+      <c r="I4" s="216"/>
+      <c r="J4" s="216"/>
+      <c r="K4" s="216"/>
+      <c r="L4" s="216"/>
+      <c r="M4" s="216"/>
+      <c r="N4" s="216"/>
+      <c r="O4" s="216"/>
+      <c r="P4" s="217"/>
+      <c r="Q4" s="14"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="226"/>
-      <c r="B5" s="227"/>
-      <c r="C5" s="227"/>
-      <c r="D5" s="227"/>
-      <c r="E5" s="227"/>
-      <c r="F5" s="227"/>
-      <c r="G5" s="227"/>
-      <c r="H5" s="227"/>
-      <c r="I5" s="227"/>
-      <c r="J5" s="227"/>
-      <c r="K5" s="227"/>
-      <c r="L5" s="227"/>
-      <c r="M5" s="227"/>
-      <c r="N5" s="227"/>
-      <c r="O5" s="227"/>
-      <c r="P5" s="228"/>
-      <c r="Q5" s="19"/>
+      <c r="A5" s="218"/>
+      <c r="B5" s="219"/>
+      <c r="C5" s="219"/>
+      <c r="D5" s="219"/>
+      <c r="E5" s="219"/>
+      <c r="F5" s="219"/>
+      <c r="G5" s="219"/>
+      <c r="H5" s="219"/>
+      <c r="I5" s="219"/>
+      <c r="J5" s="219"/>
+      <c r="K5" s="219"/>
+      <c r="L5" s="219"/>
+      <c r="M5" s="219"/>
+      <c r="N5" s="219"/>
+      <c r="O5" s="219"/>
+      <c r="P5" s="220"/>
+      <c r="Q5" s="14"/>
     </row>
     <row r="6" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="226"/>
-      <c r="B6" s="227"/>
-      <c r="C6" s="227"/>
-      <c r="D6" s="227"/>
-      <c r="E6" s="227"/>
-      <c r="F6" s="227"/>
-      <c r="G6" s="227"/>
-      <c r="H6" s="227"/>
-      <c r="I6" s="227"/>
-      <c r="J6" s="227"/>
-      <c r="K6" s="227"/>
-      <c r="L6" s="227"/>
-      <c r="M6" s="227"/>
-      <c r="N6" s="227"/>
-      <c r="O6" s="227"/>
-      <c r="P6" s="228"/>
-      <c r="Q6" s="19"/>
+      <c r="A6" s="218"/>
+      <c r="B6" s="219"/>
+      <c r="C6" s="219"/>
+      <c r="D6" s="219"/>
+      <c r="E6" s="219"/>
+      <c r="F6" s="219"/>
+      <c r="G6" s="219"/>
+      <c r="H6" s="219"/>
+      <c r="I6" s="219"/>
+      <c r="J6" s="219"/>
+      <c r="K6" s="219"/>
+      <c r="L6" s="219"/>
+      <c r="M6" s="219"/>
+      <c r="N6" s="219"/>
+      <c r="O6" s="219"/>
+      <c r="P6" s="220"/>
+      <c r="Q6" s="14"/>
     </row>
     <row r="7" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="226"/>
-      <c r="B7" s="227"/>
-      <c r="C7" s="227"/>
-      <c r="D7" s="227"/>
-      <c r="E7" s="227"/>
-      <c r="F7" s="227"/>
-      <c r="G7" s="227"/>
-      <c r="H7" s="227"/>
-      <c r="I7" s="227"/>
-      <c r="J7" s="227"/>
-      <c r="K7" s="227"/>
-      <c r="L7" s="227"/>
-      <c r="M7" s="227"/>
-      <c r="N7" s="227"/>
-      <c r="O7" s="227"/>
-      <c r="P7" s="228"/>
-      <c r="Q7" s="19"/>
+      <c r="A7" s="218"/>
+      <c r="B7" s="219"/>
+      <c r="C7" s="219"/>
+      <c r="D7" s="219"/>
+      <c r="E7" s="219"/>
+      <c r="F7" s="219"/>
+      <c r="G7" s="219"/>
+      <c r="H7" s="219"/>
+      <c r="I7" s="219"/>
+      <c r="J7" s="219"/>
+      <c r="K7" s="219"/>
+      <c r="L7" s="219"/>
+      <c r="M7" s="219"/>
+      <c r="N7" s="219"/>
+      <c r="O7" s="219"/>
+      <c r="P7" s="220"/>
+      <c r="Q7" s="14"/>
     </row>
     <row r="8" spans="1:17" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="229"/>
-      <c r="B8" s="230"/>
-      <c r="C8" s="230"/>
-      <c r="D8" s="230"/>
-      <c r="E8" s="230"/>
-      <c r="F8" s="230"/>
-      <c r="G8" s="230"/>
-      <c r="H8" s="230"/>
-      <c r="I8" s="230"/>
-      <c r="J8" s="230"/>
-      <c r="K8" s="230"/>
-      <c r="L8" s="230"/>
-      <c r="M8" s="230"/>
-      <c r="N8" s="230"/>
-      <c r="O8" s="230"/>
-      <c r="P8" s="231"/>
+      <c r="A8" s="221"/>
+      <c r="B8" s="222"/>
+      <c r="C8" s="222"/>
+      <c r="D8" s="222"/>
+      <c r="E8" s="222"/>
+      <c r="F8" s="222"/>
+      <c r="G8" s="222"/>
+      <c r="H8" s="222"/>
+      <c r="I8" s="222"/>
+      <c r="J8" s="222"/>
+      <c r="K8" s="222"/>
+      <c r="L8" s="222"/>
+      <c r="M8" s="222"/>
+      <c r="N8" s="222"/>
+      <c r="O8" s="222"/>
+      <c r="P8" s="223"/>
     </row>
     <row r="9" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="234" t="s">
+      <c r="A9" s="226" t="s">
         <v>118</v>
       </c>
-      <c r="B9" s="235"/>
-      <c r="C9" s="235"/>
-      <c r="D9" s="235"/>
-      <c r="E9" s="235"/>
-      <c r="F9" s="235"/>
-      <c r="G9" s="235"/>
-      <c r="H9" s="235"/>
-      <c r="I9" s="235"/>
-      <c r="J9" s="235"/>
-      <c r="K9" s="235"/>
-      <c r="L9" s="235"/>
-      <c r="M9" s="235"/>
-      <c r="N9" s="235"/>
-      <c r="O9" s="235"/>
-      <c r="P9" s="235"/>
+      <c r="B9" s="227"/>
+      <c r="C9" s="227"/>
+      <c r="D9" s="227"/>
+      <c r="E9" s="227"/>
+      <c r="F9" s="227"/>
+      <c r="G9" s="227"/>
+      <c r="H9" s="227"/>
+      <c r="I9" s="227"/>
+      <c r="J9" s="227"/>
+      <c r="K9" s="227"/>
+      <c r="L9" s="227"/>
+      <c r="M9" s="227"/>
+      <c r="N9" s="227"/>
+      <c r="O9" s="227"/>
+      <c r="P9" s="227"/>
     </row>
     <row r="10" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="236" t="s">
+      <c r="A10" s="228" t="s">
         <v>116</v>
       </c>
-      <c r="B10" s="236"/>
-      <c r="C10" s="236"/>
-      <c r="D10" s="236"/>
-      <c r="E10" s="236"/>
-      <c r="F10" s="236"/>
-      <c r="G10" s="236"/>
-      <c r="H10" s="236"/>
-      <c r="I10" s="236"/>
-      <c r="J10" s="236"/>
-      <c r="K10" s="236"/>
-      <c r="L10" s="236"/>
-      <c r="M10" s="236"/>
-      <c r="N10" s="236"/>
-      <c r="O10" s="236"/>
-      <c r="P10" s="236"/>
+      <c r="B10" s="228"/>
+      <c r="C10" s="228"/>
+      <c r="D10" s="228"/>
+      <c r="E10" s="228"/>
+      <c r="F10" s="228"/>
+      <c r="G10" s="228"/>
+      <c r="H10" s="228"/>
+      <c r="I10" s="228"/>
+      <c r="J10" s="228"/>
+      <c r="K10" s="228"/>
+      <c r="L10" s="228"/>
+      <c r="M10" s="228"/>
+      <c r="N10" s="228"/>
+      <c r="O10" s="228"/>
+      <c r="P10" s="228"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="217" t="s">
+      <c r="A11" s="203" t="s">
         <v>3</v>
       </c>
-      <c r="B11" s="101"/>
-      <c r="C11" s="217" t="s">
+      <c r="B11" s="94"/>
+      <c r="C11" s="203" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="217" t="s">
+      <c r="D11" s="203" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="217" t="s">
+      <c r="E11" s="203" t="s">
         <v>7</v>
       </c>
-      <c r="F11" s="213" t="s">
+      <c r="F11" s="206" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="217" t="s">
+      <c r="G11" s="203" t="s">
         <v>5</v>
       </c>
-      <c r="H11" s="219" t="s">
+      <c r="H11" s="211" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="213" t="s">
+      <c r="I11" s="206" t="s">
         <v>22</v>
       </c>
-      <c r="J11" s="213" t="s">
+      <c r="J11" s="206" t="s">
         <v>91</v>
       </c>
-      <c r="K11" s="221" t="s">
+      <c r="K11" s="213" t="s">
         <v>92</v>
       </c>
-      <c r="L11" s="213" t="s">
+      <c r="L11" s="206" t="s">
         <v>78</v>
       </c>
-      <c r="M11" s="213" t="s">
+      <c r="M11" s="206" t="s">
         <v>123</v>
       </c>
-      <c r="N11" s="39" t="s">
+      <c r="N11" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="O11" s="215" t="s">
+      <c r="O11" s="209" t="s">
         <v>12</v>
       </c>
-      <c r="P11" s="232" t="s">
+      <c r="P11" s="224" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="218"/>
-      <c r="B12" s="102"/>
-      <c r="C12" s="218"/>
-      <c r="D12" s="237"/>
-      <c r="E12" s="218"/>
-      <c r="F12" s="214"/>
-      <c r="G12" s="218"/>
-      <c r="H12" s="220"/>
-      <c r="I12" s="214"/>
-      <c r="J12" s="214"/>
-      <c r="K12" s="222"/>
-      <c r="L12" s="214"/>
-      <c r="M12" s="214"/>
-      <c r="N12" s="37" t="str">
+      <c r="A12" s="205"/>
+      <c r="B12" s="95"/>
+      <c r="C12" s="205"/>
+      <c r="D12" s="204"/>
+      <c r="E12" s="205"/>
+      <c r="F12" s="207"/>
+      <c r="G12" s="205"/>
+      <c r="H12" s="212"/>
+      <c r="I12" s="207"/>
+      <c r="J12" s="207"/>
+      <c r="K12" s="214"/>
+      <c r="L12" s="207"/>
+      <c r="M12" s="207"/>
+      <c r="N12" s="31" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 16/10</v>
       </c>
-      <c r="O12" s="216"/>
-      <c r="P12" s="233"/>
+      <c r="O12" s="210"/>
+      <c r="P12" s="225"/>
     </row>
     <row r="13" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="40">
+      <c r="A13" s="34">
         <v>1</v>
       </c>
-      <c r="B13" s="40" t="s">
+      <c r="B13" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="40" t="s">
+      <c r="C13" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="40"/>
-      <c r="E13" s="48">
+      <c r="D13" s="34"/>
+      <c r="E13" s="42">
         <v>12</v>
       </c>
-      <c r="F13" s="49">
+      <c r="F13" s="43">
         <v>360000.01</v>
       </c>
-      <c r="G13" s="246">
+      <c r="G13" s="44">
         <f>396280-G29-G31</f>
         <v>359999.64</v>
       </c>
-      <c r="H13" s="51">
+      <c r="H13" s="45">
         <f t="shared" ref="H13:H35" si="0">F13-G13</f>
         <v>0.36999999999534339</v>
       </c>
-      <c r="I13" s="51">
+      <c r="I13" s="45">
         <f>IF(H13&gt;0,H13*3%,0)</f>
         <v>1.1099999999860301E-2</v>
       </c>
-      <c r="J13" s="97">
+      <c r="J13" s="90">
         <f t="shared" ref="J13:J35" si="1">K$2*E13/100</f>
         <v>360000</v>
       </c>
-      <c r="K13" s="97">
+      <c r="K13" s="90">
         <f t="shared" ref="K13:K35" si="2">G$2*E13/100</f>
         <v>0</v>
       </c>
-      <c r="L13" s="133">
+      <c r="L13" s="126">
         <f>EDESUR!O4</f>
         <v>0</v>
       </c>
-      <c r="M13" s="147"/>
-      <c r="N13" s="132">
+      <c r="M13" s="140"/>
+      <c r="N13" s="125">
         <f>ROUND(SUM(H13:M13),0) + Q13</f>
         <v>360000.01</v>
       </c>
-      <c r="O13" s="52">
+      <c r="O13" s="46">
         <f>ROUND(N13*6% + N13,0) + Q13</f>
         <v>381600.01</v>
       </c>
-      <c r="P13" s="53">
+      <c r="P13" s="47">
         <f>ROUND(N13*3%,0) + N13</f>
         <v>370800.01</v>
       </c>
-      <c r="Q13" s="27">
+      <c r="Q13" s="21">
         <v>0.01</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="125">
+      <c r="A14" s="118">
         <v>2</v>
       </c>
-      <c r="B14" s="125" t="s">
+      <c r="B14" s="118" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="125" t="s">
+      <c r="C14" s="118" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="126"/>
-      <c r="E14" s="127">
+      <c r="D14" s="119"/>
+      <c r="E14" s="120">
         <v>6.6</v>
       </c>
-      <c r="F14" s="50">
+      <c r="F14" s="44">
         <v>339673.02</v>
       </c>
-      <c r="G14" s="246">
+      <c r="G14" s="44">
         <f>200000+140000</f>
         <v>340000</v>
       </c>
-      <c r="H14" s="128">
+      <c r="H14" s="121">
         <f t="shared" si="0"/>
         <v>-326.97999999998137</v>
       </c>
-      <c r="I14" s="128">
+      <c r="I14" s="121">
         <f t="shared" ref="I14:I35" si="3">IF(H14&gt;0,H14*3%,0)</f>
         <v>0</v>
       </c>
-      <c r="J14" s="129">
+      <c r="J14" s="122">
         <f t="shared" si="1"/>
         <v>198000</v>
       </c>
-      <c r="K14" s="129">
+      <c r="K14" s="122">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L14" s="133">
+      <c r="L14" s="126">
         <f>EDESUR!O5</f>
         <v>125263.16548665638</v>
       </c>
-      <c r="M14" s="148">
-        <v>0</v>
-      </c>
-      <c r="N14" s="132">
+      <c r="M14" s="141">
+        <v>0</v>
+      </c>
+      <c r="N14" s="125">
         <f t="shared" ref="N14:N35" si="4">ROUND(SUM(H14:M14),0) + Q14</f>
         <v>322936.02</v>
       </c>
-      <c r="O14" s="130">
+      <c r="O14" s="123">
         <f t="shared" ref="O14:O30" si="5">ROUND(N14*6% + N14,0) + Q14</f>
         <v>342312.02</v>
       </c>
-      <c r="P14" s="131">
+      <c r="P14" s="124">
         <f t="shared" ref="P14:P35" si="6">ROUND(N14*3%,0) + N14</f>
         <v>332624.02</v>
       </c>
-      <c r="Q14" s="27">
+      <c r="Q14" s="21">
         <f>Q13+0.01</f>
         <v>0.02</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="40">
+      <c r="A15" s="34">
         <v>3</v>
       </c>
-      <c r="B15" s="40" t="s">
+      <c r="B15" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="40" t="s">
+      <c r="C15" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="41" t="s">
+      <c r="D15" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="E15" s="48">
+      <c r="E15" s="42">
         <v>5.4</v>
       </c>
-      <c r="F15" s="49">
+      <c r="F15" s="43">
         <v>162000.03</v>
       </c>
-      <c r="G15" s="246">
+      <c r="G15" s="44">
         <f>F15</f>
         <v>162000.03</v>
       </c>
-      <c r="H15" s="51">
+      <c r="H15" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I15" s="51">
+      <c r="I15" s="45">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J15" s="97">
+      <c r="J15" s="90">
         <f t="shared" si="1"/>
         <v>162000.00000000003</v>
       </c>
-      <c r="K15" s="97">
+      <c r="K15" s="90">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L15" s="133">
+      <c r="L15" s="126">
         <f>EDESUR!O6</f>
         <v>0</v>
       </c>
-      <c r="M15" s="146"/>
-      <c r="N15" s="132">
+      <c r="M15" s="139"/>
+      <c r="N15" s="125">
         <f t="shared" si="4"/>
         <v>162000.03</v>
       </c>
-      <c r="O15" s="52">
+      <c r="O15" s="46">
         <f t="shared" si="5"/>
         <v>171720.03</v>
       </c>
-      <c r="P15" s="53">
+      <c r="P15" s="47">
         <f t="shared" si="6"/>
         <v>166860.03</v>
       </c>
-      <c r="Q15" s="27">
+      <c r="Q15" s="21">
         <f t="shared" ref="Q15:Q30" si="7">Q14+0.01</f>
         <v>0.03</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="40">
+      <c r="A16" s="34">
         <v>4</v>
       </c>
-      <c r="B16" s="40" t="s">
+      <c r="B16" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="40" t="s">
+      <c r="C16" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="D16" s="41" t="s">
+      <c r="D16" s="35" t="s">
         <v>121</v>
       </c>
-      <c r="E16" s="48">
+      <c r="E16" s="42">
         <v>6.6</v>
       </c>
-      <c r="F16" s="49">
+      <c r="F16" s="43">
         <v>191638.04</v>
       </c>
-      <c r="G16" s="246">
+      <c r="G16" s="44">
         <f>209778-G32</f>
         <v>191637.8</v>
       </c>
-      <c r="H16" s="51">
+      <c r="H16" s="45">
         <f t="shared" si="0"/>
         <v>0.2400000000197906</v>
       </c>
-      <c r="I16" s="51">
+      <c r="I16" s="45">
         <f t="shared" si="3"/>
         <v>7.2000000005937176E-3</v>
       </c>
-      <c r="J16" s="97">
+      <c r="J16" s="90">
         <f t="shared" si="1"/>
         <v>198000</v>
       </c>
-      <c r="K16" s="97">
+      <c r="K16" s="90">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L16" s="133">
+      <c r="L16" s="126">
         <f>EDESUR!O7</f>
         <v>0</v>
       </c>
-      <c r="M16" s="147"/>
-      <c r="N16" s="132">
+      <c r="M16" s="140"/>
+      <c r="N16" s="125">
         <f t="shared" si="4"/>
         <v>198000.04</v>
       </c>
-      <c r="O16" s="52">
+      <c r="O16" s="46">
         <f t="shared" si="5"/>
         <v>209880.04</v>
       </c>
-      <c r="P16" s="53">
+      <c r="P16" s="47">
         <f t="shared" si="6"/>
         <v>203940.04</v>
       </c>
-      <c r="Q16" s="27">
+      <c r="Q16" s="21">
         <f t="shared" si="7"/>
         <v>0.04</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="125">
+      <c r="A17" s="118">
         <v>5</v>
       </c>
-      <c r="B17" s="125" t="s">
+      <c r="B17" s="118" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="125" t="s">
+      <c r="C17" s="118" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="125" t="s">
+      <c r="D17" s="118" t="s">
         <v>90</v>
       </c>
-      <c r="E17" s="127">
+      <c r="E17" s="120">
         <v>6.6</v>
       </c>
-      <c r="F17" s="50">
+      <c r="F17" s="44">
         <v>198000.05</v>
       </c>
-      <c r="G17" s="246">
-        <f>F17</f>
+      <c r="G17" s="44">
+        <f t="shared" ref="G17:G22" si="8">F17</f>
         <v>198000.05</v>
       </c>
-      <c r="H17" s="128">
+      <c r="H17" s="121">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I17" s="128">
+      <c r="I17" s="121">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J17" s="129">
+      <c r="J17" s="122">
         <f t="shared" si="1"/>
         <v>198000</v>
       </c>
-      <c r="K17" s="129">
+      <c r="K17" s="122">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L17" s="133">
+      <c r="L17" s="126">
         <f>EDESUR!O8</f>
         <v>0</v>
       </c>
-      <c r="M17" s="148">
-        <v>0</v>
-      </c>
-      <c r="N17" s="132">
+      <c r="M17" s="141">
+        <v>0</v>
+      </c>
+      <c r="N17" s="125">
         <f t="shared" si="4"/>
         <v>198000.05</v>
       </c>
-      <c r="O17" s="130">
+      <c r="O17" s="123">
         <f t="shared" si="5"/>
         <v>209880.05</v>
       </c>
-      <c r="P17" s="131">
+      <c r="P17" s="124">
         <f t="shared" si="6"/>
         <v>203940.05</v>
       </c>
-      <c r="Q17" s="27">
+      <c r="Q17" s="21">
         <f t="shared" si="7"/>
         <v>0.05</v>
       </c>
@@ -3492,366 +3486,366 @@
       </c>
     </row>
     <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="40">
+      <c r="A18" s="34">
         <v>6</v>
       </c>
-      <c r="B18" s="40" t="s">
+      <c r="B18" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="40" t="s">
+      <c r="C18" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="D18" s="40" t="s">
+      <c r="D18" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="E18" s="48">
+      <c r="E18" s="42">
         <v>5.4</v>
       </c>
-      <c r="F18" s="49">
+      <c r="F18" s="43">
         <v>162000.06</v>
       </c>
-      <c r="G18" s="246">
-        <f>F18</f>
+      <c r="G18" s="44">
+        <f t="shared" si="8"/>
         <v>162000.06</v>
       </c>
-      <c r="H18" s="51">
+      <c r="H18" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I18" s="51">
+      <c r="I18" s="45">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J18" s="97">
+      <c r="J18" s="90">
         <f t="shared" si="1"/>
         <v>162000.00000000003</v>
       </c>
-      <c r="K18" s="97">
+      <c r="K18" s="90">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L18" s="133">
+      <c r="L18" s="126">
         <f>EDESUR!O9</f>
         <v>0</v>
       </c>
-      <c r="M18" s="147"/>
-      <c r="N18" s="132">
+      <c r="M18" s="140"/>
+      <c r="N18" s="125">
         <f t="shared" si="4"/>
         <v>162000.06</v>
       </c>
-      <c r="O18" s="52">
+      <c r="O18" s="46">
         <f t="shared" si="5"/>
         <v>171720.06</v>
       </c>
-      <c r="P18" s="53">
+      <c r="P18" s="47">
         <f t="shared" si="6"/>
         <v>166860.06</v>
       </c>
-      <c r="Q18" s="27">
+      <c r="Q18" s="21">
         <f t="shared" si="7"/>
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
     <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="125">
+      <c r="A19" s="118">
         <v>7</v>
       </c>
-      <c r="B19" s="125" t="s">
+      <c r="B19" s="118" t="s">
         <v>38</v>
       </c>
-      <c r="C19" s="125" t="s">
+      <c r="C19" s="118" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="125" t="s">
+      <c r="D19" s="118" t="s">
         <v>88</v>
       </c>
-      <c r="E19" s="127">
+      <c r="E19" s="120">
         <v>5.4</v>
       </c>
-      <c r="F19" s="50">
+      <c r="F19" s="44">
         <v>166860.07</v>
       </c>
-      <c r="G19" s="246">
-        <f>F19</f>
+      <c r="G19" s="44">
+        <f t="shared" si="8"/>
         <v>166860.07</v>
       </c>
-      <c r="H19" s="128">
+      <c r="H19" s="121">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I19" s="128">
+      <c r="I19" s="121">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J19" s="129">
+      <c r="J19" s="122">
         <f t="shared" si="1"/>
         <v>162000.00000000003</v>
       </c>
-      <c r="K19" s="129">
+      <c r="K19" s="122">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L19" s="133">
+      <c r="L19" s="126">
         <f>EDESUR!O10</f>
         <v>0</v>
       </c>
-      <c r="M19" s="147"/>
-      <c r="N19" s="132">
+      <c r="M19" s="140"/>
+      <c r="N19" s="125">
         <f t="shared" si="4"/>
         <v>162000.07</v>
       </c>
-      <c r="O19" s="130">
+      <c r="O19" s="123">
         <f t="shared" si="5"/>
         <v>171720.07</v>
       </c>
-      <c r="P19" s="131">
+      <c r="P19" s="124">
         <f t="shared" si="6"/>
         <v>166860.07</v>
       </c>
-      <c r="Q19" s="27">
+      <c r="Q19" s="21">
         <f t="shared" si="7"/>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="125">
+      <c r="A20" s="118">
         <v>8</v>
       </c>
-      <c r="B20" s="125" t="s">
+      <c r="B20" s="118" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="125" t="s">
+      <c r="C20" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="D20" s="126" t="s">
+      <c r="D20" s="119" t="s">
         <v>69</v>
       </c>
-      <c r="E20" s="127">
+      <c r="E20" s="120">
         <v>6.6</v>
       </c>
-      <c r="F20" s="50">
+      <c r="F20" s="44">
         <v>275013.08</v>
       </c>
-      <c r="G20" s="246">
-        <f>F20</f>
+      <c r="G20" s="44">
+        <f t="shared" si="8"/>
         <v>275013.08</v>
       </c>
-      <c r="H20" s="128">
+      <c r="H20" s="121">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I20" s="128">
+      <c r="I20" s="121">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J20" s="129">
+      <c r="J20" s="122">
         <f t="shared" si="1"/>
         <v>198000</v>
       </c>
-      <c r="K20" s="129">
+      <c r="K20" s="122">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L20" s="133">
+      <c r="L20" s="126">
         <f>EDESUR!O12</f>
         <v>98658.340164570633</v>
       </c>
-      <c r="M20" s="147"/>
-      <c r="N20" s="132">
+      <c r="M20" s="140"/>
+      <c r="N20" s="125">
         <f t="shared" si="4"/>
         <v>296658.08</v>
       </c>
-      <c r="O20" s="130">
+      <c r="O20" s="123">
         <f t="shared" si="5"/>
         <v>314458.08</v>
       </c>
-      <c r="P20" s="131">
+      <c r="P20" s="124">
         <f t="shared" si="6"/>
         <v>305558.08</v>
       </c>
-      <c r="Q20" s="27">
+      <c r="Q20" s="21">
         <f t="shared" si="7"/>
         <v>0.08</v>
       </c>
     </row>
     <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="125">
+      <c r="A21" s="118">
         <v>9</v>
       </c>
-      <c r="B21" s="125" t="s">
+      <c r="B21" s="118" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="125" t="s">
+      <c r="C21" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="D21" s="126" t="s">
+      <c r="D21" s="119" t="s">
         <v>72</v>
       </c>
-      <c r="E21" s="48">
+      <c r="E21" s="42">
         <v>6.6</v>
       </c>
-      <c r="F21" s="49">
+      <c r="F21" s="43">
         <v>198000.09</v>
       </c>
-      <c r="G21" s="246">
-        <f>F21</f>
+      <c r="G21" s="44">
+        <f t="shared" si="8"/>
         <v>198000.09</v>
       </c>
-      <c r="H21" s="51">
+      <c r="H21" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I21" s="51">
+      <c r="I21" s="45">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J21" s="97">
+      <c r="J21" s="90">
         <f t="shared" si="1"/>
         <v>198000</v>
       </c>
-      <c r="K21" s="97">
+      <c r="K21" s="90">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L21" s="133">
-        <v>0</v>
-      </c>
-      <c r="M21" s="147">
+      <c r="L21" s="126">
+        <v>0</v>
+      </c>
+      <c r="M21" s="140">
         <v>50000</v>
       </c>
-      <c r="N21" s="132">
+      <c r="N21" s="125">
         <f t="shared" si="4"/>
         <v>248000.09</v>
       </c>
-      <c r="O21" s="52">
+      <c r="O21" s="46">
         <f t="shared" si="5"/>
         <v>262880.09000000003</v>
       </c>
-      <c r="P21" s="53">
+      <c r="P21" s="47">
         <f t="shared" si="6"/>
         <v>255440.09</v>
       </c>
-      <c r="Q21" s="27">
+      <c r="Q21" s="21">
         <f t="shared" si="7"/>
         <v>0.09</v>
       </c>
     </row>
     <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="125">
+      <c r="A22" s="118">
         <v>10</v>
       </c>
-      <c r="B22" s="125" t="s">
+      <c r="B22" s="118" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="125" t="s">
+      <c r="C22" s="118" t="s">
         <v>45</v>
       </c>
-      <c r="D22" s="126" t="s">
+      <c r="D22" s="119" t="s">
         <v>70</v>
       </c>
-      <c r="E22" s="48">
+      <c r="E22" s="42">
         <v>5.4</v>
       </c>
-      <c r="F22" s="49">
+      <c r="F22" s="43">
         <v>4012.1</v>
       </c>
-      <c r="G22" s="246">
-        <f>F22</f>
+      <c r="G22" s="44">
+        <f t="shared" si="8"/>
         <v>4012.1</v>
       </c>
-      <c r="H22" s="51">
+      <c r="H22" s="45">
         <f>F22-G22</f>
         <v>0</v>
       </c>
-      <c r="I22" s="51">
+      <c r="I22" s="45">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J22" s="97">
+      <c r="J22" s="90">
         <f t="shared" si="1"/>
         <v>162000.00000000003</v>
       </c>
-      <c r="K22" s="97">
+      <c r="K22" s="90">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L22" s="133">
+      <c r="L22" s="126">
         <f>EDESUR!O13</f>
         <v>0</v>
       </c>
-      <c r="M22" s="147"/>
-      <c r="N22" s="132">
+      <c r="M22" s="140"/>
+      <c r="N22" s="125">
         <f t="shared" si="4"/>
         <v>162000.1</v>
       </c>
-      <c r="O22" s="52">
+      <c r="O22" s="46">
         <f t="shared" si="5"/>
         <v>171720.1</v>
       </c>
-      <c r="P22" s="53">
+      <c r="P22" s="47">
         <f t="shared" si="6"/>
         <v>166860.1</v>
       </c>
-      <c r="Q22" s="27">
+      <c r="Q22" s="21">
         <f t="shared" si="7"/>
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
     <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="40">
+      <c r="A23" s="34">
         <v>11</v>
       </c>
-      <c r="B23" s="40" t="s">
+      <c r="B23" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="C23" s="40" t="s">
+      <c r="C23" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="D23" s="41"/>
-      <c r="E23" s="48">
+      <c r="D23" s="35"/>
+      <c r="E23" s="42">
         <v>5.4</v>
       </c>
-      <c r="F23" s="49">
+      <c r="F23" s="43">
         <v>162000.10999999999</v>
       </c>
-      <c r="G23" s="246">
+      <c r="G23" s="44">
         <f>171070.33-G34</f>
         <v>162000.10999999999</v>
       </c>
-      <c r="H23" s="51">
+      <c r="H23" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I23" s="51">
+      <c r="I23" s="45">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J23" s="97">
+      <c r="J23" s="90">
         <f t="shared" si="1"/>
         <v>162000.00000000003</v>
       </c>
-      <c r="K23" s="97">
+      <c r="K23" s="90">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L23" s="133">
+      <c r="L23" s="126">
         <f>EDESUR!O14</f>
         <v>0</v>
       </c>
-      <c r="M23" s="147"/>
-      <c r="N23" s="132">
+      <c r="M23" s="140"/>
+      <c r="N23" s="125">
         <f t="shared" si="4"/>
         <v>162000.10999999999</v>
       </c>
-      <c r="O23" s="52">
+      <c r="O23" s="46">
         <f t="shared" si="5"/>
         <v>171720.11</v>
       </c>
-      <c r="P23" s="53">
+      <c r="P23" s="47">
         <f t="shared" si="6"/>
         <v>166860.10999999999</v>
       </c>
-      <c r="Q23" s="27">
+      <c r="Q23" s="21">
         <f t="shared" si="7"/>
         <v>0.10999999999999999</v>
       </c>
@@ -3860,859 +3854,853 @@
       </c>
     </row>
     <row r="24" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="40">
+      <c r="A24" s="34">
         <v>12</v>
       </c>
-      <c r="B24" s="40" t="s">
+      <c r="B24" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="C24" s="40" t="s">
+      <c r="C24" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="D24" s="41" t="s">
+      <c r="D24" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="E24" s="48">
+      <c r="E24" s="42">
         <v>6.6</v>
       </c>
-      <c r="F24" s="49">
+      <c r="F24" s="43">
         <v>198000.12</v>
       </c>
-      <c r="G24" s="246">
+      <c r="G24" s="44">
         <f>F24</f>
         <v>198000.12</v>
       </c>
-      <c r="H24" s="51">
+      <c r="H24" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I24" s="51">
+      <c r="I24" s="45">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J24" s="97">
+      <c r="J24" s="90">
         <f t="shared" si="1"/>
         <v>198000</v>
       </c>
-      <c r="K24" s="97">
+      <c r="K24" s="90">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L24" s="133">
+      <c r="L24" s="126">
         <f>EDESUR!O15</f>
         <v>0</v>
       </c>
-      <c r="M24" s="147"/>
-      <c r="N24" s="132">
+      <c r="M24" s="140"/>
+      <c r="N24" s="125">
         <f t="shared" si="4"/>
         <v>198000.12</v>
       </c>
-      <c r="O24" s="52">
+      <c r="O24" s="46">
         <f t="shared" si="5"/>
         <v>209880.12</v>
       </c>
-      <c r="P24" s="53">
+      <c r="P24" s="47">
         <f t="shared" si="6"/>
         <v>203940.12</v>
       </c>
-      <c r="Q24" s="27">
+      <c r="Q24" s="21">
         <f t="shared" si="7"/>
         <v>0.11999999999999998</v>
       </c>
     </row>
     <row r="25" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="40">
+      <c r="A25" s="34">
         <v>13</v>
       </c>
-      <c r="B25" s="40" t="s">
+      <c r="B25" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="C25" s="40" t="s">
+      <c r="C25" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="D25" s="41" t="s">
+      <c r="D25" s="35" t="s">
         <v>86</v>
       </c>
-      <c r="E25" s="48">
+      <c r="E25" s="42">
         <v>6.6</v>
       </c>
-      <c r="F25" s="49">
+      <c r="F25" s="43">
         <v>192168.13</v>
       </c>
-      <c r="G25" s="246">
+      <c r="G25" s="44">
         <v>197933.13</v>
       </c>
-      <c r="H25" s="51">
+      <c r="H25" s="45">
         <f t="shared" si="0"/>
         <v>-5765</v>
       </c>
-      <c r="I25" s="51">
+      <c r="I25" s="45">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J25" s="97">
+      <c r="J25" s="90">
         <f t="shared" si="1"/>
         <v>198000</v>
       </c>
-      <c r="K25" s="97">
+      <c r="K25" s="90">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L25" s="133">
+      <c r="L25" s="126">
         <f>EDESUR!O16</f>
         <v>0</v>
       </c>
-      <c r="M25" s="147"/>
-      <c r="N25" s="132">
+      <c r="M25" s="140"/>
+      <c r="N25" s="125">
         <f t="shared" si="4"/>
         <v>192235.13</v>
       </c>
-      <c r="O25" s="52">
+      <c r="O25" s="46">
         <f t="shared" si="5"/>
         <v>203769.13</v>
       </c>
-      <c r="P25" s="53">
+      <c r="P25" s="47">
         <f t="shared" si="6"/>
         <v>198002.13</v>
       </c>
-      <c r="Q25" s="27">
+      <c r="Q25" s="21">
         <f t="shared" si="7"/>
         <v>0.12999999999999998</v>
       </c>
     </row>
     <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="125">
+      <c r="A26" s="118">
         <v>14</v>
       </c>
-      <c r="B26" s="125" t="s">
+      <c r="B26" s="118" t="s">
         <v>52</v>
       </c>
-      <c r="C26" s="125" t="s">
+      <c r="C26" s="118" t="s">
         <v>53</v>
       </c>
-      <c r="D26" s="126"/>
-      <c r="E26" s="127">
+      <c r="D26" s="119"/>
+      <c r="E26" s="120">
         <v>5.4</v>
       </c>
-      <c r="F26" s="50">
+      <c r="F26" s="44">
         <v>162000.14000000001</v>
       </c>
-      <c r="G26" s="246">
-        <f t="shared" ref="G26:G33" si="8">F26</f>
+      <c r="G26" s="44">
+        <f t="shared" ref="G26:G32" si="9">F26</f>
         <v>162000.14000000001</v>
       </c>
-      <c r="H26" s="128">
+      <c r="H26" s="121">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I26" s="128">
+      <c r="I26" s="121">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J26" s="129">
+      <c r="J26" s="122">
         <f t="shared" si="1"/>
         <v>162000.00000000003</v>
       </c>
-      <c r="K26" s="129">
+      <c r="K26" s="122">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L26" s="133">
+      <c r="L26" s="126">
         <f>EDESUR!O17</f>
         <v>0</v>
       </c>
-      <c r="M26" s="148"/>
-      <c r="N26" s="132">
+      <c r="M26" s="141"/>
+      <c r="N26" s="125">
         <f t="shared" si="4"/>
         <v>162000.14000000001</v>
       </c>
-      <c r="O26" s="130">
+      <c r="O26" s="123">
         <f t="shared" si="5"/>
         <v>171720.14</v>
       </c>
-      <c r="P26" s="131">
+      <c r="P26" s="124">
         <f t="shared" si="6"/>
         <v>166860.14000000001</v>
       </c>
-      <c r="Q26" s="27">
+      <c r="Q26" s="21">
         <f t="shared" si="7"/>
         <v>0.13999999999999999</v>
       </c>
     </row>
     <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="40">
+      <c r="A27" s="34">
         <v>15</v>
       </c>
-      <c r="B27" s="40" t="s">
+      <c r="B27" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="C27" s="40" t="s">
+      <c r="C27" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="D27" s="41"/>
-      <c r="E27" s="48">
+      <c r="D27" s="35"/>
+      <c r="E27" s="42">
         <v>5.4</v>
       </c>
-      <c r="F27" s="49">
+      <c r="F27" s="43">
         <v>162000.15</v>
       </c>
-      <c r="G27" s="246">
-        <f t="shared" si="8"/>
+      <c r="G27" s="44">
+        <f t="shared" si="9"/>
         <v>162000.15</v>
       </c>
-      <c r="H27" s="51">
+      <c r="H27" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I27" s="51">
+      <c r="I27" s="45">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J27" s="97">
+      <c r="J27" s="90">
         <f t="shared" si="1"/>
         <v>162000.00000000003</v>
       </c>
-      <c r="K27" s="97">
+      <c r="K27" s="90">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L27" s="133">
+      <c r="L27" s="126">
         <f>EDESUR!O18</f>
         <v>0</v>
       </c>
-      <c r="M27" s="147"/>
-      <c r="N27" s="132">
+      <c r="M27" s="140"/>
+      <c r="N27" s="125">
         <f t="shared" si="4"/>
         <v>162000.15</v>
       </c>
-      <c r="O27" s="52">
+      <c r="O27" s="46">
         <f t="shared" si="5"/>
         <v>171720.15</v>
       </c>
-      <c r="P27" s="53">
+      <c r="P27" s="47">
         <f t="shared" si="6"/>
         <v>166860.15</v>
       </c>
-      <c r="Q27" s="27">
+      <c r="Q27" s="21">
         <f t="shared" si="7"/>
         <v>0.15</v>
       </c>
     </row>
     <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="125">
+      <c r="A28" s="118">
         <v>16</v>
       </c>
-      <c r="B28" s="125" t="s">
+      <c r="B28" s="118" t="s">
         <v>56</v>
       </c>
-      <c r="C28" s="125" t="s">
+      <c r="C28" s="118" t="s">
         <v>37</v>
       </c>
-      <c r="D28" s="40" t="s">
+      <c r="D28" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="E28" s="48">
+      <c r="E28" s="42">
         <v>0.7</v>
       </c>
-      <c r="F28" s="49">
+      <c r="F28" s="43">
         <v>21163.16</v>
       </c>
-      <c r="G28" s="246">
+      <c r="G28" s="44">
         <f>F28</f>
         <v>21163.16</v>
       </c>
-      <c r="H28" s="51">
+      <c r="H28" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I28" s="51">
+      <c r="I28" s="45">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J28" s="97">
+      <c r="J28" s="90">
         <f t="shared" si="1"/>
         <v>21000</v>
       </c>
-      <c r="K28" s="97">
+      <c r="K28" s="90">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L28" s="133">
+      <c r="L28" s="126">
         <f>EDESUR!O19</f>
         <v>0</v>
       </c>
-      <c r="M28" s="147"/>
-      <c r="N28" s="132">
+      <c r="M28" s="140"/>
+      <c r="N28" s="125">
         <f t="shared" si="4"/>
         <v>21000.16</v>
       </c>
-      <c r="O28" s="52">
+      <c r="O28" s="46">
         <f t="shared" si="5"/>
         <v>22260.16</v>
       </c>
-      <c r="P28" s="53">
+      <c r="P28" s="47">
         <f t="shared" si="6"/>
         <v>21630.16</v>
       </c>
-      <c r="Q28" s="27">
+      <c r="Q28" s="21">
         <f t="shared" si="7"/>
         <v>0.16</v>
       </c>
     </row>
     <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="125">
+      <c r="A29" s="118">
         <v>17</v>
       </c>
-      <c r="B29" s="125" t="s">
+      <c r="B29" s="118" t="s">
         <v>57</v>
       </c>
-      <c r="C29" s="125" t="s">
+      <c r="C29" s="118" t="s">
         <v>27</v>
       </c>
-      <c r="D29" s="41"/>
-      <c r="E29" s="48">
+      <c r="D29" s="35"/>
+      <c r="E29" s="42">
         <v>0.6</v>
       </c>
-      <c r="F29" s="50">
+      <c r="F29" s="44">
         <v>18140.169999999998</v>
       </c>
-      <c r="G29" s="246">
-        <f t="shared" si="8"/>
+      <c r="G29" s="44">
+        <f t="shared" si="9"/>
         <v>18140.169999999998</v>
       </c>
-      <c r="H29" s="51">
+      <c r="H29" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I29" s="51">
+      <c r="I29" s="45">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J29" s="97">
+      <c r="J29" s="90">
         <f t="shared" si="1"/>
         <v>18000</v>
       </c>
-      <c r="K29" s="97">
+      <c r="K29" s="90">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L29" s="133">
-        <v>0</v>
-      </c>
-      <c r="M29" s="147"/>
-      <c r="N29" s="132">
+      <c r="L29" s="126">
+        <v>0</v>
+      </c>
+      <c r="M29" s="140"/>
+      <c r="N29" s="125">
         <f t="shared" si="4"/>
         <v>18000.169999999998</v>
       </c>
-      <c r="O29" s="52">
+      <c r="O29" s="46">
         <f t="shared" si="5"/>
         <v>19080.169999999998</v>
       </c>
-      <c r="P29" s="53">
+      <c r="P29" s="47">
         <f t="shared" si="6"/>
         <v>18540.169999999998</v>
       </c>
-      <c r="Q29" s="27">
+      <c r="Q29" s="21">
         <f t="shared" si="7"/>
         <v>0.17</v>
       </c>
     </row>
     <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="40">
+      <c r="A30" s="34">
         <v>18</v>
       </c>
-      <c r="B30" s="40" t="s">
+      <c r="B30" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="C30" s="40" t="s">
+      <c r="C30" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="D30" s="83"/>
-      <c r="E30" s="48">
+      <c r="D30" s="77"/>
+      <c r="E30" s="42">
         <v>0.6</v>
       </c>
-      <c r="F30" s="49">
+      <c r="F30" s="43">
         <v>18140.18</v>
       </c>
-      <c r="G30" s="246">
+      <c r="G30" s="44">
         <f>F30</f>
         <v>18140.18</v>
       </c>
-      <c r="H30" s="51">
+      <c r="H30" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I30" s="51">
+      <c r="I30" s="45">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J30" s="97">
+      <c r="J30" s="90">
         <f t="shared" si="1"/>
         <v>18000</v>
       </c>
-      <c r="K30" s="97">
+      <c r="K30" s="90">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L30" s="133">
+      <c r="L30" s="126">
         <f>EDESUR!O21</f>
         <v>0</v>
       </c>
-      <c r="M30" s="147"/>
-      <c r="N30" s="132">
+      <c r="M30" s="140"/>
+      <c r="N30" s="125">
         <f t="shared" si="4"/>
         <v>18000.18</v>
       </c>
-      <c r="O30" s="52">
+      <c r="O30" s="46">
         <f t="shared" si="5"/>
         <v>19080.18</v>
       </c>
-      <c r="P30" s="53">
+      <c r="P30" s="47">
         <f t="shared" si="6"/>
         <v>18540.18</v>
       </c>
-      <c r="Q30" s="27">
+      <c r="Q30" s="21">
         <f t="shared" si="7"/>
         <v>0.18000000000000002</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A31" s="125">
+      <c r="A31" s="118">
         <v>19</v>
       </c>
-      <c r="B31" s="125" t="s">
+      <c r="B31" s="118" t="s">
         <v>59</v>
       </c>
-      <c r="C31" s="125" t="s">
+      <c r="C31" s="118" t="s">
         <v>49</v>
       </c>
-      <c r="D31" s="126"/>
-      <c r="E31" s="127">
+      <c r="D31" s="119"/>
+      <c r="E31" s="120">
         <v>0.6</v>
       </c>
-      <c r="F31" s="50">
+      <c r="F31" s="44">
         <v>18140.189999999999</v>
       </c>
-      <c r="G31" s="246">
-        <f t="shared" si="8"/>
+      <c r="G31" s="44">
+        <f t="shared" si="9"/>
         <v>18140.189999999999</v>
       </c>
-      <c r="H31" s="128">
+      <c r="H31" s="121">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I31" s="128">
+      <c r="I31" s="121">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J31" s="129">
+      <c r="J31" s="122">
         <f t="shared" si="1"/>
         <v>18000</v>
       </c>
-      <c r="K31" s="129">
+      <c r="K31" s="122">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L31" s="133">
+      <c r="L31" s="126">
         <f>EDESUR!O22</f>
         <v>0</v>
       </c>
-      <c r="M31" s="148"/>
-      <c r="N31" s="132">
+      <c r="M31" s="141"/>
+      <c r="N31" s="125">
         <f t="shared" si="4"/>
         <v>18000.189999999999</v>
       </c>
-      <c r="O31" s="130"/>
-      <c r="P31" s="131">
+      <c r="O31" s="123"/>
+      <c r="P31" s="124">
         <f t="shared" si="6"/>
         <v>18540.189999999999</v>
       </c>
-      <c r="Q31" s="27">
+      <c r="Q31" s="21">
         <f>Q30+0.01</f>
         <v>0.19000000000000003</v>
       </c>
     </row>
     <row r="32" spans="1:18" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A32" s="54">
+      <c r="A32" s="48">
         <v>20</v>
       </c>
-      <c r="B32" s="54" t="s">
+      <c r="B32" s="48" t="s">
         <v>60</v>
       </c>
-      <c r="C32" s="40" t="s">
+      <c r="C32" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="D32" s="41" t="s">
+      <c r="D32" s="35" t="s">
         <v>121</v>
       </c>
-      <c r="E32" s="48">
+      <c r="E32" s="42">
         <v>0.6</v>
       </c>
-      <c r="F32" s="56">
+      <c r="F32" s="50">
         <v>18140.2</v>
       </c>
-      <c r="G32" s="246">
-        <f t="shared" si="8"/>
+      <c r="G32" s="44">
+        <f t="shared" si="9"/>
         <v>18140.2</v>
       </c>
-      <c r="H32" s="51">
+      <c r="H32" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I32" s="51">
+      <c r="I32" s="45">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J32" s="97">
+      <c r="J32" s="90">
         <f t="shared" si="1"/>
         <v>18000</v>
       </c>
-      <c r="K32" s="97">
+      <c r="K32" s="90">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L32" s="133">
+      <c r="L32" s="126">
         <f>EDESUR!O23</f>
         <v>0</v>
       </c>
-      <c r="M32" s="147"/>
-      <c r="N32" s="132">
+      <c r="M32" s="140"/>
+      <c r="N32" s="125">
         <f t="shared" si="4"/>
         <v>18000.2</v>
       </c>
-      <c r="O32" s="52"/>
-      <c r="P32" s="53">
+      <c r="O32" s="46"/>
+      <c r="P32" s="47">
         <f t="shared" si="6"/>
         <v>18540.2</v>
       </c>
-      <c r="Q32" s="27">
-        <f t="shared" ref="Q32:Q35" si="9">Q31+0.01</f>
+      <c r="Q32" s="21">
+        <f t="shared" ref="Q32:Q35" si="10">Q31+0.01</f>
         <v>0.20000000000000004</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A33" s="54">
+      <c r="A33" s="48">
         <v>21</v>
       </c>
-      <c r="B33" s="54" t="s">
+      <c r="B33" s="48" t="s">
         <v>61</v>
       </c>
-      <c r="C33" s="42" t="s">
+      <c r="C33" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="D33" s="41" t="s">
+      <c r="D33" s="35" t="s">
         <v>70</v>
       </c>
-      <c r="E33" s="48">
+      <c r="E33" s="42">
         <v>0.3</v>
       </c>
-      <c r="F33" s="56">
+      <c r="F33" s="50">
         <v>9070.2099999999991</v>
       </c>
-      <c r="G33" s="246">
+      <c r="G33" s="44">
         <f>F33</f>
         <v>9070.2099999999991</v>
       </c>
-      <c r="H33" s="51">
+      <c r="H33" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I33" s="51">
+      <c r="I33" s="45">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J33" s="97">
+      <c r="J33" s="90">
         <f t="shared" si="1"/>
         <v>9000</v>
       </c>
-      <c r="K33" s="97">
+      <c r="K33" s="90">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L33" s="133">
+      <c r="L33" s="126">
         <f>EDESUR!O24</f>
         <v>0</v>
       </c>
-      <c r="M33" s="147"/>
-      <c r="N33" s="132">
+      <c r="M33" s="140"/>
+      <c r="N33" s="125">
         <f t="shared" si="4"/>
         <v>9000.2099999999991</v>
       </c>
-      <c r="O33" s="52"/>
-      <c r="P33" s="53">
+      <c r="O33" s="46"/>
+      <c r="P33" s="47">
         <f t="shared" si="6"/>
         <v>9270.2099999999991</v>
       </c>
-      <c r="Q33" s="27">
-        <f t="shared" si="9"/>
+      <c r="Q33" s="21">
+        <f t="shared" si="10"/>
         <v>0.21000000000000005</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A34" s="55">
+      <c r="A34" s="49">
         <v>22</v>
       </c>
-      <c r="B34" s="55" t="s">
+      <c r="B34" s="49" t="s">
         <v>62</v>
       </c>
-      <c r="C34" s="40" t="s">
+      <c r="C34" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="D34" s="41"/>
-      <c r="E34" s="48">
+      <c r="D34" s="35"/>
+      <c r="E34" s="42">
         <v>0.3</v>
       </c>
-      <c r="F34" s="56">
+      <c r="F34" s="50">
         <v>9070.2199999999993</v>
       </c>
-      <c r="G34" s="247">
-        <f t="shared" ref="G34" si="10">F34</f>
+      <c r="G34" s="239">
+        <f t="shared" ref="G34" si="11">F34</f>
         <v>9070.2199999999993</v>
       </c>
-      <c r="H34" s="51">
+      <c r="H34" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I34" s="51">
+      <c r="I34" s="45">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J34" s="97">
+      <c r="J34" s="90">
         <f t="shared" si="1"/>
         <v>9000</v>
       </c>
-      <c r="K34" s="97">
+      <c r="K34" s="90">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L34" s="133">
+      <c r="L34" s="126">
         <f>EDESUR!O25</f>
         <v>0</v>
       </c>
-      <c r="M34" s="147"/>
-      <c r="N34" s="132">
+      <c r="M34" s="140"/>
+      <c r="N34" s="125">
         <f t="shared" si="4"/>
         <v>9000.2199999999993</v>
       </c>
-      <c r="O34" s="52"/>
-      <c r="P34" s="53">
+      <c r="O34" s="46"/>
+      <c r="P34" s="47">
         <f t="shared" si="6"/>
         <v>9270.2199999999993</v>
       </c>
-      <c r="Q34" s="27">
-        <f t="shared" si="9"/>
+      <c r="Q34" s="21">
+        <f t="shared" si="10"/>
         <v>0.22000000000000006</v>
       </c>
     </row>
     <row r="35" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="40">
+      <c r="A35" s="34">
         <v>23</v>
       </c>
-      <c r="B35" s="57" t="s">
+      <c r="B35" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="C35" s="57" t="s">
+      <c r="C35" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="D35" s="41" t="s">
+      <c r="D35" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="E35" s="48">
+      <c r="E35" s="42">
         <v>0.3</v>
       </c>
-      <c r="F35" s="56">
+      <c r="F35" s="50">
         <v>9070.23</v>
       </c>
-      <c r="G35" s="246">
+      <c r="G35" s="44">
         <f>F35</f>
         <v>9070.23</v>
       </c>
-      <c r="H35" s="51">
+      <c r="H35" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I35" s="51">
+      <c r="I35" s="45">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J35" s="97">
+      <c r="J35" s="90">
         <f t="shared" si="1"/>
         <v>9000</v>
       </c>
-      <c r="K35" s="97">
+      <c r="K35" s="90">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L35" s="133">
+      <c r="L35" s="126">
         <f>EDESUR!O26</f>
         <v>0</v>
       </c>
-      <c r="M35" s="147"/>
-      <c r="N35" s="132">
+      <c r="M35" s="140"/>
+      <c r="N35" s="125">
         <f t="shared" si="4"/>
         <v>9000.23</v>
       </c>
-      <c r="O35" s="58"/>
-      <c r="P35" s="53">
+      <c r="O35" s="52"/>
+      <c r="P35" s="47">
         <f t="shared" si="6"/>
         <v>9270.23</v>
       </c>
-      <c r="Q35" s="27">
-        <f t="shared" si="9"/>
+      <c r="Q35" s="21">
+        <f t="shared" si="10"/>
         <v>0.23000000000000007</v>
       </c>
     </row>
     <row r="36" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="59"/>
-      <c r="B36" s="59"/>
-      <c r="C36" s="60"/>
-      <c r="D36" s="60"/>
-      <c r="E36" s="103">
+      <c r="A36" s="53"/>
+      <c r="B36" s="53"/>
+      <c r="C36" s="54"/>
+      <c r="D36" s="54"/>
+      <c r="E36" s="96">
         <f>SUM(E13:E35)</f>
         <v>99.999999999999986</v>
       </c>
-      <c r="F36" s="34">
+      <c r="F36" s="28">
         <f>SUM(F13:F35)</f>
         <v>3054299.7600000012</v>
       </c>
-      <c r="G36" s="38">
+      <c r="G36" s="240">
         <f>SUM(G13:G35)</f>
         <v>3060391.1300000008</v>
       </c>
-      <c r="H36" s="38">
+      <c r="H36" s="32">
         <f>SUM(H13:H35)</f>
         <v>-6091.3699999999662</v>
       </c>
-      <c r="I36" s="38">
-        <f t="shared" ref="I36:O36" si="11">SUM(I13:I35)</f>
+      <c r="I36" s="32">
+        <f t="shared" ref="I36:O36" si="12">SUM(I13:I35)</f>
         <v>1.8300000000454019E-2</v>
       </c>
-      <c r="J36" s="86">
-        <f t="shared" si="11"/>
+      <c r="J36" s="80">
+        <f t="shared" si="12"/>
         <v>3000000</v>
       </c>
-      <c r="K36" s="38">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L36" s="61">
+      <c r="K36" s="32">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="L36" s="55">
         <f>SUM(L13:L35)</f>
         <v>223921.50565122702</v>
       </c>
-      <c r="M36" s="61"/>
-      <c r="N36" s="61">
+      <c r="M36" s="55"/>
+      <c r="N36" s="55">
         <f>SUM(N13:N35)</f>
         <v>3267831.7600000007</v>
       </c>
-      <c r="O36" s="61">
-        <f t="shared" si="11"/>
+      <c r="O36" s="55">
+        <f t="shared" si="12"/>
         <v>3397120.7100000004</v>
       </c>
-      <c r="P36" s="61">
+      <c r="P36" s="55">
         <f>SUM(P13:P35)</f>
         <v>3365866.7600000007</v>
       </c>
     </row>
     <row r="37" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C37" s="33"/>
-      <c r="D37" s="33"/>
+      <c r="C37" s="27"/>
+      <c r="D37" s="27"/>
     </row>
     <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="39" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C39" s="209" t="str">
+      <c r="C39" s="194" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. PORFAVOR RESPETAR LOS CENTAVOS AL ABONAR.</v>
       </c>
-      <c r="D39" s="209"/>
-      <c r="E39" s="209"/>
-      <c r="F39" s="209"/>
-      <c r="G39" s="209"/>
-      <c r="H39" s="209"/>
-      <c r="I39" s="209"/>
-      <c r="J39" s="209"/>
-      <c r="K39" s="209"/>
-      <c r="L39" s="209"/>
-      <c r="M39" s="209"/>
-      <c r="N39" s="209"/>
+      <c r="D39" s="194"/>
+      <c r="E39" s="194"/>
+      <c r="F39" s="194"/>
+      <c r="G39" s="194"/>
+      <c r="H39" s="194"/>
+      <c r="I39" s="194"/>
+      <c r="J39" s="194"/>
+      <c r="K39" s="194"/>
+      <c r="L39" s="194"/>
+      <c r="M39" s="194"/>
+      <c r="N39" s="194"/>
     </row>
     <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C40" s="209"/>
-      <c r="D40" s="209"/>
-      <c r="E40" s="209"/>
-      <c r="F40" s="209"/>
-      <c r="G40" s="209"/>
-      <c r="H40" s="209"/>
-      <c r="I40" s="209"/>
-      <c r="J40" s="209"/>
-      <c r="K40" s="209"/>
-      <c r="L40" s="209"/>
-      <c r="M40" s="209"/>
-      <c r="N40" s="209"/>
+      <c r="C40" s="194"/>
+      <c r="D40" s="194"/>
+      <c r="E40" s="194"/>
+      <c r="F40" s="194"/>
+      <c r="G40" s="194"/>
+      <c r="H40" s="194"/>
+      <c r="I40" s="194"/>
+      <c r="J40" s="194"/>
+      <c r="K40" s="194"/>
+      <c r="L40" s="194"/>
+      <c r="M40" s="194"/>
+      <c r="N40" s="194"/>
     </row>
     <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C41" s="209"/>
-      <c r="D41" s="209"/>
-      <c r="E41" s="209"/>
-      <c r="F41" s="209"/>
-      <c r="G41" s="209"/>
-      <c r="H41" s="209"/>
-      <c r="I41" s="209"/>
-      <c r="J41" s="209"/>
-      <c r="K41" s="209"/>
-      <c r="L41" s="209"/>
-      <c r="M41" s="209"/>
-      <c r="N41" s="209"/>
+      <c r="C41" s="194"/>
+      <c r="D41" s="194"/>
+      <c r="E41" s="194"/>
+      <c r="F41" s="194"/>
+      <c r="G41" s="194"/>
+      <c r="H41" s="194"/>
+      <c r="I41" s="194"/>
+      <c r="J41" s="194"/>
+      <c r="K41" s="194"/>
+      <c r="L41" s="194"/>
+      <c r="M41" s="194"/>
+      <c r="N41" s="194"/>
     </row>
     <row r="42" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C42" s="209"/>
-      <c r="D42" s="209"/>
-      <c r="E42" s="209"/>
-      <c r="F42" s="209"/>
-      <c r="G42" s="209"/>
-      <c r="H42" s="209"/>
-      <c r="I42" s="209"/>
-      <c r="J42" s="209"/>
-      <c r="K42" s="209"/>
-      <c r="L42" s="209"/>
-      <c r="M42" s="209"/>
-      <c r="N42" s="209"/>
+      <c r="C42" s="194"/>
+      <c r="D42" s="194"/>
+      <c r="E42" s="194"/>
+      <c r="F42" s="194"/>
+      <c r="G42" s="194"/>
+      <c r="H42" s="194"/>
+      <c r="I42" s="194"/>
+      <c r="J42" s="194"/>
+      <c r="K42" s="194"/>
+      <c r="L42" s="194"/>
+      <c r="M42" s="194"/>
+      <c r="N42" s="194"/>
     </row>
     <row r="43" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C43" s="209"/>
-      <c r="D43" s="209"/>
-      <c r="E43" s="209"/>
-      <c r="F43" s="209"/>
-      <c r="G43" s="209"/>
-      <c r="H43" s="209"/>
-      <c r="I43" s="209"/>
-      <c r="J43" s="209"/>
-      <c r="K43" s="209"/>
-      <c r="L43" s="209"/>
-      <c r="M43" s="209"/>
-      <c r="N43" s="209"/>
+      <c r="C43" s="194"/>
+      <c r="D43" s="194"/>
+      <c r="E43" s="194"/>
+      <c r="F43" s="194"/>
+      <c r="G43" s="194"/>
+      <c r="H43" s="194"/>
+      <c r="I43" s="194"/>
+      <c r="J43" s="194"/>
+      <c r="K43" s="194"/>
+      <c r="L43" s="194"/>
+      <c r="M43" s="194"/>
+      <c r="N43" s="194"/>
     </row>
     <row r="44" spans="1:17" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C44" s="209"/>
-      <c r="D44" s="209"/>
-      <c r="E44" s="209"/>
-      <c r="F44" s="209"/>
-      <c r="G44" s="209"/>
-      <c r="H44" s="209"/>
-      <c r="I44" s="209"/>
-      <c r="J44" s="209"/>
-      <c r="K44" s="209"/>
-      <c r="L44" s="209"/>
-      <c r="M44" s="209"/>
-      <c r="N44" s="209"/>
+      <c r="C44" s="194"/>
+      <c r="D44" s="194"/>
+      <c r="E44" s="194"/>
+      <c r="F44" s="194"/>
+      <c r="G44" s="194"/>
+      <c r="H44" s="194"/>
+      <c r="I44" s="194"/>
+      <c r="J44" s="194"/>
+      <c r="K44" s="194"/>
+      <c r="L44" s="194"/>
+      <c r="M44" s="194"/>
+      <c r="N44" s="194"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="C39:N44"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="M11:M12"/>
     <mergeCell ref="E1:N1"/>
     <mergeCell ref="I11:I12"/>
     <mergeCell ref="F11:F12"/>
@@ -4726,6 +4714,12 @@
     <mergeCell ref="A9:P9"/>
     <mergeCell ref="A10:P10"/>
     <mergeCell ref="L11:L12"/>
+    <mergeCell ref="C39:N44"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="M11:M12"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" orientation="landscape" r:id="rId1"/>
@@ -4747,631 +4741,631 @@
     <col min="8" max="8" width="10.5703125" customWidth="1"/>
     <col min="9" max="9" width="14.28515625" customWidth="1"/>
     <col min="10" max="10" width="1.85546875" customWidth="1"/>
-    <col min="11" max="11" width="19.5703125" style="108" customWidth="1"/>
+    <col min="11" max="11" width="19.5703125" style="101" customWidth="1"/>
     <col min="12" max="12" width="2.140625" customWidth="1"/>
-    <col min="13" max="13" width="19.7109375" style="109" customWidth="1"/>
+    <col min="13" max="13" width="19.7109375" style="102" customWidth="1"/>
     <col min="14" max="14" width="2" customWidth="1"/>
-    <col min="15" max="15" width="15.28515625" style="175" customWidth="1"/>
+    <col min="15" max="15" width="15.28515625" style="167" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="D2" s="238" t="s">
+      <c r="D2" s="229" t="s">
         <v>135</v>
       </c>
-      <c r="E2" s="238"/>
-      <c r="F2" s="238"/>
+      <c r="E2" s="229"/>
+      <c r="F2" s="229"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="239" t="s">
+      <c r="H2" s="230" t="s">
         <v>136</v>
       </c>
-      <c r="I2" s="240"/>
+      <c r="I2" s="231"/>
       <c r="J2" s="1"/>
-      <c r="K2" s="198" t="s">
+      <c r="K2" s="190" t="s">
         <v>137</v>
       </c>
-      <c r="M2" s="185" t="s">
+      <c r="M2" s="177" t="s">
         <v>138</v>
       </c>
-      <c r="O2" s="198" t="s">
+      <c r="O2" s="190" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B3" s="106" t="s">
+      <c r="B3" s="99" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="106" t="s">
+      <c r="C3" s="99" t="s">
         <v>80</v>
       </c>
-      <c r="D3" s="106" t="s">
+      <c r="D3" s="99" t="s">
         <v>126</v>
       </c>
-      <c r="E3" s="106" t="s">
+      <c r="E3" s="99" t="s">
         <v>127</v>
       </c>
-      <c r="F3" s="198" t="s">
+      <c r="F3" s="190" t="s">
         <v>128</v>
       </c>
-      <c r="H3" s="106" t="s">
+      <c r="H3" s="99" t="s">
         <v>140</v>
       </c>
-      <c r="I3" s="170" t="s">
+      <c r="I3" s="162" t="s">
         <v>129</v>
       </c>
-      <c r="K3" s="106"/>
-      <c r="M3" s="107"/>
-      <c r="O3" s="198"/>
+      <c r="K3" s="99"/>
+      <c r="M3" s="100"/>
+      <c r="O3" s="190"/>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B4" s="186">
+      <c r="B4" s="178">
         <v>1</v>
       </c>
-      <c r="C4" s="186" t="s">
+      <c r="C4" s="178" t="s">
         <v>81</v>
       </c>
-      <c r="D4" s="187">
-        <v>0</v>
-      </c>
-      <c r="E4" s="188">
-        <v>0</v>
-      </c>
-      <c r="F4" s="189">
-        <v>0</v>
-      </c>
-      <c r="H4" s="171">
+      <c r="D4" s="179">
+        <v>0</v>
+      </c>
+      <c r="E4" s="180">
+        <v>0</v>
+      </c>
+      <c r="F4" s="181">
+        <v>0</v>
+      </c>
+      <c r="H4" s="163">
         <v>0.12</v>
       </c>
-      <c r="I4" s="190">
+      <c r="I4" s="182">
         <v>5711.4946104294486</v>
       </c>
-      <c r="K4" s="149">
+      <c r="K4" s="142">
         <f>I4+F4</f>
         <v>5711.4946104294486</v>
       </c>
-      <c r="M4" s="191">
+      <c r="M4" s="183">
         <f>K4</f>
         <v>5711.4946104294486</v>
       </c>
-      <c r="O4" s="149">
+      <c r="O4" s="142">
         <f>K4-M4</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B5" s="106">
+      <c r="B5" s="99">
         <v>1</v>
       </c>
-      <c r="C5" s="106" t="s">
+      <c r="C5" s="99" t="s">
         <v>82</v>
       </c>
-      <c r="D5" s="173">
+      <c r="D5" s="165">
         <v>300.19999999999982</v>
       </c>
-      <c r="E5" s="188">
+      <c r="E5" s="180">
         <v>0.56112149532710243</v>
       </c>
-      <c r="F5" s="189">
+      <c r="F5" s="181">
         <v>122121.84345092018</v>
       </c>
-      <c r="H5" s="172">
+      <c r="H5" s="164">
         <v>6.6000000000000003E-2</v>
       </c>
-      <c r="I5" s="190">
+      <c r="I5" s="182">
         <v>3141.322035736197</v>
       </c>
-      <c r="K5" s="149">
+      <c r="K5" s="142">
         <f t="shared" ref="K5:K18" si="0">I5+F5</f>
         <v>125263.16548665638</v>
       </c>
-      <c r="M5" s="191">
-        <v>0</v>
-      </c>
-      <c r="O5" s="149">
+      <c r="M5" s="183">
+        <v>0</v>
+      </c>
+      <c r="O5" s="142">
         <f t="shared" ref="O5:O18" si="1">K5-M5</f>
         <v>125263.16548665638</v>
       </c>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B6" s="186">
+      <c r="B6" s="178">
         <v>1</v>
       </c>
-      <c r="C6" s="186" t="s">
+      <c r="C6" s="178" t="s">
         <v>83</v>
       </c>
-      <c r="D6" s="187">
-        <v>0</v>
-      </c>
-      <c r="E6" s="188">
-        <v>0</v>
-      </c>
-      <c r="F6" s="189">
-        <v>0</v>
-      </c>
-      <c r="H6" s="172">
+      <c r="D6" s="179">
+        <v>0</v>
+      </c>
+      <c r="E6" s="180">
+        <v>0</v>
+      </c>
+      <c r="F6" s="181">
+        <v>0</v>
+      </c>
+      <c r="H6" s="164">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="I6" s="190">
+      <c r="I6" s="182">
         <v>2570.172574693252</v>
       </c>
-      <c r="K6" s="149">
+      <c r="K6" s="142">
         <f t="shared" si="0"/>
         <v>2570.172574693252</v>
       </c>
-      <c r="M6" s="191">
+      <c r="M6" s="183">
         <f t="shared" ref="M6:M18" si="2">K6</f>
         <v>2570.172574693252</v>
       </c>
-      <c r="O6" s="149">
+      <c r="O6" s="142">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B7" s="186">
+      <c r="B7" s="178">
         <v>2</v>
       </c>
-      <c r="C7" s="186" t="s">
+      <c r="C7" s="178" t="s">
         <v>81</v>
       </c>
-      <c r="D7" s="187">
-        <v>0</v>
-      </c>
-      <c r="E7" s="188">
-        <v>0</v>
-      </c>
-      <c r="F7" s="189">
-        <v>0</v>
-      </c>
-      <c r="H7" s="172">
+      <c r="D7" s="179">
+        <v>0</v>
+      </c>
+      <c r="E7" s="180">
+        <v>0</v>
+      </c>
+      <c r="F7" s="181">
+        <v>0</v>
+      </c>
+      <c r="H7" s="164">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="I7" s="190">
+      <c r="I7" s="182">
         <v>2570.172574693252</v>
       </c>
-      <c r="K7" s="149">
+      <c r="K7" s="142">
         <f t="shared" si="0"/>
         <v>2570.172574693252</v>
       </c>
-      <c r="M7" s="191">
+      <c r="M7" s="183">
         <f t="shared" si="2"/>
         <v>2570.172574693252</v>
       </c>
-      <c r="O7" s="149">
+      <c r="O7" s="142">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B8" s="186">
+      <c r="B8" s="178">
         <v>2</v>
       </c>
-      <c r="C8" s="186" t="s">
+      <c r="C8" s="178" t="s">
         <v>84</v>
       </c>
-      <c r="D8" s="187">
-        <v>0</v>
-      </c>
-      <c r="E8" s="188">
-        <v>0</v>
-      </c>
-      <c r="F8" s="189">
-        <v>0</v>
-      </c>
-      <c r="H8" s="172">
+      <c r="D8" s="179">
+        <v>0</v>
+      </c>
+      <c r="E8" s="180">
+        <v>0</v>
+      </c>
+      <c r="F8" s="181">
+        <v>0</v>
+      </c>
+      <c r="H8" s="164">
         <v>6.6000000000000003E-2</v>
       </c>
-      <c r="I8" s="190">
+      <c r="I8" s="182">
         <v>3141.322035736197</v>
       </c>
-      <c r="K8" s="149">
+      <c r="K8" s="142">
         <f t="shared" si="0"/>
         <v>3141.322035736197</v>
       </c>
-      <c r="M8" s="191">
+      <c r="M8" s="183">
         <f t="shared" si="2"/>
         <v>3141.322035736197</v>
       </c>
-      <c r="O8" s="149">
+      <c r="O8" s="142">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B9" s="186">
+      <c r="B9" s="178">
         <v>2</v>
       </c>
-      <c r="C9" s="186" t="s">
+      <c r="C9" s="178" t="s">
         <v>82</v>
       </c>
-      <c r="D9" s="187">
-        <v>0</v>
-      </c>
-      <c r="E9" s="188">
-        <v>0</v>
-      </c>
-      <c r="F9" s="189">
-        <v>0</v>
-      </c>
-      <c r="H9" s="172">
+      <c r="D9" s="179">
+        <v>0</v>
+      </c>
+      <c r="E9" s="180">
+        <v>0</v>
+      </c>
+      <c r="F9" s="181">
+        <v>0</v>
+      </c>
+      <c r="H9" s="164">
         <v>6.6000000000000003E-2</v>
       </c>
-      <c r="I9" s="190">
+      <c r="I9" s="182">
         <v>3141.322035736197</v>
       </c>
-      <c r="K9" s="149">
+      <c r="K9" s="142">
         <f t="shared" si="0"/>
         <v>3141.322035736197</v>
       </c>
-      <c r="M9" s="191">
+      <c r="M9" s="183">
         <f t="shared" si="2"/>
         <v>3141.322035736197</v>
       </c>
-      <c r="O9" s="149">
+      <c r="O9" s="142">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B10" s="186">
+      <c r="B10" s="178">
         <v>2</v>
       </c>
-      <c r="C10" s="186" t="s">
+      <c r="C10" s="178" t="s">
         <v>83</v>
       </c>
-      <c r="D10" s="187">
-        <v>0</v>
-      </c>
-      <c r="E10" s="188">
-        <v>0</v>
-      </c>
-      <c r="F10" s="192">
-        <v>0</v>
-      </c>
-      <c r="H10" s="172">
+      <c r="D10" s="179">
+        <v>0</v>
+      </c>
+      <c r="E10" s="180">
+        <v>0</v>
+      </c>
+      <c r="F10" s="184">
+        <v>0</v>
+      </c>
+      <c r="H10" s="164">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="I10" s="190">
+      <c r="I10" s="182">
         <v>2570.172574693252</v>
       </c>
-      <c r="K10" s="149">
+      <c r="K10" s="142">
         <f t="shared" si="0"/>
         <v>2570.172574693252</v>
       </c>
-      <c r="M10" s="191">
+      <c r="M10" s="183">
         <f t="shared" si="2"/>
         <v>2570.172574693252</v>
       </c>
-      <c r="O10" s="149">
+      <c r="O10" s="142">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B11" s="186">
+      <c r="B11" s="178">
         <v>3</v>
       </c>
-      <c r="C11" s="186" t="s">
+      <c r="C11" s="178" t="s">
         <v>81</v>
       </c>
-      <c r="D11" s="187">
-        <v>0</v>
-      </c>
-      <c r="E11" s="188">
-        <v>0</v>
-      </c>
-      <c r="F11" s="189">
-        <v>0</v>
-      </c>
-      <c r="H11" s="172">
+      <c r="D11" s="179">
+        <v>0</v>
+      </c>
+      <c r="E11" s="180">
+        <v>0</v>
+      </c>
+      <c r="F11" s="181">
+        <v>0</v>
+      </c>
+      <c r="H11" s="164">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="I11" s="190">
+      <c r="I11" s="182">
         <v>2570.172574693252</v>
       </c>
-      <c r="K11" s="149">
+      <c r="K11" s="142">
         <f t="shared" si="0"/>
         <v>2570.172574693252</v>
       </c>
-      <c r="M11" s="191">
+      <c r="M11" s="183">
         <f t="shared" si="2"/>
         <v>2570.172574693252</v>
       </c>
-      <c r="O11" s="149">
+      <c r="O11" s="142">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B12" s="106">
+      <c r="B12" s="99">
         <v>3</v>
       </c>
-      <c r="C12" s="106" t="s">
+      <c r="C12" s="99" t="s">
         <v>84</v>
       </c>
-      <c r="D12" s="173">
+      <c r="D12" s="165">
         <v>234.80000000000018</v>
       </c>
-      <c r="E12" s="188">
+      <c r="E12" s="180">
         <v>0.43887850467289752</v>
       </c>
-      <c r="F12" s="189">
+      <c r="F12" s="181">
         <v>95517.018128834432</v>
       </c>
-      <c r="H12" s="172">
+      <c r="H12" s="164">
         <v>6.6000000000000003E-2</v>
       </c>
-      <c r="I12" s="190">
+      <c r="I12" s="182">
         <v>3141.322035736197</v>
       </c>
-      <c r="K12" s="149">
+      <c r="K12" s="142">
         <f t="shared" si="0"/>
         <v>98658.340164570633</v>
       </c>
-      <c r="M12" s="191">
-        <v>0</v>
-      </c>
-      <c r="O12" s="149">
+      <c r="M12" s="183">
+        <v>0</v>
+      </c>
+      <c r="O12" s="142">
         <f t="shared" si="1"/>
         <v>98658.340164570633</v>
       </c>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B13" s="186">
+      <c r="B13" s="178">
         <v>3</v>
       </c>
-      <c r="C13" s="186" t="s">
+      <c r="C13" s="178" t="s">
         <v>82</v>
       </c>
-      <c r="D13" s="187">
-        <v>0</v>
-      </c>
-      <c r="E13" s="188">
-        <v>0</v>
-      </c>
-      <c r="F13" s="189">
-        <v>0</v>
-      </c>
-      <c r="H13" s="172">
+      <c r="D13" s="179">
+        <v>0</v>
+      </c>
+      <c r="E13" s="180">
+        <v>0</v>
+      </c>
+      <c r="F13" s="181">
+        <v>0</v>
+      </c>
+      <c r="H13" s="164">
         <v>6.6000000000000003E-2</v>
       </c>
-      <c r="I13" s="190">
+      <c r="I13" s="182">
         <v>3141.322035736197</v>
       </c>
-      <c r="K13" s="149">
+      <c r="K13" s="142">
         <f t="shared" si="0"/>
         <v>3141.322035736197</v>
       </c>
-      <c r="M13" s="191">
+      <c r="M13" s="183">
         <f t="shared" si="2"/>
         <v>3141.322035736197</v>
       </c>
-      <c r="O13" s="149">
+      <c r="O13" s="142">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B14" s="186">
+      <c r="B14" s="178">
         <v>3</v>
       </c>
-      <c r="C14" s="186" t="s">
+      <c r="C14" s="178" t="s">
         <v>83</v>
       </c>
-      <c r="D14" s="187">
-        <v>0</v>
-      </c>
-      <c r="E14" s="188">
-        <v>0</v>
-      </c>
-      <c r="F14" s="189">
-        <v>0</v>
-      </c>
-      <c r="H14" s="172">
+      <c r="D14" s="179">
+        <v>0</v>
+      </c>
+      <c r="E14" s="180">
+        <v>0</v>
+      </c>
+      <c r="F14" s="181">
+        <v>0</v>
+      </c>
+      <c r="H14" s="164">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="I14" s="190">
+      <c r="I14" s="182">
         <v>2570.172574693252</v>
       </c>
-      <c r="K14" s="149">
+      <c r="K14" s="142">
         <f t="shared" si="0"/>
         <v>2570.172574693252</v>
       </c>
-      <c r="M14" s="191">
+      <c r="M14" s="183">
         <f t="shared" si="2"/>
         <v>2570.172574693252</v>
       </c>
-      <c r="O14" s="149">
+      <c r="O14" s="142">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B15" s="186">
+      <c r="B15" s="178">
         <v>4</v>
       </c>
-      <c r="C15" s="186" t="s">
+      <c r="C15" s="178" t="s">
         <v>81</v>
       </c>
-      <c r="D15" s="187">
-        <v>0</v>
-      </c>
-      <c r="E15" s="188">
-        <v>0</v>
-      </c>
-      <c r="F15" s="189">
-        <v>0</v>
-      </c>
-      <c r="H15" s="172">
+      <c r="D15" s="179">
+        <v>0</v>
+      </c>
+      <c r="E15" s="180">
+        <v>0</v>
+      </c>
+      <c r="F15" s="181">
+        <v>0</v>
+      </c>
+      <c r="H15" s="164">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="I15" s="190">
+      <c r="I15" s="182">
         <v>2570.172574693252</v>
       </c>
-      <c r="K15" s="149">
+      <c r="K15" s="142">
         <f t="shared" si="0"/>
         <v>2570.172574693252</v>
       </c>
-      <c r="M15" s="191">
+      <c r="M15" s="183">
         <f t="shared" si="2"/>
         <v>2570.172574693252</v>
       </c>
-      <c r="O15" s="149">
+      <c r="O15" s="142">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B16" s="186">
+      <c r="B16" s="178">
         <v>4</v>
       </c>
-      <c r="C16" s="186" t="s">
+      <c r="C16" s="178" t="s">
         <v>84</v>
       </c>
-      <c r="D16" s="187">
-        <v>0</v>
-      </c>
-      <c r="E16" s="188">
-        <v>0</v>
-      </c>
-      <c r="F16" s="189">
-        <v>0</v>
-      </c>
-      <c r="H16" s="172">
+      <c r="D16" s="179">
+        <v>0</v>
+      </c>
+      <c r="E16" s="180">
+        <v>0</v>
+      </c>
+      <c r="F16" s="181">
+        <v>0</v>
+      </c>
+      <c r="H16" s="164">
         <v>6.6000000000000003E-2</v>
       </c>
-      <c r="I16" s="190">
+      <c r="I16" s="182">
         <v>3141.322035736197</v>
       </c>
-      <c r="K16" s="149">
+      <c r="K16" s="142">
         <f t="shared" si="0"/>
         <v>3141.322035736197</v>
       </c>
-      <c r="M16" s="191">
+      <c r="M16" s="183">
         <f t="shared" si="2"/>
         <v>3141.322035736197</v>
       </c>
-      <c r="O16" s="149">
+      <c r="O16" s="142">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B17" s="186">
+      <c r="B17" s="178">
         <v>4</v>
       </c>
-      <c r="C17" s="186" t="s">
+      <c r="C17" s="178" t="s">
         <v>82</v>
       </c>
-      <c r="D17" s="187">
-        <v>0</v>
-      </c>
-      <c r="E17" s="188">
-        <v>0</v>
-      </c>
-      <c r="F17" s="189">
-        <v>0</v>
-      </c>
-      <c r="H17" s="172">
+      <c r="D17" s="179">
+        <v>0</v>
+      </c>
+      <c r="E17" s="180">
+        <v>0</v>
+      </c>
+      <c r="F17" s="181">
+        <v>0</v>
+      </c>
+      <c r="H17" s="164">
         <v>6.6000000000000003E-2</v>
       </c>
-      <c r="I17" s="190">
+      <c r="I17" s="182">
         <v>3141.322035736197</v>
       </c>
-      <c r="K17" s="149">
+      <c r="K17" s="142">
         <f t="shared" si="0"/>
         <v>3141.322035736197</v>
       </c>
-      <c r="M17" s="191">
+      <c r="M17" s="183">
         <f t="shared" si="2"/>
         <v>3141.322035736197</v>
       </c>
-      <c r="O17" s="149">
+      <c r="O17" s="142">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B18" s="186">
+      <c r="B18" s="178">
         <v>4</v>
       </c>
-      <c r="C18" s="186" t="s">
+      <c r="C18" s="178" t="s">
         <v>83</v>
       </c>
-      <c r="D18" s="187">
-        <v>0</v>
-      </c>
-      <c r="E18" s="188">
-        <v>0</v>
-      </c>
-      <c r="F18" s="189">
-        <v>0</v>
-      </c>
-      <c r="H18" s="172">
+      <c r="D18" s="179">
+        <v>0</v>
+      </c>
+      <c r="E18" s="180">
+        <v>0</v>
+      </c>
+      <c r="F18" s="181">
+        <v>0</v>
+      </c>
+      <c r="H18" s="164">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="I18" s="190">
+      <c r="I18" s="182">
         <v>2570.172574693252</v>
       </c>
-      <c r="K18" s="149">
+      <c r="K18" s="142">
         <f t="shared" si="0"/>
         <v>2570.172574693252</v>
       </c>
-      <c r="M18" s="191">
+      <c r="M18" s="183">
         <f t="shared" si="2"/>
         <v>2570.172574693252</v>
       </c>
-      <c r="O18" s="149">
+      <c r="O18" s="142">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B19" s="186"/>
-      <c r="C19" s="186"/>
-      <c r="D19" s="187"/>
-      <c r="E19" s="188"/>
-      <c r="F19" s="193"/>
-      <c r="H19" s="106"/>
-      <c r="I19" s="174"/>
-      <c r="K19" s="106"/>
-      <c r="M19" s="107"/>
-      <c r="O19" s="198"/>
+      <c r="B19" s="178"/>
+      <c r="C19" s="178"/>
+      <c r="D19" s="179"/>
+      <c r="E19" s="180"/>
+      <c r="F19" s="185"/>
+      <c r="H19" s="99"/>
+      <c r="I19" s="166"/>
+      <c r="K19" s="99"/>
+      <c r="M19" s="100"/>
+      <c r="O19" s="190"/>
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B20" s="106"/>
-      <c r="C20" s="106" t="s">
+      <c r="B20" s="99"/>
+      <c r="C20" s="99" t="s">
         <v>141</v>
       </c>
-      <c r="D20" s="173">
+      <c r="D20" s="165">
         <f>SUM(D4:D19)</f>
         <v>535</v>
       </c>
-      <c r="E20" s="198"/>
-      <c r="F20" s="193">
+      <c r="E20" s="190"/>
+      <c r="F20" s="185">
         <f>SUM(F4:F19)</f>
         <v>217638.86157975462</v>
       </c>
-      <c r="H20" s="194"/>
-      <c r="I20" s="174">
+      <c r="H20" s="186"/>
+      <c r="I20" s="166">
         <f>SUM(I4:I19)</f>
         <v>45691.956883435589</v>
       </c>
-      <c r="K20" s="149">
+      <c r="K20" s="142">
         <f>SUM(K4:K19)</f>
         <v>263330.81846319023</v>
       </c>
-      <c r="M20" s="195">
+      <c r="M20" s="187">
         <f>SUM(M4:M19)</f>
         <v>39409.312811963202</v>
       </c>
-      <c r="O20" s="149">
+      <c r="O20" s="142">
         <f>SUM(O4:O19)</f>
         <v>223921.50565122702</v>
       </c>
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B21" s="106"/>
-      <c r="C21" s="106"/>
+      <c r="B21" s="99"/>
+      <c r="C21" s="99"/>
       <c r="D21" s="4"/>
       <c r="E21" s="4" t="s">
         <v>142</v>
@@ -5379,274 +5373,274 @@
       <c r="F21" s="4"/>
     </row>
     <row r="22" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B22" s="106" t="s">
+      <c r="B22" s="99" t="s">
         <v>85</v>
       </c>
-      <c r="C22" s="106">
+      <c r="C22" s="99">
         <v>1</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
-      <c r="H22" s="172">
+      <c r="H22" s="164">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="I22" s="190">
+      <c r="I22" s="182">
         <v>333.17051894171789</v>
       </c>
-      <c r="K22" s="190">
+      <c r="K22" s="182">
         <f>I22</f>
         <v>333.17051894171789</v>
       </c>
-      <c r="M22" s="196">
+      <c r="M22" s="188">
         <v>333.17051894171789</v>
       </c>
-      <c r="O22" s="149">
+      <c r="O22" s="142">
         <f>K22-M22</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B23" s="106" t="s">
+      <c r="B23" s="99" t="s">
         <v>85</v>
       </c>
-      <c r="C23" s="106">
+      <c r="C23" s="99">
         <v>2</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
-      <c r="H23" s="172">
+      <c r="H23" s="164">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="I23" s="190">
+      <c r="I23" s="182">
         <v>285.57473052147247</v>
       </c>
-      <c r="K23" s="190">
+      <c r="K23" s="182">
         <f t="shared" ref="K23:K29" si="3">I23</f>
         <v>285.57473052147247</v>
       </c>
-      <c r="M23" s="196">
+      <c r="M23" s="188">
         <v>285.57473052147247</v>
       </c>
-      <c r="O23" s="149">
+      <c r="O23" s="142">
         <f t="shared" ref="O23:O29" si="4">K23-M23</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B24" s="106" t="s">
+      <c r="B24" s="99" t="s">
         <v>85</v>
       </c>
-      <c r="C24" s="106">
+      <c r="C24" s="99">
         <v>3</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
-      <c r="H24" s="172">
+      <c r="H24" s="164">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="I24" s="190">
+      <c r="I24" s="182">
         <v>285.57473052147247</v>
       </c>
-      <c r="K24" s="190">
+      <c r="K24" s="182">
         <f t="shared" si="3"/>
         <v>285.57473052147247</v>
       </c>
-      <c r="M24" s="196">
+      <c r="M24" s="188">
         <v>285.57473052147247</v>
       </c>
-      <c r="O24" s="149">
+      <c r="O24" s="142">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B25" s="106" t="s">
+      <c r="B25" s="99" t="s">
         <v>85</v>
       </c>
-      <c r="C25" s="106">
+      <c r="C25" s="99">
         <v>4</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
-      <c r="H25" s="172">
+      <c r="H25" s="164">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="I25" s="190">
+      <c r="I25" s="182">
         <v>285.57473052147247</v>
       </c>
-      <c r="K25" s="190">
+      <c r="K25" s="182">
         <f t="shared" si="3"/>
         <v>285.57473052147247</v>
       </c>
-      <c r="M25" s="196">
+      <c r="M25" s="188">
         <v>285.57473052147247</v>
       </c>
-      <c r="O25" s="149">
+      <c r="O25" s="142">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B26" s="106" t="s">
+      <c r="B26" s="99" t="s">
         <v>85</v>
       </c>
-      <c r="C26" s="106">
+      <c r="C26" s="99">
         <v>5</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
-      <c r="H26" s="172">
+      <c r="H26" s="164">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="I26" s="190">
+      <c r="I26" s="182">
         <v>285.57473052147247</v>
       </c>
-      <c r="K26" s="190">
+      <c r="K26" s="182">
         <f t="shared" si="3"/>
         <v>285.57473052147247</v>
       </c>
-      <c r="M26" s="196">
+      <c r="M26" s="188">
         <v>285.57473052147247</v>
       </c>
-      <c r="O26" s="149">
+      <c r="O26" s="142">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B27" s="106" t="s">
+      <c r="B27" s="99" t="s">
         <v>85</v>
       </c>
-      <c r="C27" s="106">
+      <c r="C27" s="99">
         <v>6</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
-      <c r="H27" s="172">
+      <c r="H27" s="164">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="I27" s="190">
+      <c r="I27" s="182">
         <v>142.78736526073624</v>
       </c>
-      <c r="K27" s="190">
+      <c r="K27" s="182">
         <f t="shared" si="3"/>
         <v>142.78736526073624</v>
       </c>
-      <c r="M27" s="196">
+      <c r="M27" s="188">
         <v>142.78736526073624</v>
       </c>
-      <c r="O27" s="149">
+      <c r="O27" s="142">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B28" s="106" t="s">
+      <c r="B28" s="99" t="s">
         <v>85</v>
       </c>
-      <c r="C28" s="106">
+      <c r="C28" s="99">
         <v>7</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
-      <c r="H28" s="172">
+      <c r="H28" s="164">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="I28" s="190">
+      <c r="I28" s="182">
         <v>142.78736526073624</v>
       </c>
-      <c r="K28" s="190">
+      <c r="K28" s="182">
         <f t="shared" si="3"/>
         <v>142.78736526073624</v>
       </c>
-      <c r="M28" s="196">
+      <c r="M28" s="188">
         <v>142.78736526073624</v>
       </c>
-      <c r="O28" s="149">
+      <c r="O28" s="142">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B29" s="106" t="s">
+      <c r="B29" s="99" t="s">
         <v>85</v>
       </c>
-      <c r="C29" s="106">
+      <c r="C29" s="99">
         <v>8</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
-      <c r="H29" s="172">
+      <c r="H29" s="164">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="I29" s="190">
+      <c r="I29" s="182">
         <v>142.78736526073624</v>
       </c>
-      <c r="K29" s="190">
+      <c r="K29" s="182">
         <f t="shared" si="3"/>
         <v>142.78736526073624</v>
       </c>
-      <c r="M29" s="196">
+      <c r="M29" s="188">
         <v>142.78736526073624</v>
       </c>
-      <c r="O29" s="149">
+      <c r="O29" s="142">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="H30" s="198" t="s">
+      <c r="H30" s="190" t="s">
         <v>130</v>
       </c>
-      <c r="I30" s="190">
+      <c r="I30" s="182">
         <f>SUM(I22:I29)</f>
         <v>1903.8315368098165</v>
       </c>
-      <c r="K30" s="244">
+      <c r="K30" s="193">
         <f>SUM(K22:K29)</f>
         <v>1903.8315368098165</v>
       </c>
-      <c r="M30" s="195">
+      <c r="M30" s="187">
         <f>SUM(M22:M29)</f>
         <v>1903.8315368098165</v>
       </c>
-      <c r="O30" s="149">
+      <c r="O30" s="142">
         <f>SUM(O22:O29)</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="O31" s="149"/>
+      <c r="O31" s="142"/>
     </row>
     <row r="32" spans="2:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="D32" s="241" t="s">
+      <c r="D32" s="232" t="s">
         <v>131</v>
       </c>
-      <c r="E32" s="242"/>
-      <c r="F32" s="176">
+      <c r="E32" s="233"/>
+      <c r="F32" s="168">
         <v>265234.65000000002</v>
       </c>
-      <c r="I32" s="197">
+      <c r="I32" s="189">
         <f>F20+I20+I30</f>
         <v>265234.65000000002</v>
       </c>
-      <c r="K32" s="149">
+      <c r="K32" s="142">
         <f>K20+K30</f>
         <v>265234.65000000002</v>
       </c>
-      <c r="M32" s="195">
+      <c r="M32" s="187">
         <f>M20+M30</f>
         <v>41313.144348773021</v>
       </c>
-      <c r="O32" s="149">
+      <c r="O32" s="142">
         <f>O20+O30</f>
         <v>223921.50565122702</v>
       </c>
@@ -5667,7 +5661,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="3" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C3" s="177" t="s">
+      <c r="C3" s="169" t="s">
         <v>132</v>
       </c>
     </row>

--- a/2026/SALTA 1167/Septiembre/SALTA1167-Septiembre.xlsx
+++ b/2026/SALTA 1167/Septiembre/SALTA1167-Septiembre.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\SALTA 1167\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ED1FC23-7FB0-4F03-96CA-618F395DA8E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{968A8C17-7AEE-40B1-BF78-11997AFF8483}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="156">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -501,6 +501,9 @@
   </si>
   <si>
     <t>SALDO A 30/09</t>
+  </si>
+  <si>
+    <t>Transf 28/09</t>
   </si>
 </sst>
 </file>
@@ -1473,132 +1476,6 @@
     <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="8" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1606,6 +1483,132 @@
     </xf>
     <xf numFmtId="44" fontId="14" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -2040,12 +2043,12 @@
     </row>
     <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8"/>
-      <c r="B3" s="201" t="s">
+      <c r="B3" s="203" t="s">
         <v>75</v>
       </c>
-      <c r="C3" s="201"/>
-      <c r="D3" s="201"/>
-      <c r="E3" s="202"/>
+      <c r="C3" s="203"/>
+      <c r="D3" s="203"/>
+      <c r="E3" s="204"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
@@ -2084,24 +2087,24 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="66"/>
-      <c r="B8" s="234" t="s">
+      <c r="B8" s="206" t="s">
         <v>143</v>
       </c>
-      <c r="C8" s="234"/>
+      <c r="C8" s="206"/>
       <c r="D8" s="66"/>
       <c r="E8" s="66"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="66"/>
-      <c r="B9" s="234"/>
-      <c r="C9" s="234"/>
+      <c r="B9" s="206"/>
+      <c r="C9" s="206"/>
       <c r="D9" s="66"/>
       <c r="E9" s="66"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="66"/>
-      <c r="B10" s="234"/>
-      <c r="C10" s="234"/>
+      <c r="B10" s="206"/>
+      <c r="C10" s="206"/>
       <c r="D10" s="66"/>
       <c r="E10" s="66"/>
     </row>
@@ -2120,34 +2123,34 @@
       <c r="E12" s="66"/>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="235" t="s">
+      <c r="A13" s="205" t="s">
         <v>98</v>
       </c>
-      <c r="B13" s="235"/>
-      <c r="C13" s="235"/>
-      <c r="D13" s="235"/>
-      <c r="E13" s="235"/>
+      <c r="B13" s="205"/>
+      <c r="C13" s="205"/>
+      <c r="D13" s="205"/>
+      <c r="E13" s="205"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="235"/>
-      <c r="B14" s="235"/>
-      <c r="C14" s="235"/>
-      <c r="D14" s="235"/>
-      <c r="E14" s="235"/>
+      <c r="A14" s="205"/>
+      <c r="B14" s="205"/>
+      <c r="C14" s="205"/>
+      <c r="D14" s="205"/>
+      <c r="E14" s="205"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="235"/>
-      <c r="B15" s="235"/>
-      <c r="C15" s="235"/>
-      <c r="D15" s="235"/>
-      <c r="E15" s="235"/>
+      <c r="A15" s="205"/>
+      <c r="B15" s="205"/>
+      <c r="C15" s="205"/>
+      <c r="D15" s="205"/>
+      <c r="E15" s="205"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="235"/>
-      <c r="B16" s="235"/>
-      <c r="C16" s="235"/>
-      <c r="D16" s="235"/>
-      <c r="E16" s="235"/>
+      <c r="A16" s="205"/>
+      <c r="B16" s="205"/>
+      <c r="C16" s="205"/>
+      <c r="D16" s="205"/>
+      <c r="E16" s="205"/>
     </row>
     <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="66"/>
@@ -2157,7 +2160,7 @@
       <c r="E17" s="66"/>
     </row>
     <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="236"/>
+      <c r="A18" s="194"/>
       <c r="B18" s="66"/>
       <c r="C18" s="66"/>
       <c r="D18" s="66"/>
@@ -2189,10 +2192,10 @@
       <c r="E21" s="134"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="197" t="s">
+      <c r="A22" s="201" t="s">
         <v>112</v>
       </c>
-      <c r="B22" s="198"/>
+      <c r="B22" s="202"/>
       <c r="C22" s="143"/>
       <c r="D22" s="170">
         <v>510846.85</v>
@@ -2203,8 +2206,8 @@
       <c r="H22" s="76"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="197"/>
-      <c r="B23" s="198"/>
+      <c r="A23" s="201"/>
+      <c r="B23" s="202"/>
       <c r="C23" s="143"/>
       <c r="D23" s="170"/>
       <c r="E23" s="87"/>
@@ -2232,12 +2235,12 @@
       <c r="E25" s="130"/>
     </row>
     <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="197" t="s">
+      <c r="A26" s="201" t="s">
         <v>117</v>
       </c>
-      <c r="B26" s="198"/>
+      <c r="B26" s="202"/>
       <c r="C26" s="146"/>
-      <c r="D26" s="237">
+      <c r="D26" s="195">
         <v>74244</v>
       </c>
       <c r="E26" s="89" t="s">
@@ -2272,10 +2275,10 @@
       <c r="B29" s="59"/>
       <c r="C29" s="59"/>
       <c r="D29" s="88">
-        <v>265234.65000000002</v>
+        <v>233485</v>
       </c>
       <c r="E29" s="89" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -2340,7 +2343,7 @@
       <c r="D34" s="174"/>
       <c r="E34" s="132">
         <f>SUM(D29:D33)</f>
-        <v>1727363.18</v>
+        <v>1695613.5299999998</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2351,10 +2354,10 @@
       <c r="E35" s="133"/>
     </row>
     <row r="36" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="197" t="s">
+      <c r="A36" s="201" t="s">
         <v>114</v>
       </c>
-      <c r="B36" s="198"/>
+      <c r="B36" s="202"/>
       <c r="C36" s="59"/>
       <c r="D36" s="88">
         <v>82000</v>
@@ -2377,10 +2380,10 @@
       </c>
     </row>
     <row r="38" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="197" t="s">
+      <c r="A38" s="201" t="s">
         <v>152</v>
       </c>
-      <c r="B38" s="198"/>
+      <c r="B38" s="202"/>
       <c r="C38" s="59"/>
       <c r="D38" s="62">
         <v>200000</v>
@@ -2411,12 +2414,12 @@
       <c r="E40" s="134"/>
     </row>
     <row r="41" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="197" t="s">
+      <c r="A41" s="201" t="s">
         <v>145</v>
       </c>
-      <c r="B41" s="198"/>
+      <c r="B41" s="202"/>
       <c r="C41" s="143"/>
-      <c r="D41" s="238">
+      <c r="D41" s="196">
         <v>190000</v>
       </c>
       <c r="E41" s="135" t="s">
@@ -2493,8 +2496,8 @@
       <c r="C48" s="154"/>
       <c r="D48" s="65"/>
       <c r="E48" s="98">
-        <f>3000000-2872201.74</f>
-        <v>127798.25999999978</v>
+        <f>3000000-2840452.09</f>
+        <v>159547.91000000015</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2514,7 +2517,7 @@
       <c r="D50" s="68"/>
       <c r="E50" s="69">
         <f>(SUM(E21:E48))</f>
-        <v>2999999.9999999995</v>
+        <v>3000000</v>
       </c>
       <c r="F50" s="86"/>
       <c r="G50" s="21"/>
@@ -2551,8 +2554,8 @@
       <c r="E54" s="60"/>
     </row>
     <row r="55" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="196"/>
-      <c r="B55" s="196"/>
+      <c r="A55" s="209"/>
+      <c r="B55" s="209"/>
       <c r="C55" s="59"/>
       <c r="D55" s="88"/>
       <c r="E55" s="60"/>
@@ -2612,7 +2615,7 @@
       </c>
       <c r="B65" s="58">
         <f>E50</f>
-        <v>2999999.9999999995</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2621,7 +2624,7 @@
       </c>
       <c r="B66" s="58">
         <f>E50-E48</f>
-        <v>2872201.7399999998</v>
+        <v>2840452.09</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2652,7 +2655,7 @@
         <v>106</v>
       </c>
       <c r="B71" s="103">
-        <v>231226.35000000335</v>
+        <v>502577.06</v>
       </c>
       <c r="C71" s="18"/>
       <c r="D71" s="24"/>
@@ -2663,7 +2666,7 @@
       </c>
       <c r="B72" s="83">
         <f>-B66</f>
-        <v>-2872201.7399999998</v>
+        <v>-2840452.09</v>
       </c>
       <c r="E72" s="21"/>
     </row>
@@ -2691,7 +2694,7 @@
       </c>
       <c r="B75" s="82">
         <f>SUM(B71:C74)</f>
-        <v>419415.74000000441</v>
+        <v>722516.10000000102</v>
       </c>
       <c r="D75" s="21"/>
     </row>
@@ -2796,16 +2799,16 @@
     </row>
     <row r="88" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="89" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A89" s="195" t="s">
+      <c r="A89" s="208" t="s">
         <v>18</v>
       </c>
-      <c r="B89" s="195"/>
-      <c r="C89" s="195"/>
+      <c r="B89" s="208"/>
+      <c r="C89" s="208"/>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A90" s="195"/>
-      <c r="B90" s="195"/>
-      <c r="C90" s="195"/>
+      <c r="A90" s="208"/>
+      <c r="B90" s="208"/>
+      <c r="C90" s="208"/>
     </row>
     <row r="91" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="73"/>
@@ -2835,35 +2838,41 @@
       <c r="M94" s="5"/>
     </row>
     <row r="95" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="194"/>
-      <c r="B95" s="194"/>
-      <c r="C95" s="194"/>
-      <c r="D95" s="194"/>
-      <c r="E95" s="194"/>
+      <c r="A95" s="207"/>
+      <c r="B95" s="207"/>
+      <c r="C95" s="207"/>
+      <c r="D95" s="207"/>
+      <c r="E95" s="207"/>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A96" s="194"/>
-      <c r="B96" s="194"/>
-      <c r="C96" s="194"/>
-      <c r="D96" s="194"/>
-      <c r="E96" s="194"/>
+      <c r="A96" s="207"/>
+      <c r="B96" s="207"/>
+      <c r="C96" s="207"/>
+      <c r="D96" s="207"/>
+      <c r="E96" s="207"/>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" s="194"/>
-      <c r="B97" s="194"/>
-      <c r="C97" s="194"/>
-      <c r="D97" s="194"/>
-      <c r="E97" s="194"/>
+      <c r="A97" s="207"/>
+      <c r="B97" s="207"/>
+      <c r="C97" s="207"/>
+      <c r="D97" s="207"/>
+      <c r="E97" s="207"/>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="194"/>
-      <c r="B98" s="194"/>
-      <c r="C98" s="194"/>
-      <c r="D98" s="194"/>
-      <c r="E98" s="194"/>
+      <c r="A98" s="207"/>
+      <c r="B98" s="207"/>
+      <c r="C98" s="207"/>
+      <c r="D98" s="207"/>
+      <c r="E98" s="207"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A95:E98"/>
+    <mergeCell ref="A89:C90"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A41:B41"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="A22:B22"/>
@@ -2871,12 +2880,6 @@
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="B8:C10"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A95:E98"/>
-    <mergeCell ref="A89:C90"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A41:B41"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2914,16 +2917,16 @@
       <c r="B1" s="105"/>
       <c r="C1" s="106"/>
       <c r="D1" s="106"/>
-      <c r="E1" s="208"/>
-      <c r="F1" s="208"/>
-      <c r="G1" s="208"/>
-      <c r="H1" s="208"/>
-      <c r="I1" s="208"/>
-      <c r="J1" s="208"/>
-      <c r="K1" s="208"/>
-      <c r="L1" s="208"/>
-      <c r="M1" s="208"/>
-      <c r="N1" s="208"/>
+      <c r="E1" s="210"/>
+      <c r="F1" s="210"/>
+      <c r="G1" s="210"/>
+      <c r="H1" s="210"/>
+      <c r="I1" s="210"/>
+      <c r="J1" s="210"/>
+      <c r="K1" s="210"/>
+      <c r="L1" s="210"/>
+      <c r="M1" s="210"/>
+      <c r="N1" s="210"/>
       <c r="O1" s="105"/>
       <c r="P1" s="107"/>
     </row>
@@ -2974,209 +2977,209 @@
       <c r="Q3" s="14"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="215" t="s">
+      <c r="A4" s="221" t="s">
         <v>119</v>
       </c>
-      <c r="B4" s="216"/>
-      <c r="C4" s="216"/>
-      <c r="D4" s="216"/>
-      <c r="E4" s="216"/>
-      <c r="F4" s="216"/>
-      <c r="G4" s="216"/>
-      <c r="H4" s="216"/>
-      <c r="I4" s="216"/>
-      <c r="J4" s="216"/>
-      <c r="K4" s="216"/>
-      <c r="L4" s="216"/>
-      <c r="M4" s="216"/>
-      <c r="N4" s="216"/>
-      <c r="O4" s="216"/>
-      <c r="P4" s="217"/>
+      <c r="B4" s="222"/>
+      <c r="C4" s="222"/>
+      <c r="D4" s="222"/>
+      <c r="E4" s="222"/>
+      <c r="F4" s="222"/>
+      <c r="G4" s="222"/>
+      <c r="H4" s="222"/>
+      <c r="I4" s="222"/>
+      <c r="J4" s="222"/>
+      <c r="K4" s="222"/>
+      <c r="L4" s="222"/>
+      <c r="M4" s="222"/>
+      <c r="N4" s="222"/>
+      <c r="O4" s="222"/>
+      <c r="P4" s="223"/>
       <c r="Q4" s="14"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="218"/>
-      <c r="B5" s="219"/>
-      <c r="C5" s="219"/>
-      <c r="D5" s="219"/>
-      <c r="E5" s="219"/>
-      <c r="F5" s="219"/>
-      <c r="G5" s="219"/>
-      <c r="H5" s="219"/>
-      <c r="I5" s="219"/>
-      <c r="J5" s="219"/>
-      <c r="K5" s="219"/>
-      <c r="L5" s="219"/>
-      <c r="M5" s="219"/>
-      <c r="N5" s="219"/>
-      <c r="O5" s="219"/>
-      <c r="P5" s="220"/>
+      <c r="A5" s="224"/>
+      <c r="B5" s="225"/>
+      <c r="C5" s="225"/>
+      <c r="D5" s="225"/>
+      <c r="E5" s="225"/>
+      <c r="F5" s="225"/>
+      <c r="G5" s="225"/>
+      <c r="H5" s="225"/>
+      <c r="I5" s="225"/>
+      <c r="J5" s="225"/>
+      <c r="K5" s="225"/>
+      <c r="L5" s="225"/>
+      <c r="M5" s="225"/>
+      <c r="N5" s="225"/>
+      <c r="O5" s="225"/>
+      <c r="P5" s="226"/>
       <c r="Q5" s="14"/>
     </row>
     <row r="6" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="218"/>
-      <c r="B6" s="219"/>
-      <c r="C6" s="219"/>
-      <c r="D6" s="219"/>
-      <c r="E6" s="219"/>
-      <c r="F6" s="219"/>
-      <c r="G6" s="219"/>
-      <c r="H6" s="219"/>
-      <c r="I6" s="219"/>
-      <c r="J6" s="219"/>
-      <c r="K6" s="219"/>
-      <c r="L6" s="219"/>
-      <c r="M6" s="219"/>
-      <c r="N6" s="219"/>
-      <c r="O6" s="219"/>
-      <c r="P6" s="220"/>
+      <c r="A6" s="224"/>
+      <c r="B6" s="225"/>
+      <c r="C6" s="225"/>
+      <c r="D6" s="225"/>
+      <c r="E6" s="225"/>
+      <c r="F6" s="225"/>
+      <c r="G6" s="225"/>
+      <c r="H6" s="225"/>
+      <c r="I6" s="225"/>
+      <c r="J6" s="225"/>
+      <c r="K6" s="225"/>
+      <c r="L6" s="225"/>
+      <c r="M6" s="225"/>
+      <c r="N6" s="225"/>
+      <c r="O6" s="225"/>
+      <c r="P6" s="226"/>
       <c r="Q6" s="14"/>
     </row>
     <row r="7" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="218"/>
-      <c r="B7" s="219"/>
-      <c r="C7" s="219"/>
-      <c r="D7" s="219"/>
-      <c r="E7" s="219"/>
-      <c r="F7" s="219"/>
-      <c r="G7" s="219"/>
-      <c r="H7" s="219"/>
-      <c r="I7" s="219"/>
-      <c r="J7" s="219"/>
-      <c r="K7" s="219"/>
-      <c r="L7" s="219"/>
-      <c r="M7" s="219"/>
-      <c r="N7" s="219"/>
-      <c r="O7" s="219"/>
-      <c r="P7" s="220"/>
+      <c r="A7" s="224"/>
+      <c r="B7" s="225"/>
+      <c r="C7" s="225"/>
+      <c r="D7" s="225"/>
+      <c r="E7" s="225"/>
+      <c r="F7" s="225"/>
+      <c r="G7" s="225"/>
+      <c r="H7" s="225"/>
+      <c r="I7" s="225"/>
+      <c r="J7" s="225"/>
+      <c r="K7" s="225"/>
+      <c r="L7" s="225"/>
+      <c r="M7" s="225"/>
+      <c r="N7" s="225"/>
+      <c r="O7" s="225"/>
+      <c r="P7" s="226"/>
       <c r="Q7" s="14"/>
     </row>
     <row r="8" spans="1:17" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="221"/>
-      <c r="B8" s="222"/>
-      <c r="C8" s="222"/>
-      <c r="D8" s="222"/>
-      <c r="E8" s="222"/>
-      <c r="F8" s="222"/>
-      <c r="G8" s="222"/>
-      <c r="H8" s="222"/>
-      <c r="I8" s="222"/>
-      <c r="J8" s="222"/>
-      <c r="K8" s="222"/>
-      <c r="L8" s="222"/>
-      <c r="M8" s="222"/>
-      <c r="N8" s="222"/>
-      <c r="O8" s="222"/>
-      <c r="P8" s="223"/>
+      <c r="A8" s="227"/>
+      <c r="B8" s="228"/>
+      <c r="C8" s="228"/>
+      <c r="D8" s="228"/>
+      <c r="E8" s="228"/>
+      <c r="F8" s="228"/>
+      <c r="G8" s="228"/>
+      <c r="H8" s="228"/>
+      <c r="I8" s="228"/>
+      <c r="J8" s="228"/>
+      <c r="K8" s="228"/>
+      <c r="L8" s="228"/>
+      <c r="M8" s="228"/>
+      <c r="N8" s="228"/>
+      <c r="O8" s="228"/>
+      <c r="P8" s="229"/>
     </row>
     <row r="9" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="226" t="s">
+      <c r="A9" s="232" t="s">
         <v>118</v>
       </c>
-      <c r="B9" s="227"/>
-      <c r="C9" s="227"/>
-      <c r="D9" s="227"/>
-      <c r="E9" s="227"/>
-      <c r="F9" s="227"/>
-      <c r="G9" s="227"/>
-      <c r="H9" s="227"/>
-      <c r="I9" s="227"/>
-      <c r="J9" s="227"/>
-      <c r="K9" s="227"/>
-      <c r="L9" s="227"/>
-      <c r="M9" s="227"/>
-      <c r="N9" s="227"/>
-      <c r="O9" s="227"/>
-      <c r="P9" s="227"/>
+      <c r="B9" s="233"/>
+      <c r="C9" s="233"/>
+      <c r="D9" s="233"/>
+      <c r="E9" s="233"/>
+      <c r="F9" s="233"/>
+      <c r="G9" s="233"/>
+      <c r="H9" s="233"/>
+      <c r="I9" s="233"/>
+      <c r="J9" s="233"/>
+      <c r="K9" s="233"/>
+      <c r="L9" s="233"/>
+      <c r="M9" s="233"/>
+      <c r="N9" s="233"/>
+      <c r="O9" s="233"/>
+      <c r="P9" s="233"/>
     </row>
     <row r="10" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="228" t="s">
+      <c r="A10" s="234" t="s">
         <v>116</v>
       </c>
-      <c r="B10" s="228"/>
-      <c r="C10" s="228"/>
-      <c r="D10" s="228"/>
-      <c r="E10" s="228"/>
-      <c r="F10" s="228"/>
-      <c r="G10" s="228"/>
-      <c r="H10" s="228"/>
-      <c r="I10" s="228"/>
-      <c r="J10" s="228"/>
-      <c r="K10" s="228"/>
-      <c r="L10" s="228"/>
-      <c r="M10" s="228"/>
-      <c r="N10" s="228"/>
-      <c r="O10" s="228"/>
-      <c r="P10" s="228"/>
+      <c r="B10" s="234"/>
+      <c r="C10" s="234"/>
+      <c r="D10" s="234"/>
+      <c r="E10" s="234"/>
+      <c r="F10" s="234"/>
+      <c r="G10" s="234"/>
+      <c r="H10" s="234"/>
+      <c r="I10" s="234"/>
+      <c r="J10" s="234"/>
+      <c r="K10" s="234"/>
+      <c r="L10" s="234"/>
+      <c r="M10" s="234"/>
+      <c r="N10" s="234"/>
+      <c r="O10" s="234"/>
+      <c r="P10" s="234"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="203" t="s">
+      <c r="A11" s="215" t="s">
         <v>3</v>
       </c>
       <c r="B11" s="94"/>
-      <c r="C11" s="203" t="s">
+      <c r="C11" s="215" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="203" t="s">
+      <c r="D11" s="215" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="203" t="s">
+      <c r="E11" s="215" t="s">
         <v>7</v>
       </c>
-      <c r="F11" s="206" t="s">
+      <c r="F11" s="211" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="203" t="s">
+      <c r="G11" s="215" t="s">
         <v>5</v>
       </c>
-      <c r="H11" s="211" t="s">
+      <c r="H11" s="217" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="206" t="s">
+      <c r="I11" s="211" t="s">
         <v>22</v>
       </c>
-      <c r="J11" s="206" t="s">
+      <c r="J11" s="211" t="s">
         <v>91</v>
       </c>
-      <c r="K11" s="213" t="s">
+      <c r="K11" s="219" t="s">
         <v>92</v>
       </c>
-      <c r="L11" s="206" t="s">
+      <c r="L11" s="211" t="s">
         <v>78</v>
       </c>
-      <c r="M11" s="206" t="s">
+      <c r="M11" s="211" t="s">
         <v>123</v>
       </c>
       <c r="N11" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="O11" s="209" t="s">
+      <c r="O11" s="213" t="s">
         <v>12</v>
       </c>
-      <c r="P11" s="224" t="s">
+      <c r="P11" s="230" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="205"/>
+      <c r="A12" s="216"/>
       <c r="B12" s="95"/>
-      <c r="C12" s="205"/>
-      <c r="D12" s="204"/>
-      <c r="E12" s="205"/>
-      <c r="F12" s="207"/>
-      <c r="G12" s="205"/>
-      <c r="H12" s="212"/>
-      <c r="I12" s="207"/>
-      <c r="J12" s="207"/>
-      <c r="K12" s="214"/>
-      <c r="L12" s="207"/>
-      <c r="M12" s="207"/>
+      <c r="C12" s="216"/>
+      <c r="D12" s="235"/>
+      <c r="E12" s="216"/>
+      <c r="F12" s="212"/>
+      <c r="G12" s="216"/>
+      <c r="H12" s="218"/>
+      <c r="I12" s="212"/>
+      <c r="J12" s="212"/>
+      <c r="K12" s="220"/>
+      <c r="L12" s="212"/>
+      <c r="M12" s="212"/>
       <c r="N12" s="31" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 16/10</v>
       </c>
-      <c r="O12" s="210"/>
-      <c r="P12" s="225"/>
+      <c r="O12" s="214"/>
+      <c r="P12" s="231"/>
     </row>
     <row r="13" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="34">
@@ -4459,7 +4462,7 @@
       <c r="F34" s="50">
         <v>9070.2199999999993</v>
       </c>
-      <c r="G34" s="239">
+      <c r="G34" s="197">
         <f t="shared" ref="G34" si="11">F34</f>
         <v>9070.2199999999993</v>
       </c>
@@ -4569,7 +4572,7 @@
         <f>SUM(F13:F35)</f>
         <v>3054299.7600000012</v>
       </c>
-      <c r="G36" s="240">
+      <c r="G36" s="198">
         <f>SUM(G13:G35)</f>
         <v>3060391.1300000008</v>
       </c>
@@ -4613,94 +4616,100 @@
     </row>
     <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="39" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C39" s="194" t="str">
+      <c r="C39" s="207" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. PORFAVOR RESPETAR LOS CENTAVOS AL ABONAR.</v>
       </c>
-      <c r="D39" s="194"/>
-      <c r="E39" s="194"/>
-      <c r="F39" s="194"/>
-      <c r="G39" s="194"/>
-      <c r="H39" s="194"/>
-      <c r="I39" s="194"/>
-      <c r="J39" s="194"/>
-      <c r="K39" s="194"/>
-      <c r="L39" s="194"/>
-      <c r="M39" s="194"/>
-      <c r="N39" s="194"/>
+      <c r="D39" s="207"/>
+      <c r="E39" s="207"/>
+      <c r="F39" s="207"/>
+      <c r="G39" s="207"/>
+      <c r="H39" s="207"/>
+      <c r="I39" s="207"/>
+      <c r="J39" s="207"/>
+      <c r="K39" s="207"/>
+      <c r="L39" s="207"/>
+      <c r="M39" s="207"/>
+      <c r="N39" s="207"/>
     </row>
     <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C40" s="194"/>
-      <c r="D40" s="194"/>
-      <c r="E40" s="194"/>
-      <c r="F40" s="194"/>
-      <c r="G40" s="194"/>
-      <c r="H40" s="194"/>
-      <c r="I40" s="194"/>
-      <c r="J40" s="194"/>
-      <c r="K40" s="194"/>
-      <c r="L40" s="194"/>
-      <c r="M40" s="194"/>
-      <c r="N40" s="194"/>
+      <c r="C40" s="207"/>
+      <c r="D40" s="207"/>
+      <c r="E40" s="207"/>
+      <c r="F40" s="207"/>
+      <c r="G40" s="207"/>
+      <c r="H40" s="207"/>
+      <c r="I40" s="207"/>
+      <c r="J40" s="207"/>
+      <c r="K40" s="207"/>
+      <c r="L40" s="207"/>
+      <c r="M40" s="207"/>
+      <c r="N40" s="207"/>
     </row>
     <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C41" s="194"/>
-      <c r="D41" s="194"/>
-      <c r="E41" s="194"/>
-      <c r="F41" s="194"/>
-      <c r="G41" s="194"/>
-      <c r="H41" s="194"/>
-      <c r="I41" s="194"/>
-      <c r="J41" s="194"/>
-      <c r="K41" s="194"/>
-      <c r="L41" s="194"/>
-      <c r="M41" s="194"/>
-      <c r="N41" s="194"/>
+      <c r="C41" s="207"/>
+      <c r="D41" s="207"/>
+      <c r="E41" s="207"/>
+      <c r="F41" s="207"/>
+      <c r="G41" s="207"/>
+      <c r="H41" s="207"/>
+      <c r="I41" s="207"/>
+      <c r="J41" s="207"/>
+      <c r="K41" s="207"/>
+      <c r="L41" s="207"/>
+      <c r="M41" s="207"/>
+      <c r="N41" s="207"/>
     </row>
     <row r="42" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C42" s="194"/>
-      <c r="D42" s="194"/>
-      <c r="E42" s="194"/>
-      <c r="F42" s="194"/>
-      <c r="G42" s="194"/>
-      <c r="H42" s="194"/>
-      <c r="I42" s="194"/>
-      <c r="J42" s="194"/>
-      <c r="K42" s="194"/>
-      <c r="L42" s="194"/>
-      <c r="M42" s="194"/>
-      <c r="N42" s="194"/>
+      <c r="C42" s="207"/>
+      <c r="D42" s="207"/>
+      <c r="E42" s="207"/>
+      <c r="F42" s="207"/>
+      <c r="G42" s="207"/>
+      <c r="H42" s="207"/>
+      <c r="I42" s="207"/>
+      <c r="J42" s="207"/>
+      <c r="K42" s="207"/>
+      <c r="L42" s="207"/>
+      <c r="M42" s="207"/>
+      <c r="N42" s="207"/>
     </row>
     <row r="43" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C43" s="194"/>
-      <c r="D43" s="194"/>
-      <c r="E43" s="194"/>
-      <c r="F43" s="194"/>
-      <c r="G43" s="194"/>
-      <c r="H43" s="194"/>
-      <c r="I43" s="194"/>
-      <c r="J43" s="194"/>
-      <c r="K43" s="194"/>
-      <c r="L43" s="194"/>
-      <c r="M43" s="194"/>
-      <c r="N43" s="194"/>
+      <c r="C43" s="207"/>
+      <c r="D43" s="207"/>
+      <c r="E43" s="207"/>
+      <c r="F43" s="207"/>
+      <c r="G43" s="207"/>
+      <c r="H43" s="207"/>
+      <c r="I43" s="207"/>
+      <c r="J43" s="207"/>
+      <c r="K43" s="207"/>
+      <c r="L43" s="207"/>
+      <c r="M43" s="207"/>
+      <c r="N43" s="207"/>
     </row>
     <row r="44" spans="1:17" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C44" s="194"/>
-      <c r="D44" s="194"/>
-      <c r="E44" s="194"/>
-      <c r="F44" s="194"/>
-      <c r="G44" s="194"/>
-      <c r="H44" s="194"/>
-      <c r="I44" s="194"/>
-      <c r="J44" s="194"/>
-      <c r="K44" s="194"/>
-      <c r="L44" s="194"/>
-      <c r="M44" s="194"/>
-      <c r="N44" s="194"/>
+      <c r="C44" s="207"/>
+      <c r="D44" s="207"/>
+      <c r="E44" s="207"/>
+      <c r="F44" s="207"/>
+      <c r="G44" s="207"/>
+      <c r="H44" s="207"/>
+      <c r="I44" s="207"/>
+      <c r="J44" s="207"/>
+      <c r="K44" s="207"/>
+      <c r="L44" s="207"/>
+      <c r="M44" s="207"/>
+      <c r="N44" s="207"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="C39:N44"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="M11:M12"/>
     <mergeCell ref="E1:N1"/>
     <mergeCell ref="I11:I12"/>
     <mergeCell ref="F11:F12"/>
@@ -4714,12 +4723,6 @@
     <mergeCell ref="A9:P9"/>
     <mergeCell ref="A10:P10"/>
     <mergeCell ref="L11:L12"/>
-    <mergeCell ref="C39:N44"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="M11:M12"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" orientation="landscape" r:id="rId1"/>
@@ -4749,16 +4752,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="D2" s="229" t="s">
+      <c r="D2" s="236" t="s">
         <v>135</v>
       </c>
-      <c r="E2" s="229"/>
-      <c r="F2" s="229"/>
+      <c r="E2" s="236"/>
+      <c r="F2" s="236"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="230" t="s">
+      <c r="H2" s="237" t="s">
         <v>136</v>
       </c>
-      <c r="I2" s="231"/>
+      <c r="I2" s="238"/>
       <c r="J2" s="1"/>
       <c r="K2" s="190" t="s">
         <v>137</v>
@@ -5621,10 +5624,10 @@
       <c r="O31" s="142"/>
     </row>
     <row r="32" spans="2:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="D32" s="232" t="s">
+      <c r="D32" s="239" t="s">
         <v>131</v>
       </c>
-      <c r="E32" s="233"/>
+      <c r="E32" s="240"/>
       <c r="F32" s="168">
         <v>265234.65000000002</v>
       </c>

--- a/2026/SALTA 1167/Septiembre/SALTA1167-Septiembre.xlsx
+++ b/2026/SALTA 1167/Septiembre/SALTA1167-Septiembre.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\SALTA 1167\Septiembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\SALTA 1167\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{968A8C17-7AEE-40B1-BF78-11997AFF8483}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A98DFE70-CCD2-4F04-B478-D603059DBF73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -23,16 +23,11 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$94</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="157">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -504,6 +499,9 @@
   </si>
   <si>
     <t>Transf 28/09</t>
+  </si>
+  <si>
+    <t>Cristian oscar Rifici</t>
   </si>
 </sst>
 </file>
@@ -1141,7 +1139,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="241">
+  <cellXfs count="240">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1467,9 +1465,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1483,18 +1478,27 @@
     </xf>
     <xf numFmtId="44" fontId="14" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="14" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1507,36 +1511,30 @@
     <xf numFmtId="0" fontId="24" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1590,9 +1588,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1688,9 +1683,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1728,9 +1723,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1763,26 +1758,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1815,26 +1793,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2009,21 +1970,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M98"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.5703125" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.5703125" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.5546875" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.5546875" customWidth="1"/>
+    <col min="5" max="5" width="14.5546875" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.42578125" customWidth="1"/>
+    <col min="12" max="12" width="18.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="7"/>
       <c r="B1" s="38" t="s">
         <v>73</v>
@@ -2032,7 +1993,7 @@
       <c r="D1" s="38"/>
       <c r="E1" s="39"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="8"/>
       <c r="B2" s="40" t="s">
         <v>14</v>
@@ -2041,16 +2002,16 @@
       <c r="D2" s="40"/>
       <c r="E2" s="41"/>
     </row>
-    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="8"/>
-      <c r="B3" s="203" t="s">
+      <c r="B3" s="205" t="s">
         <v>75</v>
       </c>
-      <c r="C3" s="203"/>
-      <c r="D3" s="203"/>
-      <c r="E3" s="204"/>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C3" s="205"/>
+      <c r="D3" s="205"/>
+      <c r="E3" s="206"/>
+    </row>
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="11" t="s">
         <v>0</v>
       </c>
@@ -2061,7 +2022,7 @@
       <c r="D4" s="12"/>
       <c r="E4" s="13"/>
     </row>
-    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
         <v>74</v>
       </c>
@@ -2074,7 +2035,7 @@
       </c>
       <c r="E5" s="10"/>
     </row>
-    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="11" t="s">
         <v>122</v>
       </c>
@@ -2085,95 +2046,95 @@
       </c>
       <c r="E6" s="13"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="66"/>
-      <c r="B8" s="206" t="s">
+      <c r="B8" s="208" t="s">
         <v>143</v>
       </c>
-      <c r="C8" s="206"/>
+      <c r="C8" s="208"/>
       <c r="D8" s="66"/>
       <c r="E8" s="66"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="66"/>
-      <c r="B9" s="206"/>
-      <c r="C9" s="206"/>
+      <c r="B9" s="208"/>
+      <c r="C9" s="208"/>
       <c r="D9" s="66"/>
       <c r="E9" s="66"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="66"/>
-      <c r="B10" s="206"/>
-      <c r="C10" s="206"/>
+      <c r="B10" s="208"/>
+      <c r="C10" s="208"/>
       <c r="D10" s="66"/>
       <c r="E10" s="66"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="66"/>
       <c r="B11" s="66"/>
       <c r="C11" s="66"/>
       <c r="D11" s="66"/>
       <c r="E11" s="66"/>
     </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="66"/>
       <c r="B12" s="66"/>
       <c r="C12" s="66"/>
       <c r="D12" s="66"/>
       <c r="E12" s="66"/>
     </row>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="205" t="s">
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="207" t="s">
         <v>98</v>
       </c>
-      <c r="B13" s="205"/>
-      <c r="C13" s="205"/>
-      <c r="D13" s="205"/>
-      <c r="E13" s="205"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="205"/>
-      <c r="B14" s="205"/>
-      <c r="C14" s="205"/>
-      <c r="D14" s="205"/>
-      <c r="E14" s="205"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="205"/>
-      <c r="B15" s="205"/>
-      <c r="C15" s="205"/>
-      <c r="D15" s="205"/>
-      <c r="E15" s="205"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="205"/>
-      <c r="B16" s="205"/>
-      <c r="C16" s="205"/>
-      <c r="D16" s="205"/>
-      <c r="E16" s="205"/>
-    </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="207"/>
+      <c r="C13" s="207"/>
+      <c r="D13" s="207"/>
+      <c r="E13" s="207"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="207"/>
+      <c r="B14" s="207"/>
+      <c r="C14" s="207"/>
+      <c r="D14" s="207"/>
+      <c r="E14" s="207"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="207"/>
+      <c r="B15" s="207"/>
+      <c r="C15" s="207"/>
+      <c r="D15" s="207"/>
+      <c r="E15" s="207"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="207"/>
+      <c r="B16" s="207"/>
+      <c r="C16" s="207"/>
+      <c r="D16" s="207"/>
+      <c r="E16" s="207"/>
+    </row>
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="66"/>
       <c r="B17" s="66"/>
       <c r="C17" s="66"/>
       <c r="D17" s="66"/>
       <c r="E17" s="66"/>
     </row>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="194"/>
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="193"/>
       <c r="B18" s="66"/>
       <c r="C18" s="66"/>
       <c r="D18" s="66"/>
       <c r="E18" s="66"/>
     </row>
-    <row r="19" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="66"/>
       <c r="B19" s="66"/>
       <c r="C19" s="66"/>
       <c r="D19" s="66"/>
       <c r="E19" s="66"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="158" t="s">
         <v>101</v>
       </c>
@@ -2182,7 +2143,7 @@
       <c r="D20" s="70"/>
       <c r="E20" s="71"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="145" t="s">
         <v>76</v>
       </c>
@@ -2191,7 +2152,7 @@
       <c r="D21" s="91"/>
       <c r="E21" s="134"/>
     </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="201" t="s">
         <v>112</v>
       </c>
@@ -2205,7 +2166,7 @@
       </c>
       <c r="H22" s="76"/>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="201"/>
       <c r="B23" s="202"/>
       <c r="C23" s="143"/>
@@ -2213,7 +2174,7 @@
       <c r="E23" s="87"/>
       <c r="H23" s="76"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="144" t="s">
         <v>9</v>
       </c>
@@ -2225,7 +2186,7 @@
         <v>510846.85</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="145" t="s">
         <v>17</v>
       </c>
@@ -2234,20 +2195,20 @@
       <c r="D25" s="172"/>
       <c r="E25" s="130"/>
     </row>
-    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="201" t="s">
         <v>117</v>
       </c>
       <c r="B26" s="202"/>
       <c r="C26" s="146"/>
-      <c r="D26" s="195">
+      <c r="D26" s="194">
         <v>74244</v>
       </c>
       <c r="E26" s="89" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="144" t="s">
         <v>1</v>
       </c>
@@ -2259,7 +2220,7 @@
         <v>74244</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="145" t="s">
         <v>10</v>
       </c>
@@ -2268,7 +2229,7 @@
       <c r="D28" s="173"/>
       <c r="E28" s="131"/>
     </row>
-    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="59" t="s">
         <v>66</v>
       </c>
@@ -2281,7 +2242,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="59" t="s">
         <v>65</v>
       </c>
@@ -2295,7 +2256,7 @@
         <v>Transf 07/09</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="59" t="s">
         <v>65</v>
       </c>
@@ -2308,11 +2269,11 @@
         <v>147</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="199" t="s">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" s="203" t="s">
         <v>67</v>
       </c>
-      <c r="B32" s="200"/>
+      <c r="B32" s="204"/>
       <c r="C32" s="59"/>
       <c r="D32" s="88">
         <v>872785.72</v>
@@ -2321,11 +2282,11 @@
         <v>147</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="149" t="s">
         <v>77</v>
       </c>
-      <c r="B33" s="191"/>
+      <c r="B33" s="150"/>
       <c r="C33" s="59"/>
       <c r="D33" s="88">
         <v>30111.39</v>
@@ -2334,7 +2295,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="144" t="s">
         <v>2</v>
       </c>
@@ -2346,14 +2307,14 @@
         <v>1695613.5299999998</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="145"/>
       <c r="B35" s="144"/>
       <c r="C35" s="144"/>
       <c r="D35" s="171"/>
       <c r="E35" s="133"/>
     </row>
-    <row r="36" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="201" t="s">
         <v>114</v>
       </c>
@@ -2366,11 +2327,11 @@
         <v>149</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="151" t="s">
         <v>151</v>
       </c>
-      <c r="B37" s="192"/>
+      <c r="B37" s="191"/>
       <c r="C37" s="59"/>
       <c r="D37" s="88">
         <v>52253.440000000002</v>
@@ -2379,7 +2340,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="201" t="s">
         <v>152</v>
       </c>
@@ -2392,7 +2353,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="144" t="s">
         <v>6</v>
       </c>
@@ -2404,7 +2365,7 @@
         <v>334253.44</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="145" t="s">
         <v>11</v>
       </c>
@@ -2413,20 +2374,20 @@
       <c r="D40" s="91"/>
       <c r="E40" s="134"/>
     </row>
-    <row r="41" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="201" t="s">
         <v>145</v>
       </c>
       <c r="B41" s="202"/>
       <c r="C41" s="143"/>
-      <c r="D41" s="196">
+      <c r="D41" s="195">
         <v>190000</v>
       </c>
       <c r="E41" s="135" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="144" t="s">
         <v>9</v>
       </c>
@@ -2438,7 +2399,7 @@
         <v>190000</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="145" t="s">
         <v>8</v>
       </c>
@@ -2447,7 +2408,7 @@
       <c r="D43" s="175"/>
       <c r="E43" s="97"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="59" t="s">
         <v>133</v>
       </c>
@@ -2458,7 +2419,7 @@
       <c r="D44" s="88"/>
       <c r="E44" s="136"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="59" t="s">
         <v>113</v>
       </c>
@@ -2469,7 +2430,7 @@
       </c>
       <c r="E45" s="137"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="153" t="s">
         <v>9</v>
       </c>
@@ -2481,14 +2442,14 @@
         <v>35494.269999999997</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="59"/>
       <c r="B47" s="59"/>
       <c r="C47" s="59"/>
       <c r="D47" s="59"/>
       <c r="E47" s="64"/>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="154" t="s">
         <v>97</v>
       </c>
@@ -2500,7 +2461,7 @@
         <v>159547.91000000015</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="155"/>
       <c r="B49" s="66"/>
       <c r="C49" s="66"/>
@@ -2508,7 +2469,7 @@
       <c r="E49" s="67"/>
       <c r="F49" s="21"/>
     </row>
-    <row r="50" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="156" t="s">
         <v>93</v>
       </c>
@@ -2522,14 +2483,14 @@
       <c r="F50" s="86"/>
       <c r="G50" s="21"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="66"/>
       <c r="B51" s="66"/>
       <c r="C51" s="66"/>
       <c r="D51" s="66"/>
       <c r="E51" s="66"/>
     </row>
-    <row r="52" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="66"/>
       <c r="B52" s="66"/>
       <c r="C52" s="66"/>
@@ -2537,7 +2498,7 @@
       <c r="E52" s="66"/>
       <c r="H52" s="92"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="158" t="s">
         <v>94</v>
       </c>
@@ -2546,35 +2507,35 @@
       <c r="D53" s="70"/>
       <c r="E53" s="71"/>
     </row>
-    <row r="54" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="161"/>
       <c r="B54" s="150"/>
       <c r="C54" s="59"/>
       <c r="D54" s="62"/>
       <c r="E54" s="60"/>
     </row>
-    <row r="55" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="209"/>
-      <c r="B55" s="209"/>
+    <row r="55" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="200"/>
+      <c r="B55" s="200"/>
       <c r="C55" s="59"/>
       <c r="D55" s="88"/>
       <c r="E55" s="60"/>
     </row>
-    <row r="56" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="61"/>
       <c r="B57" s="63"/>
       <c r="C57" s="4"/>
       <c r="D57" s="62"/>
       <c r="E57" s="60"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="26"/>
       <c r="B58" s="25"/>
       <c r="C58" s="25"/>
@@ -2584,9 +2545,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="15" t="s">
         <v>96</v>
       </c>
@@ -2595,8 +2556,8 @@
       <c r="D61" s="16"/>
       <c r="E61" s="127"/>
     </row>
-    <row r="62" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="63" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="63" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
         <v>95</v>
       </c>
@@ -2608,8 +2569,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="65" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="65" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="57" t="s">
         <v>102</v>
       </c>
@@ -2618,7 +2579,7 @@
         <v>3000000</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="57" t="s">
         <v>103</v>
       </c>
@@ -2627,7 +2588,7 @@
         <v>2840452.09</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="57" t="s">
         <v>104</v>
       </c>
@@ -2636,7 +2597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="57" t="s">
         <v>105</v>
       </c>
@@ -2645,12 +2606,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:5" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" s="19" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A70"/>
       <c r="B70" s="20"/>
       <c r="C70" s="18"/>
     </row>
-    <row r="71" spans="1:5" s="19" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" s="19" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A71" s="78" t="s">
         <v>106</v>
       </c>
@@ -2660,7 +2621,7 @@
       <c r="C71" s="18"/>
       <c r="D71" s="24"/>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="29" t="s">
         <v>99</v>
       </c>
@@ -2670,7 +2631,7 @@
       </c>
       <c r="E72" s="21"/>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="29" t="s">
         <v>25</v>
       </c>
@@ -2679,7 +2640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="29" t="s">
         <v>108</v>
       </c>
@@ -2688,7 +2649,7 @@
         <v>3060391.1300000008</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="81" t="s">
         <v>110</v>
       </c>
@@ -2698,13 +2659,13 @@
       </c>
       <c r="D75" s="21"/>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="79"/>
       <c r="B76" s="79"/>
       <c r="D76" s="21"/>
       <c r="E76" s="20"/>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="78" t="s">
         <v>107</v>
       </c>
@@ -2714,7 +2675,7 @@
       <c r="D77" s="20"/>
       <c r="E77" s="21"/>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="29" t="s">
         <v>100</v>
       </c>
@@ -2725,7 +2686,7 @@
       <c r="D78" s="21"/>
       <c r="E78" s="21"/>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="29" t="s">
         <v>25</v>
       </c>
@@ -2735,7 +2696,7 @@
       </c>
       <c r="D79" s="21"/>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="29" t="s">
         <v>109</v>
       </c>
@@ -2744,7 +2705,7 @@
       </c>
       <c r="D80" s="128"/>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81" s="85" t="s">
         <v>24</v>
       </c>
@@ -2753,7 +2714,7 @@
       <c r="E81" s="21"/>
       <c r="F81" s="20"/>
     </row>
-    <row r="82" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="81" t="s">
         <v>111</v>
       </c>
@@ -2765,15 +2726,15 @@
       <c r="E82" s="21"/>
       <c r="F82" s="21"/>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" s="79"/>
       <c r="B83" s="79"/>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A84" s="79"/>
       <c r="B84" s="79"/>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A85" s="78" t="s">
         <v>124</v>
       </c>
@@ -2781,7 +2742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A86" s="29" t="s">
         <v>125</v>
       </c>
@@ -2789,7 +2750,7 @@
         <v>1054849.6000000001</v>
       </c>
     </row>
-    <row r="87" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="81" t="s">
         <v>154</v>
       </c>
@@ -2797,20 +2758,20 @@
         <v>1070612.72</v>
       </c>
     </row>
-    <row r="88" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A89" s="208" t="s">
+    <row r="88" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A89" s="199" t="s">
         <v>18</v>
       </c>
-      <c r="B89" s="208"/>
-      <c r="C89" s="208"/>
-    </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A90" s="208"/>
-      <c r="B90" s="208"/>
-      <c r="C90" s="208"/>
-    </row>
-    <row r="91" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B89" s="199"/>
+      <c r="C89" s="199"/>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A90" s="199"/>
+      <c r="B90" s="199"/>
+      <c r="C90" s="199"/>
+    </row>
+    <row r="91" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="73"/>
       <c r="B91" s="17"/>
       <c r="C91" s="17">
@@ -2818,13 +2779,13 @@
       </c>
       <c r="E91" s="86"/>
     </row>
-    <row r="92" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="73"/>
       <c r="B92" s="75"/>
       <c r="C92" s="72"/>
       <c r="D92" s="86"/>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A93" s="22" t="s">
         <v>6</v>
       </c>
@@ -2834,45 +2795,39 @@
       </c>
       <c r="C93" s="23"/>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M94" s="5"/>
     </row>
-    <row r="95" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="207"/>
-      <c r="B95" s="207"/>
-      <c r="C95" s="207"/>
-      <c r="D95" s="207"/>
-      <c r="E95" s="207"/>
-    </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A96" s="207"/>
-      <c r="B96" s="207"/>
-      <c r="C96" s="207"/>
-      <c r="D96" s="207"/>
-      <c r="E96" s="207"/>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" s="207"/>
-      <c r="B97" s="207"/>
-      <c r="C97" s="207"/>
-      <c r="D97" s="207"/>
-      <c r="E97" s="207"/>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="207"/>
-      <c r="B98" s="207"/>
-      <c r="C98" s="207"/>
-      <c r="D98" s="207"/>
-      <c r="E98" s="207"/>
+    <row r="95" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="198"/>
+      <c r="B95" s="198"/>
+      <c r="C95" s="198"/>
+      <c r="D95" s="198"/>
+      <c r="E95" s="198"/>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A96" s="198"/>
+      <c r="B96" s="198"/>
+      <c r="C96" s="198"/>
+      <c r="D96" s="198"/>
+      <c r="E96" s="198"/>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A97" s="198"/>
+      <c r="B97" s="198"/>
+      <c r="C97" s="198"/>
+      <c r="D97" s="198"/>
+      <c r="E97" s="198"/>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A98" s="198"/>
+      <c r="B98" s="198"/>
+      <c r="C98" s="198"/>
+      <c r="D98" s="198"/>
+      <c r="E98" s="198"/>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A95:E98"/>
-    <mergeCell ref="A89:C90"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A41:B41"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="A22:B22"/>
@@ -2880,6 +2835,12 @@
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="B8:C10"/>
     <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A95:E98"/>
+    <mergeCell ref="A89:C90"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A41:B41"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2890,47 +2851,47 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R44"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="4.42578125" customWidth="1"/>
-    <col min="3" max="3" width="18.5703125" customWidth="1"/>
+    <col min="1" max="2" width="4.44140625" customWidth="1"/>
+    <col min="3" max="3" width="18.5546875" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="8.42578125" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" customWidth="1"/>
-    <col min="9" max="9" width="9.5703125" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" customWidth="1"/>
+    <col min="5" max="5" width="8.44140625" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" customWidth="1"/>
+    <col min="8" max="8" width="10.5546875" customWidth="1"/>
+    <col min="9" max="9" width="9.5546875" customWidth="1"/>
+    <col min="10" max="10" width="12.44140625" customWidth="1"/>
+    <col min="11" max="11" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5546875" customWidth="1"/>
+    <col min="13" max="13" width="13.44140625" customWidth="1"/>
+    <col min="14" max="14" width="14.5546875" customWidth="1"/>
     <col min="15" max="15" width="12" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" customWidth="1"/>
-    <col min="17" max="17" width="7.42578125" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="14.44140625" customWidth="1"/>
+    <col min="17" max="17" width="7.44140625" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="104"/>
       <c r="B1" s="105"/>
       <c r="C1" s="106"/>
       <c r="D1" s="106"/>
-      <c r="E1" s="210"/>
-      <c r="F1" s="210"/>
-      <c r="G1" s="210"/>
-      <c r="H1" s="210"/>
-      <c r="I1" s="210"/>
-      <c r="J1" s="210"/>
-      <c r="K1" s="210"/>
-      <c r="L1" s="210"/>
-      <c r="M1" s="210"/>
-      <c r="N1" s="210"/>
+      <c r="E1" s="214"/>
+      <c r="F1" s="214"/>
+      <c r="G1" s="214"/>
+      <c r="H1" s="214"/>
+      <c r="I1" s="214"/>
+      <c r="J1" s="214"/>
+      <c r="K1" s="214"/>
+      <c r="L1" s="214"/>
+      <c r="M1" s="214"/>
+      <c r="N1" s="214"/>
       <c r="O1" s="105"/>
       <c r="P1" s="107"/>
     </row>
-    <row r="2" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="108"/>
       <c r="B2" s="109"/>
       <c r="C2" s="110"/>
@@ -2957,7 +2918,7 @@
       <c r="P2" s="116"/>
       <c r="Q2" s="14"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="108"/>
       <c r="B3" s="109"/>
       <c r="C3" s="110"/>
@@ -2976,7 +2937,7 @@
       <c r="P3" s="116"/>
       <c r="Q3" s="14"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="221" t="s">
         <v>119</v>
       </c>
@@ -2997,7 +2958,7 @@
       <c r="P4" s="223"/>
       <c r="Q4" s="14"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="224"/>
       <c r="B5" s="225"/>
       <c r="C5" s="225"/>
@@ -3016,7 +2977,7 @@
       <c r="P5" s="226"/>
       <c r="Q5" s="14"/>
     </row>
-    <row r="6" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="224"/>
       <c r="B6" s="225"/>
       <c r="C6" s="225"/>
@@ -3035,7 +2996,7 @@
       <c r="P6" s="226"/>
       <c r="Q6" s="14"/>
     </row>
-    <row r="7" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="224"/>
       <c r="B7" s="225"/>
       <c r="C7" s="225"/>
@@ -3054,7 +3015,7 @@
       <c r="P7" s="226"/>
       <c r="Q7" s="14"/>
     </row>
-    <row r="8" spans="1:17" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="227"/>
       <c r="B8" s="228"/>
       <c r="C8" s="228"/>
@@ -3072,7 +3033,7 @@
       <c r="O8" s="228"/>
       <c r="P8" s="229"/>
     </row>
-    <row r="9" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="232" t="s">
         <v>118</v>
       </c>
@@ -3092,7 +3053,7 @@
       <c r="O9" s="233"/>
       <c r="P9" s="233"/>
     </row>
-    <row r="10" spans="1:17" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="234" t="s">
         <v>116</v>
       </c>
@@ -3112,76 +3073,76 @@
       <c r="O10" s="234"/>
       <c r="P10" s="234"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="215" t="s">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A11" s="209" t="s">
         <v>3</v>
       </c>
       <c r="B11" s="94"/>
-      <c r="C11" s="215" t="s">
+      <c r="C11" s="209" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="215" t="s">
+      <c r="D11" s="209" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="215" t="s">
+      <c r="E11" s="209" t="s">
         <v>7</v>
       </c>
-      <c r="F11" s="211" t="s">
+      <c r="F11" s="212" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="215" t="s">
+      <c r="G11" s="209" t="s">
         <v>5</v>
       </c>
       <c r="H11" s="217" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="211" t="s">
+      <c r="I11" s="212" t="s">
         <v>22</v>
       </c>
-      <c r="J11" s="211" t="s">
+      <c r="J11" s="212" t="s">
         <v>91</v>
       </c>
       <c r="K11" s="219" t="s">
         <v>92</v>
       </c>
-      <c r="L11" s="211" t="s">
+      <c r="L11" s="212" t="s">
         <v>78</v>
       </c>
-      <c r="M11" s="211" t="s">
+      <c r="M11" s="212" t="s">
         <v>123</v>
       </c>
       <c r="N11" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="O11" s="213" t="s">
+      <c r="O11" s="215" t="s">
         <v>12</v>
       </c>
       <c r="P11" s="230" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="216"/>
+    <row r="12" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="211"/>
       <c r="B12" s="95"/>
-      <c r="C12" s="216"/>
-      <c r="D12" s="235"/>
-      <c r="E12" s="216"/>
-      <c r="F12" s="212"/>
-      <c r="G12" s="216"/>
+      <c r="C12" s="211"/>
+      <c r="D12" s="210"/>
+      <c r="E12" s="211"/>
+      <c r="F12" s="213"/>
+      <c r="G12" s="211"/>
       <c r="H12" s="218"/>
-      <c r="I12" s="212"/>
-      <c r="J12" s="212"/>
+      <c r="I12" s="213"/>
+      <c r="J12" s="213"/>
       <c r="K12" s="220"/>
-      <c r="L12" s="212"/>
-      <c r="M12" s="212"/>
+      <c r="L12" s="213"/>
+      <c r="M12" s="213"/>
       <c r="N12" s="31" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 16/10</v>
       </c>
-      <c r="O12" s="214"/>
+      <c r="O12" s="216"/>
       <c r="P12" s="231"/>
     </row>
-    <row r="13" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="34">
         <v>1</v>
       </c>
@@ -3239,7 +3200,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="118">
         <v>2</v>
       </c>
@@ -3300,7 +3261,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="34">
         <v>3</v>
       </c>
@@ -3361,7 +3322,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="34">
         <v>4</v>
       </c>
@@ -3421,8 +3382,11 @@
         <f t="shared" si="7"/>
         <v>0.04</v>
       </c>
-    </row>
-    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R16" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="118">
         <v>5</v>
       </c>
@@ -3488,7 +3452,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="34">
         <v>6</v>
       </c>
@@ -3549,7 +3513,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="118">
         <v>7</v>
       </c>
@@ -3610,7 +3574,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="118">
         <v>8</v>
       </c>
@@ -3671,7 +3635,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="118">
         <v>9</v>
       </c>
@@ -3733,7 +3697,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="118">
         <v>10</v>
       </c>
@@ -3794,7 +3758,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="34">
         <v>11</v>
       </c>
@@ -3856,7 +3820,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="34">
         <v>12</v>
       </c>
@@ -3917,7 +3881,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="34">
         <v>13</v>
       </c>
@@ -3977,7 +3941,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="118">
         <v>14</v>
       </c>
@@ -4036,7 +4000,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="34">
         <v>15</v>
       </c>
@@ -4095,7 +4059,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="118">
         <v>16</v>
       </c>
@@ -4156,7 +4120,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="118">
         <v>17</v>
       </c>
@@ -4214,7 +4178,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="34">
         <v>18</v>
       </c>
@@ -4273,7 +4237,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" s="118">
         <v>19</v>
       </c>
@@ -4329,7 +4293,7 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A32" s="48">
         <v>20</v>
       </c>
@@ -4387,7 +4351,7 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="48">
         <v>21</v>
       </c>
@@ -4445,7 +4409,7 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="49">
         <v>22</v>
       </c>
@@ -4462,7 +4426,7 @@
       <c r="F34" s="50">
         <v>9070.2199999999993</v>
       </c>
-      <c r="G34" s="197">
+      <c r="G34" s="196">
         <f t="shared" ref="G34" si="11">F34</f>
         <v>9070.2199999999993</v>
       </c>
@@ -4501,7 +4465,7 @@
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="34">
         <v>23</v>
       </c>
@@ -4559,7 +4523,7 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="53"/>
       <c r="B36" s="53"/>
       <c r="C36" s="54"/>
@@ -4572,7 +4536,7 @@
         <f>SUM(F13:F35)</f>
         <v>3054299.7600000012</v>
       </c>
-      <c r="G36" s="198">
+      <c r="G36" s="197">
         <f>SUM(G13:G35)</f>
         <v>3060391.1300000008</v>
       </c>
@@ -4610,106 +4574,100 @@
         <v>3365866.7600000007</v>
       </c>
     </row>
-    <row r="37" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C37" s="27"/>
       <c r="D37" s="27"/>
     </row>
-    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C39" s="207" t="str">
+    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="39" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C39" s="198" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. PORFAVOR RESPETAR LOS CENTAVOS AL ABONAR.</v>
       </c>
-      <c r="D39" s="207"/>
-      <c r="E39" s="207"/>
-      <c r="F39" s="207"/>
-      <c r="G39" s="207"/>
-      <c r="H39" s="207"/>
-      <c r="I39" s="207"/>
-      <c r="J39" s="207"/>
-      <c r="K39" s="207"/>
-      <c r="L39" s="207"/>
-      <c r="M39" s="207"/>
-      <c r="N39" s="207"/>
-    </row>
-    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C40" s="207"/>
-      <c r="D40" s="207"/>
-      <c r="E40" s="207"/>
-      <c r="F40" s="207"/>
-      <c r="G40" s="207"/>
-      <c r="H40" s="207"/>
-      <c r="I40" s="207"/>
-      <c r="J40" s="207"/>
-      <c r="K40" s="207"/>
-      <c r="L40" s="207"/>
-      <c r="M40" s="207"/>
-      <c r="N40" s="207"/>
-    </row>
-    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C41" s="207"/>
-      <c r="D41" s="207"/>
-      <c r="E41" s="207"/>
-      <c r="F41" s="207"/>
-      <c r="G41" s="207"/>
-      <c r="H41" s="207"/>
-      <c r="I41" s="207"/>
-      <c r="J41" s="207"/>
-      <c r="K41" s="207"/>
-      <c r="L41" s="207"/>
-      <c r="M41" s="207"/>
-      <c r="N41" s="207"/>
-    </row>
-    <row r="42" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C42" s="207"/>
-      <c r="D42" s="207"/>
-      <c r="E42" s="207"/>
-      <c r="F42" s="207"/>
-      <c r="G42" s="207"/>
-      <c r="H42" s="207"/>
-      <c r="I42" s="207"/>
-      <c r="J42" s="207"/>
-      <c r="K42" s="207"/>
-      <c r="L42" s="207"/>
-      <c r="M42" s="207"/>
-      <c r="N42" s="207"/>
-    </row>
-    <row r="43" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C43" s="207"/>
-      <c r="D43" s="207"/>
-      <c r="E43" s="207"/>
-      <c r="F43" s="207"/>
-      <c r="G43" s="207"/>
-      <c r="H43" s="207"/>
-      <c r="I43" s="207"/>
-      <c r="J43" s="207"/>
-      <c r="K43" s="207"/>
-      <c r="L43" s="207"/>
-      <c r="M43" s="207"/>
-      <c r="N43" s="207"/>
-    </row>
-    <row r="44" spans="1:17" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C44" s="207"/>
-      <c r="D44" s="207"/>
-      <c r="E44" s="207"/>
-      <c r="F44" s="207"/>
-      <c r="G44" s="207"/>
-      <c r="H44" s="207"/>
-      <c r="I44" s="207"/>
-      <c r="J44" s="207"/>
-      <c r="K44" s="207"/>
-      <c r="L44" s="207"/>
-      <c r="M44" s="207"/>
-      <c r="N44" s="207"/>
+      <c r="D39" s="198"/>
+      <c r="E39" s="198"/>
+      <c r="F39" s="198"/>
+      <c r="G39" s="198"/>
+      <c r="H39" s="198"/>
+      <c r="I39" s="198"/>
+      <c r="J39" s="198"/>
+      <c r="K39" s="198"/>
+      <c r="L39" s="198"/>
+      <c r="M39" s="198"/>
+      <c r="N39" s="198"/>
+    </row>
+    <row r="40" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C40" s="198"/>
+      <c r="D40" s="198"/>
+      <c r="E40" s="198"/>
+      <c r="F40" s="198"/>
+      <c r="G40" s="198"/>
+      <c r="H40" s="198"/>
+      <c r="I40" s="198"/>
+      <c r="J40" s="198"/>
+      <c r="K40" s="198"/>
+      <c r="L40" s="198"/>
+      <c r="M40" s="198"/>
+      <c r="N40" s="198"/>
+    </row>
+    <row r="41" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C41" s="198"/>
+      <c r="D41" s="198"/>
+      <c r="E41" s="198"/>
+      <c r="F41" s="198"/>
+      <c r="G41" s="198"/>
+      <c r="H41" s="198"/>
+      <c r="I41" s="198"/>
+      <c r="J41" s="198"/>
+      <c r="K41" s="198"/>
+      <c r="L41" s="198"/>
+      <c r="M41" s="198"/>
+      <c r="N41" s="198"/>
+    </row>
+    <row r="42" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C42" s="198"/>
+      <c r="D42" s="198"/>
+      <c r="E42" s="198"/>
+      <c r="F42" s="198"/>
+      <c r="G42" s="198"/>
+      <c r="H42" s="198"/>
+      <c r="I42" s="198"/>
+      <c r="J42" s="198"/>
+      <c r="K42" s="198"/>
+      <c r="L42" s="198"/>
+      <c r="M42" s="198"/>
+      <c r="N42" s="198"/>
+    </row>
+    <row r="43" spans="1:17" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C43" s="198"/>
+      <c r="D43" s="198"/>
+      <c r="E43" s="198"/>
+      <c r="F43" s="198"/>
+      <c r="G43" s="198"/>
+      <c r="H43" s="198"/>
+      <c r="I43" s="198"/>
+      <c r="J43" s="198"/>
+      <c r="K43" s="198"/>
+      <c r="L43" s="198"/>
+      <c r="M43" s="198"/>
+      <c r="N43" s="198"/>
+    </row>
+    <row r="44" spans="1:17" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C44" s="198"/>
+      <c r="D44" s="198"/>
+      <c r="E44" s="198"/>
+      <c r="F44" s="198"/>
+      <c r="G44" s="198"/>
+      <c r="H44" s="198"/>
+      <c r="I44" s="198"/>
+      <c r="J44" s="198"/>
+      <c r="K44" s="198"/>
+      <c r="L44" s="198"/>
+      <c r="M44" s="198"/>
+      <c r="N44" s="198"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="C39:N44"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="M11:M12"/>
     <mergeCell ref="E1:N1"/>
     <mergeCell ref="I11:I12"/>
     <mergeCell ref="F11:F12"/>
@@ -4723,6 +4681,12 @@
     <mergeCell ref="A9:P9"/>
     <mergeCell ref="A10:P10"/>
     <mergeCell ref="L11:L12"/>
+    <mergeCell ref="C39:N44"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="M11:M12"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" orientation="landscape" r:id="rId1"/>
@@ -4732,36 +4696,36 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E11DE44-94AC-4627-8367-E065E39D764D}">
   <dimension ref="B2:O32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" customWidth="1"/>
+    <col min="2" max="2" width="8.44140625" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="15.28515625" customWidth="1"/>
-    <col min="7" max="7" width="1.85546875" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" customWidth="1"/>
-    <col min="10" max="10" width="1.85546875" customWidth="1"/>
-    <col min="11" max="11" width="19.5703125" style="101" customWidth="1"/>
-    <col min="12" max="12" width="2.140625" customWidth="1"/>
-    <col min="13" max="13" width="19.7109375" style="102" customWidth="1"/>
+    <col min="6" max="6" width="15.33203125" customWidth="1"/>
+    <col min="7" max="7" width="1.88671875" customWidth="1"/>
+    <col min="8" max="8" width="10.5546875" customWidth="1"/>
+    <col min="9" max="9" width="14.33203125" customWidth="1"/>
+    <col min="10" max="10" width="1.88671875" customWidth="1"/>
+    <col min="11" max="11" width="19.5546875" style="101" customWidth="1"/>
+    <col min="12" max="12" width="2.109375" customWidth="1"/>
+    <col min="13" max="13" width="19.6640625" style="102" customWidth="1"/>
     <col min="14" max="14" width="2" customWidth="1"/>
-    <col min="15" max="15" width="15.28515625" style="167" customWidth="1"/>
+    <col min="15" max="15" width="15.33203125" style="167" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="D2" s="236" t="s">
+    <row r="2" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="D2" s="235" t="s">
         <v>135</v>
       </c>
-      <c r="E2" s="236"/>
-      <c r="F2" s="236"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="237" t="s">
+      <c r="H2" s="236" t="s">
         <v>136</v>
       </c>
-      <c r="I2" s="238"/>
+      <c r="I2" s="237"/>
       <c r="J2" s="1"/>
       <c r="K2" s="190" t="s">
         <v>137</v>
@@ -4773,7 +4737,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B3" s="99" t="s">
         <v>79</v>
       </c>
@@ -4799,7 +4763,7 @@
       <c r="M3" s="100"/>
       <c r="O3" s="190"/>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B4" s="178">
         <v>1</v>
       </c>
@@ -4834,7 +4798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B5" s="99">
         <v>1</v>
       </c>
@@ -4868,7 +4832,7 @@
         <v>125263.16548665638</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B6" s="178">
         <v>1</v>
       </c>
@@ -4903,7 +4867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B7" s="178">
         <v>2</v>
       </c>
@@ -4938,7 +4902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B8" s="178">
         <v>2</v>
       </c>
@@ -4973,7 +4937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B9" s="178">
         <v>2</v>
       </c>
@@ -5008,7 +4972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B10" s="178">
         <v>2</v>
       </c>
@@ -5043,7 +5007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B11" s="178">
         <v>3</v>
       </c>
@@ -5078,7 +5042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B12" s="99">
         <v>3</v>
       </c>
@@ -5112,7 +5076,7 @@
         <v>98658.340164570633</v>
       </c>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B13" s="178">
         <v>3</v>
       </c>
@@ -5147,7 +5111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B14" s="178">
         <v>3</v>
       </c>
@@ -5182,7 +5146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B15" s="178">
         <v>4</v>
       </c>
@@ -5217,7 +5181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B16" s="178">
         <v>4</v>
       </c>
@@ -5252,7 +5216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B17" s="178">
         <v>4</v>
       </c>
@@ -5287,7 +5251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B18" s="178">
         <v>4</v>
       </c>
@@ -5322,7 +5286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B19" s="178"/>
       <c r="C19" s="178"/>
       <c r="D19" s="179"/>
@@ -5334,7 +5298,7 @@
       <c r="M19" s="100"/>
       <c r="O19" s="190"/>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B20" s="99"/>
       <c r="C20" s="99" t="s">
         <v>141</v>
@@ -5366,7 +5330,7 @@
         <v>223921.50565122702</v>
       </c>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B21" s="99"/>
       <c r="C21" s="99"/>
       <c r="D21" s="4"/>
@@ -5375,7 +5339,7 @@
       </c>
       <c r="F21" s="4"/>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B22" s="99" t="s">
         <v>85</v>
       </c>
@@ -5403,7 +5367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B23" s="99" t="s">
         <v>85</v>
       </c>
@@ -5431,7 +5395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B24" s="99" t="s">
         <v>85</v>
       </c>
@@ -5459,7 +5423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B25" s="99" t="s">
         <v>85</v>
       </c>
@@ -5487,7 +5451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B26" s="99" t="s">
         <v>85</v>
       </c>
@@ -5515,7 +5479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B27" s="99" t="s">
         <v>85</v>
       </c>
@@ -5543,7 +5507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B28" s="99" t="s">
         <v>85</v>
       </c>
@@ -5571,7 +5535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B29" s="99" t="s">
         <v>85</v>
       </c>
@@ -5599,7 +5563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
       <c r="H30" s="190" t="s">
         <v>130</v>
       </c>
@@ -5607,7 +5571,7 @@
         <f>SUM(I22:I29)</f>
         <v>1903.8315368098165</v>
       </c>
-      <c r="K30" s="193">
+      <c r="K30" s="192">
         <f>SUM(K22:K29)</f>
         <v>1903.8315368098165</v>
       </c>
@@ -5620,14 +5584,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
       <c r="O31" s="142"/>
     </row>
-    <row r="32" spans="2:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="D32" s="239" t="s">
+    <row r="32" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="D32" s="238" t="s">
         <v>131</v>
       </c>
-      <c r="E32" s="240"/>
+      <c r="E32" s="239"/>
       <c r="F32" s="168">
         <v>265234.65000000002</v>
       </c>
@@ -5661,9 +5625,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B474AF3-BA14-4AC3-BE41-D99CD4C43EE8}">
   <dimension ref="C3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="3" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C3" s="169" t="s">
         <v>132</v>
       </c>
